--- a/youzi/徐晓/index.xlsx
+++ b/youzi/徐晓/index.xlsx
@@ -45,66 +45,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -117,19 +57,109 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -141,13 +171,1771 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD8AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -159,91 +1947,115 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -261,13 +2073,505 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -279,37 +2583,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -321,37 +2685,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -369,61 +2769,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,97 +2829,487 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD8AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -537,19 +3321,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,127 +3393,235 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -693,2947 +3633,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9994,7 +9994,7 @@
       <c r="C2" t="str">
         <v>600120</v>
       </c>
-      <c r="D2" s="12" t="str">
+      <c r="D2" s="2" t="str">
         <v>净卖: -1.33亿</v>
       </c>
       <c r="E2">
@@ -10009,40 +10009,40 @@
       <c r="H2">
         <v>9.97</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2" s="3">
         <v>-12.49</v>
       </c>
-      <c r="J2" s="13">
+      <c r="J2" s="4">
         <v>-21.25</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="9">
         <v>-22.96</v>
       </c>
-      <c r="L2" s="2">
+      <c r="L2" s="10">
         <v>-26.08</v>
       </c>
-      <c r="M2" s="3">
+      <c r="M2" s="12">
         <v>-20.85</v>
       </c>
-      <c r="N2" s="6">
+      <c r="N2" s="5">
         <v>-20.85</v>
       </c>
-      <c r="O2" s="8">
+      <c r="O2" s="13">
         <v>-22.16</v>
       </c>
-      <c r="P2" s="9">
+      <c r="P2" s="6">
         <v>-26.28</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="7">
         <v>-25.48</v>
       </c>
-      <c r="R2" s="4">
+      <c r="R2" s="11">
         <v>-24.07</v>
       </c>
-      <c r="S2" s="7">
+      <c r="S2" s="1">
         <v>-25.78</v>
       </c>
-      <c r="T2" s="11">
+      <c r="T2" s="8">
         <v>-42.3</v>
       </c>
     </row>
@@ -10056,7 +10056,7 @@
       <c r="C3" t="str">
         <v>003021</v>
       </c>
-      <c r="D3" s="20" t="str">
+      <c r="D3" s="16" t="str">
         <v>净卖: -3895.40万</v>
       </c>
       <c r="E3">
@@ -10071,40 +10071,40 @@
       <c r="H3">
         <v>-3</v>
       </c>
-      <c r="I3" s="21">
+      <c r="I3" s="26">
         <v>-7.22</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="17">
         <v>-10.22</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="22">
         <v>-4.57</v>
       </c>
-      <c r="L3" s="26">
+      <c r="L3" s="18">
         <v>-7.52</v>
       </c>
-      <c r="M3" s="23">
+      <c r="M3" s="19">
         <v>-0.02</v>
       </c>
-      <c r="N3" s="19">
+      <c r="N3" s="20">
         <v>4.27</v>
       </c>
-      <c r="O3" s="18">
+      <c r="O3" s="21">
         <v>5.17</v>
       </c>
-      <c r="P3" s="24">
+      <c r="P3" s="14">
         <v>3.7</v>
       </c>
-      <c r="Q3" s="14">
+      <c r="Q3" s="23">
         <v>13.88</v>
       </c>
-      <c r="R3" s="25">
+      <c r="R3" s="15">
         <v>25.27</v>
       </c>
-      <c r="S3" s="15">
+      <c r="S3" s="24">
         <v>24.52</v>
       </c>
-      <c r="T3" s="16">
+      <c r="T3" s="25">
         <v>-19.33</v>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       <c r="C4" t="str">
         <v>002896</v>
       </c>
-      <c r="D4" s="36" t="str">
+      <c r="D4" s="32" t="str">
         <v>净买: 5162.35万</v>
       </c>
       <c r="E4">
@@ -10133,40 +10133,40 @@
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="33">
+      <c r="I4" s="38">
         <v>6.79</v>
       </c>
-      <c r="J4" s="37">
+      <c r="J4" s="29">
         <v>17.47</v>
       </c>
-      <c r="K4" s="38">
+      <c r="K4" s="39">
         <v>5.82</v>
       </c>
-      <c r="L4" s="27">
+      <c r="L4" s="30">
         <v>15.69</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="27">
         <v>27.26</v>
       </c>
-      <c r="N4" s="34">
+      <c r="N4" s="28">
         <v>39.98</v>
       </c>
-      <c r="O4" s="29">
+      <c r="O4" s="33">
         <v>25.98</v>
       </c>
-      <c r="P4" s="31">
+      <c r="P4" s="34">
         <v>13.39</v>
       </c>
-      <c r="Q4" s="39">
+      <c r="Q4" s="35">
         <v>16.45</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="36">
         <v>19.91</v>
       </c>
-      <c r="S4" s="32">
+      <c r="S4" s="31">
         <v>19.53</v>
       </c>
-      <c r="T4" s="35">
+      <c r="T4" s="37">
         <v>-10.2</v>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       <c r="C5" t="str">
         <v>600602</v>
       </c>
-      <c r="D5" s="47" t="str">
+      <c r="D5" s="43" t="str">
         <v>净买: 1.03亿</v>
       </c>
       <c r="E5">
@@ -10195,40 +10195,40 @@
       <c r="H5">
         <v>-2.66</v>
       </c>
-      <c r="I5" s="43">
+      <c r="I5" s="44">
         <v>10.77</v>
       </c>
-      <c r="J5" s="41">
+      <c r="J5" s="50">
         <v>5.81</v>
       </c>
-      <c r="K5" s="48">
+      <c r="K5" s="45">
         <v>-3.88</v>
       </c>
-      <c r="L5" s="42">
+      <c r="L5" s="46">
         <v>-13.5</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="51">
         <v>-15.88</v>
       </c>
-      <c r="N5" s="45">
+      <c r="N5" s="47">
         <v>-14.23</v>
       </c>
-      <c r="O5" s="46">
+      <c r="O5" s="52">
         <v>-8.5</v>
       </c>
-      <c r="P5" s="49">
+      <c r="P5" s="40">
         <v>-5.04</v>
       </c>
-      <c r="Q5" s="50">
+      <c r="Q5" s="48">
         <v>4.46</v>
       </c>
-      <c r="R5" s="51">
+      <c r="R5" s="49">
         <v>6.31</v>
       </c>
-      <c r="S5" s="52">
+      <c r="S5" s="41">
         <v>10.62</v>
       </c>
-      <c r="T5" s="40">
+      <c r="T5" s="42">
         <v>-7.38</v>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       <c r="C6" t="str">
         <v>003021</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="56" t="str">
         <v>净买: 5581.43万</v>
       </c>
       <c r="E6">
@@ -10257,40 +10257,40 @@
       <c r="H6">
         <v>-1.3</v>
       </c>
-      <c r="I6" s="57">
+      <c r="I6" s="60">
         <v>11.45</v>
       </c>
-      <c r="J6" s="56">
+      <c r="J6" s="57">
         <v>10.79</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="53">
         <v>-0.29</v>
       </c>
-      <c r="L6" s="61">
+      <c r="L6" s="58">
         <v>-5.12</v>
       </c>
-      <c r="M6" s="64">
+      <c r="M6" s="59">
         <v>4.3</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="61">
         <v>14.73</v>
       </c>
-      <c r="O6" s="65">
+      <c r="O6" s="54">
         <v>13.05</v>
       </c>
-      <c r="P6" s="59">
+      <c r="P6" s="63">
         <v>12.06</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="62">
         <v>13.73</v>
       </c>
-      <c r="R6" s="62">
+      <c r="R6" s="55">
         <v>10.86</v>
       </c>
-      <c r="S6" s="63">
+      <c r="S6" s="64">
         <v>10.2</v>
       </c>
-      <c r="T6" s="54">
+      <c r="T6" s="65">
         <v>-28.23</v>
       </c>
     </row>
@@ -10319,40 +10319,40 @@
       <c r="H7">
         <v>-5.38</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="69">
         <v>-4.11</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="76">
         <v>-13.74</v>
       </c>
       <c r="K7" s="70">
         <v>-21.64</v>
       </c>
-      <c r="L7" s="74">
+      <c r="L7" s="72">
         <v>-19.75</v>
       </c>
-      <c r="M7" s="75">
+      <c r="M7" s="67">
         <v>-18.96</v>
       </c>
-      <c r="N7" s="71">
+      <c r="N7" s="77">
         <v>-16.9</v>
       </c>
-      <c r="O7" s="72">
+      <c r="O7" s="78">
         <v>-18.64</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="73">
         <v>-16.27</v>
       </c>
-      <c r="Q7" s="78">
+      <c r="Q7" s="74">
         <v>-17.06</v>
       </c>
-      <c r="R7" s="68">
+      <c r="R7" s="75">
         <v>-16.75</v>
       </c>
-      <c r="S7" s="73">
+      <c r="S7" s="68">
         <v>-19.59</v>
       </c>
-      <c r="T7" s="69">
+      <c r="T7" s="71">
         <v>-2.21</v>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       <c r="C8" t="str">
         <v>003021</v>
       </c>
-      <c r="D8" s="87" t="str">
+      <c r="D8" s="88" t="str">
         <v>净卖: -7322.64万</v>
       </c>
       <c r="E8">
@@ -10381,40 +10381,40 @@
       <c r="H8">
         <v>-1.2</v>
       </c>
-      <c r="I8" s="79">
+      <c r="I8" s="85">
         <v>11.33</v>
       </c>
-      <c r="J8" s="88">
+      <c r="J8" s="89">
         <v>9.7</v>
       </c>
-      <c r="K8" s="83">
+      <c r="K8" s="82">
         <v>8.74</v>
       </c>
-      <c r="L8" s="80">
+      <c r="L8" s="83">
         <v>10.37</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="90">
         <v>7.58</v>
       </c>
-      <c r="N8" s="84">
+      <c r="N8" s="91">
         <v>6.94</v>
       </c>
-      <c r="O8" s="85">
+      <c r="O8" s="79">
         <v>-0.96</v>
       </c>
-      <c r="P8" s="81">
+      <c r="P8" s="84">
         <v>1.12</v>
       </c>
       <c r="Q8" s="86">
         <v>2.48</v>
       </c>
-      <c r="R8" s="90">
+      <c r="R8" s="80">
         <v>-0.05</v>
       </c>
-      <c r="S8" s="91">
+      <c r="S8" s="81">
         <v>-2.14</v>
       </c>
-      <c r="T8" s="82">
+      <c r="T8" s="87">
         <v>-30.35</v>
       </c>
     </row>
@@ -10428,7 +10428,7 @@
       <c r="C9" t="str">
         <v>002261</v>
       </c>
-      <c r="D9" s="101" t="str">
+      <c r="D9" s="95" t="str">
         <v>净卖: -1.12亿</v>
       </c>
       <c r="E9">
@@ -10443,40 +10443,40 @@
       <c r="H9">
         <v>-3.17</v>
       </c>
-      <c r="I9" s="104">
+      <c r="I9" s="103">
         <v>-7.06</v>
       </c>
-      <c r="J9" s="92">
+      <c r="J9" s="104">
         <v>-13.04</v>
       </c>
-      <c r="K9" s="93">
+      <c r="K9" s="92">
         <v>-11.69</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="100">
         <v>-10.05</v>
       </c>
-      <c r="M9" s="96">
+      <c r="M9" s="98">
         <v>-11.15</v>
       </c>
-      <c r="N9" s="98">
+      <c r="N9" s="93">
         <v>-12.48</v>
       </c>
-      <c r="O9" s="94">
+      <c r="O9" s="96">
         <v>-11.61</v>
       </c>
-      <c r="P9" s="102">
+      <c r="P9" s="94">
         <v>-10.56</v>
       </c>
-      <c r="Q9" s="99">
+      <c r="Q9" s="97">
         <v>-12.51</v>
       </c>
-      <c r="R9" s="103">
+      <c r="R9" s="99">
         <v>-9.97</v>
       </c>
-      <c r="S9" s="100">
+      <c r="S9" s="101">
         <v>-18.06</v>
       </c>
-      <c r="T9" s="97">
+      <c r="T9" s="102">
         <v>-3.68</v>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       <c r="C10" t="str">
         <v>000799</v>
       </c>
-      <c r="D10" s="108" t="str">
+      <c r="D10" s="113" t="str">
         <v>净卖: -41.89万</v>
       </c>
       <c r="E10">
@@ -10505,40 +10505,40 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="111">
+      <c r="I10" s="117">
         <v>10.01</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="110">
         <v>9.1</v>
       </c>
-      <c r="K10" s="110">
+      <c r="K10" s="114">
         <v>8.38</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="115">
         <v>7.23</v>
       </c>
-      <c r="M10" s="113">
+      <c r="M10" s="111">
         <v>5.75</v>
       </c>
-      <c r="N10" s="106">
+      <c r="N10" s="108">
         <v>5</v>
       </c>
-      <c r="O10" s="115">
+      <c r="O10" s="112">
         <v>4.96</v>
       </c>
-      <c r="P10" s="114">
+      <c r="P10" s="109">
         <v>6.34</v>
       </c>
-      <c r="Q10" s="116">
+      <c r="Q10" s="105">
         <v>5.62</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="106">
         <v>4.79</v>
       </c>
       <c r="S10" s="107">
         <v>1.89</v>
       </c>
-      <c r="T10" s="105">
+      <c r="T10" s="116">
         <v>-8.59</v>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       <c r="C11" t="str">
         <v>688108</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="124" t="str">
         <v>净买: 3339.73万</v>
       </c>
       <c r="E11">
@@ -10567,40 +10567,40 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="126">
+      <c r="I11" s="130">
         <v>14.27</v>
       </c>
-      <c r="J11" s="120">
+      <c r="J11" s="118">
         <v>11.35</v>
       </c>
-      <c r="K11" s="130">
+      <c r="K11" s="125">
         <v>2.7</v>
       </c>
-      <c r="L11" s="118">
+      <c r="L11" s="126">
         <v>-5.73</v>
       </c>
       <c r="M11" s="119">
         <v>-9.92</v>
       </c>
-      <c r="N11" s="121">
+      <c r="N11" s="120">
         <v>-8.04</v>
       </c>
-      <c r="O11" s="127">
+      <c r="O11" s="121">
         <v>-12.4</v>
       </c>
-      <c r="P11" s="122">
+      <c r="P11" s="127">
         <v>-16.72</v>
       </c>
       <c r="Q11" s="123">
         <v>-12.2</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="122">
         <v>-8.57</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="128">
         <v>-6.23</v>
       </c>
-      <c r="T11" s="124">
+      <c r="T11" s="129">
         <v>-40.94</v>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       <c r="C12" t="str">
         <v>300222</v>
       </c>
-      <c r="D12" s="138" t="str">
+      <c r="D12" s="140" t="str">
         <v>净卖: -6818.64万</v>
       </c>
       <c r="E12">
@@ -10629,40 +10629,40 @@
       <c r="H12">
         <v>2.15</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="141">
         <v>16.68</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="136">
         <v>11.46</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="137">
         <v>5.46</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="134">
         <v>3.27</v>
       </c>
-      <c r="M12" s="137">
+      <c r="M12" s="142">
         <v>4.13</v>
       </c>
       <c r="N12" s="131">
         <v>-1.95</v>
       </c>
-      <c r="O12" s="132">
+      <c r="O12" s="135">
         <v>-3.66</v>
       </c>
-      <c r="P12" s="133">
+      <c r="P12" s="132">
         <v>-0.94</v>
       </c>
-      <c r="Q12" s="139">
+      <c r="Q12" s="133">
         <v>1.56</v>
       </c>
-      <c r="R12" s="141">
+      <c r="R12" s="143">
         <v>-1.56</v>
       </c>
-      <c r="S12" s="142">
+      <c r="S12" s="138">
         <v>-0.78</v>
       </c>
-      <c r="T12" s="134">
+      <c r="T12" s="139">
         <v>-12.63</v>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       <c r="C13" t="str">
         <v>002837</v>
       </c>
-      <c r="D13" s="153" t="str">
+      <c r="D13" s="155" t="str">
         <v>净买: 1.07亿</v>
       </c>
       <c r="E13">
@@ -10691,13 +10691,13 @@
       <c r="H13">
         <v>-3.13</v>
       </c>
-      <c r="I13" s="154">
+      <c r="I13" s="147">
         <v>13.56</v>
       </c>
-      <c r="J13" s="147">
+      <c r="J13" s="150">
         <v>14.94</v>
       </c>
-      <c r="K13" s="155">
+      <c r="K13" s="156">
         <v>15.17</v>
       </c>
       <c r="L13" s="144">
@@ -10709,22 +10709,22 @@
       <c r="N13" s="145">
         <v>-2.76</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="151">
         <v>2.11</v>
       </c>
-      <c r="P13" s="150">
+      <c r="P13" s="153">
         <v>-0.68</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="154">
         <v>-3.52</v>
       </c>
-      <c r="R13" s="146">
+      <c r="R13" s="152">
         <v>3.92</v>
       </c>
-      <c r="S13" s="156">
+      <c r="S13" s="149">
         <v>8.92</v>
       </c>
-      <c r="T13" s="152">
+      <c r="T13" s="146">
         <v>59.01</v>
       </c>
     </row>
@@ -10738,7 +10738,7 @@
       <c r="C14" t="str">
         <v>600521</v>
       </c>
-      <c r="D14" s="166" t="str">
+      <c r="D14" s="163" t="str">
         <v>净买: 2288.75万</v>
       </c>
       <c r="E14">
@@ -10753,40 +10753,40 @@
       <c r="H14">
         <v>-0.63</v>
       </c>
-      <c r="I14" s="160">
+      <c r="I14" s="159">
         <v>-9.43</v>
       </c>
-      <c r="J14" s="167">
+      <c r="J14" s="160">
         <v>-8.27</v>
       </c>
-      <c r="K14" s="164">
+      <c r="K14" s="167">
         <v>-12.18</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="161">
         <v>-7.04</v>
       </c>
-      <c r="M14" s="158">
+      <c r="M14" s="168">
         <v>-9.99</v>
       </c>
-      <c r="N14" s="168">
+      <c r="N14" s="169">
         <v>-12.07</v>
       </c>
-      <c r="O14" s="161">
+      <c r="O14" s="164">
         <v>-12</v>
       </c>
       <c r="P14" s="162">
         <v>-13.97</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="157">
         <v>-14.46</v>
       </c>
-      <c r="R14" s="159">
+      <c r="R14" s="165">
         <v>-16.47</v>
       </c>
-      <c r="S14" s="169">
+      <c r="S14" s="158">
         <v>-19.15</v>
       </c>
-      <c r="T14" s="165">
+      <c r="T14" s="166">
         <v>-37.11</v>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       <c r="C15" t="str">
         <v>600629</v>
       </c>
-      <c r="D15" s="174" t="str">
+      <c r="D15" s="170" t="str">
         <v>净卖: -1267.40万</v>
       </c>
       <c r="E15">
@@ -10815,34 +10815,34 @@
       <c r="H15">
         <v>7.68</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="179">
         <v>2.16</v>
       </c>
-      <c r="J15" s="182">
+      <c r="J15" s="177">
         <v>12.36</v>
       </c>
-      <c r="K15" s="178">
+      <c r="K15" s="180">
         <v>23.61</v>
       </c>
-      <c r="L15" s="170">
+      <c r="L15" s="181">
         <v>18.97</v>
       </c>
-      <c r="M15" s="179">
+      <c r="M15" s="174">
         <v>17.66</v>
       </c>
-      <c r="N15" s="171">
+      <c r="N15" s="175">
         <v>25.9</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="182">
         <v>25.51</v>
       </c>
-      <c r="P15" s="175">
+      <c r="P15" s="178">
         <v>28.19</v>
       </c>
-      <c r="Q15" s="180">
+      <c r="Q15" s="171">
         <v>28.12</v>
       </c>
-      <c r="R15" s="181">
+      <c r="R15" s="172">
         <v>40.94</v>
       </c>
       <c r="S15" s="173">
@@ -10862,7 +10862,7 @@
       <c r="C16" t="str">
         <v>600403</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="188" t="str">
         <v>净买: 1894.16万</v>
       </c>
       <c r="E16">
@@ -10877,13 +10877,13 @@
       <c r="H16">
         <v>-2.81</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="193">
         <v>9.03</v>
       </c>
-      <c r="J16" s="189">
+      <c r="J16" s="184">
         <v>-1.93</v>
       </c>
-      <c r="K16" s="183">
+      <c r="K16" s="189">
         <v>-0.24</v>
       </c>
       <c r="L16" s="185">
@@ -10892,25 +10892,25 @@
       <c r="M16" s="190">
         <v>9.27</v>
       </c>
-      <c r="N16" s="186">
+      <c r="N16" s="191">
         <v>6.74</v>
       </c>
-      <c r="O16" s="187">
+      <c r="O16" s="194">
         <v>10.95</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="195">
         <v>22.02</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="186">
         <v>34.18</v>
       </c>
-      <c r="R16" s="191">
+      <c r="R16" s="183">
         <v>23.47</v>
       </c>
-      <c r="S16" s="193">
+      <c r="S16" s="187">
         <v>11.07</v>
       </c>
-      <c r="T16" s="194">
+      <c r="T16" s="192">
         <v>-31.77</v>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       <c r="C17" t="str">
         <v>600403</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="207" t="str">
         <v>净卖: -1651.88万</v>
       </c>
       <c r="E17">
@@ -10939,40 +10939,40 @@
       <c r="H17">
         <v>-7.84</v>
       </c>
-      <c r="I17" s="208">
+      <c r="I17" s="196">
         <v>-2.4</v>
       </c>
-      <c r="J17" s="196">
+      <c r="J17" s="208">
         <v>-0.72</v>
       </c>
-      <c r="K17" s="204">
+      <c r="K17" s="199">
         <v>-1.2</v>
       </c>
-      <c r="L17" s="201">
+      <c r="L17" s="204">
         <v>8.74</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="197">
         <v>6.23</v>
       </c>
-      <c r="N17" s="200">
+      <c r="N17" s="198">
         <v>10.42</v>
       </c>
-      <c r="O17" s="206">
+      <c r="O17" s="200">
         <v>21.44</v>
       </c>
-      <c r="P17" s="202">
+      <c r="P17" s="201">
         <v>33.53</v>
       </c>
-      <c r="Q17" s="207">
+      <c r="Q17" s="202">
         <v>22.87</v>
       </c>
-      <c r="R17" s="197">
+      <c r="R17" s="203">
         <v>10.54</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="205">
         <v>-0.48</v>
       </c>
-      <c r="T17" s="198">
+      <c r="T17" s="206">
         <v>-32.1</v>
       </c>
     </row>
@@ -10986,7 +10986,7 @@
       <c r="C18" t="str">
         <v>000799</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="209" t="str">
         <v>净卖: -4574.20万</v>
       </c>
       <c r="E18">
@@ -11001,40 +11001,40 @@
       <c r="H18">
         <v>-0.22</v>
       </c>
-      <c r="I18" s="217">
+      <c r="I18" s="210">
         <v>10.23</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="211">
         <v>11.19</v>
       </c>
-      <c r="K18" s="215">
+      <c r="K18" s="216">
         <v>9.73</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="217">
         <v>12.16</v>
       </c>
-      <c r="M18" s="209">
+      <c r="M18" s="218">
         <v>9.55</v>
       </c>
-      <c r="N18" s="210">
+      <c r="N18" s="212">
         <v>8.7</v>
       </c>
-      <c r="O18" s="211">
+      <c r="O18" s="213">
         <v>6.71</v>
       </c>
-      <c r="P18" s="213">
+      <c r="P18" s="219">
         <v>4.16</v>
       </c>
-      <c r="Q18" s="216">
+      <c r="Q18" s="214">
         <v>2.68</v>
       </c>
-      <c r="R18" s="212">
+      <c r="R18" s="220">
         <v>-2.26</v>
       </c>
-      <c r="S18" s="218">
+      <c r="S18" s="215">
         <v>-4.4</v>
       </c>
-      <c r="T18" s="214">
+      <c r="T18" s="221">
         <v>-27.91</v>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       <c r="C19" t="str">
         <v>000069</v>
       </c>
-      <c r="D19" s="224" t="str">
+      <c r="D19" s="223" t="str">
         <v>净卖: -7553.88万</v>
       </c>
       <c r="E19">
@@ -11063,40 +11063,40 @@
       <c r="H19">
         <v>1.88</v>
       </c>
-      <c r="I19" s="225">
+      <c r="I19" s="233">
         <v>8.12</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="227">
         <v>3.69</v>
       </c>
-      <c r="K19" s="222">
+      <c r="K19" s="224">
         <v>4.06</v>
       </c>
-      <c r="L19" s="223">
+      <c r="L19" s="228">
         <v>2.95</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="234">
         <v>4.8</v>
       </c>
-      <c r="N19" s="227">
+      <c r="N19" s="225">
         <v>0.37</v>
       </c>
-      <c r="O19" s="228">
+      <c r="O19" s="229">
         <v>-2.95</v>
       </c>
-      <c r="P19" s="229">
+      <c r="P19" s="226">
         <v>0</v>
       </c>
       <c r="Q19" s="231">
         <v>-1.11</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="230">
         <v>-1.85</v>
       </c>
-      <c r="S19" s="233">
+      <c r="S19" s="232">
         <v>0</v>
       </c>
-      <c r="T19" s="234">
+      <c r="T19" s="222">
         <v>-17.71</v>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       <c r="C20" t="str">
         <v>002709</v>
       </c>
-      <c r="D20" s="243" t="str">
+      <c r="D20" s="244" t="str">
         <v>净买: 1.65亿</v>
       </c>
       <c r="E20">
@@ -11125,25 +11125,25 @@
       <c r="H20">
         <v>1.37</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="238">
         <v>8.51</v>
       </c>
-      <c r="J20" s="241">
+      <c r="J20" s="247">
         <v>7.15</v>
       </c>
       <c r="K20" s="235">
         <v>9.4</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="242">
         <v>-1.54</v>
       </c>
-      <c r="M20" s="240">
+      <c r="M20" s="236">
         <v>3.1</v>
       </c>
       <c r="N20" s="237">
         <v>1.91</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="243">
         <v>-8.25</v>
       </c>
       <c r="P20" s="245">
@@ -11155,10 +11155,10 @@
       <c r="R20" s="246">
         <v>-9.03</v>
       </c>
-      <c r="S20" s="247">
+      <c r="S20" s="240">
         <v>-6.57</v>
       </c>
-      <c r="T20" s="242">
+      <c r="T20" s="241">
         <v>12.16</v>
       </c>
     </row>
@@ -11172,7 +11172,7 @@
       <c r="C21" t="str">
         <v>300497</v>
       </c>
-      <c r="D21" s="253" t="str">
+      <c r="D21" s="255" t="str">
         <v>净买: 4667.27万</v>
       </c>
       <c r="E21">
@@ -11187,13 +11187,13 @@
       <c r="H21">
         <v>3.39</v>
       </c>
-      <c r="I21" s="254">
+      <c r="I21" s="253">
         <v>8.46</v>
       </c>
-      <c r="J21" s="255">
+      <c r="J21" s="249">
         <v>-7.74</v>
       </c>
-      <c r="K21" s="249">
+      <c r="K21" s="251">
         <v>-6.92</v>
       </c>
       <c r="L21" s="250">
@@ -11202,25 +11202,25 @@
       <c r="M21" s="256">
         <v>-20</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="257">
         <v>-17.49</v>
       </c>
       <c r="O21" s="252">
         <v>-15.9</v>
       </c>
-      <c r="P21" s="257">
+      <c r="P21" s="258">
         <v>-19.69</v>
       </c>
-      <c r="Q21" s="258">
+      <c r="Q21" s="259">
         <v>-16.56</v>
       </c>
-      <c r="R21" s="251">
+      <c r="R21" s="260">
         <v>-17.03</v>
       </c>
-      <c r="S21" s="260">
+      <c r="S21" s="248">
         <v>-17.59</v>
       </c>
-      <c r="T21" s="248">
+      <c r="T21" s="254">
         <v>-3.38</v>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       <c r="C22" t="str">
         <v>600343</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="264" t="str">
         <v>净卖: -1.50亿</v>
       </c>
       <c r="E22">
@@ -11249,10 +11249,10 @@
       <c r="H22">
         <v>-2.42</v>
       </c>
-      <c r="I22" s="261">
+      <c r="I22" s="263">
         <v>5.68</v>
       </c>
-      <c r="J22" s="267">
+      <c r="J22" s="272">
         <v>9.44</v>
       </c>
       <c r="K22" s="268">
@@ -11261,28 +11261,28 @@
       <c r="L22" s="273">
         <v>32.45</v>
       </c>
-      <c r="M22" s="271">
+      <c r="M22" s="265">
         <v>25.78</v>
       </c>
       <c r="N22" s="269">
         <v>29.91</v>
       </c>
-      <c r="O22" s="270">
+      <c r="O22" s="261">
         <v>19.51</v>
       </c>
-      <c r="P22" s="262">
+      <c r="P22" s="266">
         <v>20.5</v>
       </c>
-      <c r="Q22" s="263">
+      <c r="Q22" s="262">
         <v>27.5</v>
       </c>
-      <c r="R22" s="272">
+      <c r="R22" s="267">
         <v>22.58</v>
       </c>
-      <c r="S22" s="264">
+      <c r="S22" s="270">
         <v>25.45</v>
       </c>
-      <c r="T22" s="265">
+      <c r="T22" s="271">
         <v>17.76</v>
       </c>
     </row>
@@ -11296,7 +11296,7 @@
       <c r="C23" t="str">
         <v>600151</v>
       </c>
-      <c r="D23" s="277" t="str">
+      <c r="D23" s="276" t="str">
         <v>净买: 9889.49万</v>
       </c>
       <c r="E23">
@@ -11311,40 +11311,40 @@
       <c r="H23">
         <v>3.9</v>
       </c>
-      <c r="I23" s="286">
+      <c r="I23" s="281">
         <v>5.88</v>
       </c>
-      <c r="J23" s="274">
+      <c r="J23" s="278">
         <v>7.37</v>
       </c>
-      <c r="K23" s="278">
+      <c r="K23" s="279">
         <v>13.25</v>
       </c>
-      <c r="L23" s="279">
+      <c r="L23" s="282">
         <v>18.63</v>
       </c>
-      <c r="M23" s="282">
+      <c r="M23" s="283">
         <v>18</v>
       </c>
-      <c r="N23" s="275">
+      <c r="N23" s="286">
         <v>11.5</v>
       </c>
-      <c r="O23" s="283">
+      <c r="O23" s="280">
         <v>0.37</v>
       </c>
-      <c r="P23" s="276">
+      <c r="P23" s="274">
         <v>-0.62</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="284">
         <v>2.81</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="275">
         <v>3.94</v>
       </c>
-      <c r="S23" s="284">
+      <c r="S23" s="285">
         <v>14.31</v>
       </c>
-      <c r="T23" s="285">
+      <c r="T23" s="277">
         <v>-8.63</v>
       </c>
     </row>
@@ -11358,7 +11358,7 @@
       <c r="C24" t="str">
         <v>603698</v>
       </c>
-      <c r="D24" s="297" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -4244.39万</v>
       </c>
       <c r="E24">
@@ -11373,40 +11373,40 @@
       <c r="H24">
         <v>-5.05</v>
       </c>
-      <c r="I24" s="289">
+      <c r="I24" s="290">
         <v>6.05</v>
       </c>
-      <c r="J24" s="292">
+      <c r="J24" s="298">
         <v>-4.33</v>
       </c>
-      <c r="K24" s="298">
+      <c r="K24" s="295">
         <v>-4.4</v>
       </c>
-      <c r="L24" s="299">
+      <c r="L24" s="296">
         <v>5.17</v>
       </c>
-      <c r="M24" s="296">
+      <c r="M24" s="299">
         <v>7.66</v>
       </c>
-      <c r="N24" s="287">
+      <c r="N24" s="293">
         <v>18.42</v>
       </c>
-      <c r="O24" s="293">
+      <c r="O24" s="297">
         <v>30.25</v>
       </c>
-      <c r="P24" s="288">
+      <c r="P24" s="291">
         <v>43.26</v>
       </c>
-      <c r="Q24" s="294">
+      <c r="Q24" s="292">
         <v>50.8</v>
       </c>
-      <c r="R24" s="295">
+      <c r="R24" s="287">
         <v>42.08</v>
       </c>
-      <c r="S24" s="290">
+      <c r="S24" s="288">
         <v>40.89</v>
       </c>
-      <c r="T24" s="291">
+      <c r="T24" s="289">
         <v>76.84</v>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
       <c r="C25" t="str">
         <v>002149</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="306" t="str">
         <v>净买: 8459.47万</v>
       </c>
       <c r="E25">
@@ -11435,22 +11435,22 @@
       <c r="H25">
         <v>1.6</v>
       </c>
-      <c r="I25" s="305">
+      <c r="I25" s="307">
         <v>8.27</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="311">
         <v>19.1</v>
       </c>
       <c r="K25" s="302">
         <v>17.78</v>
       </c>
-      <c r="L25" s="306">
+      <c r="L25" s="308">
         <v>22.26</v>
       </c>
-      <c r="M25" s="303">
+      <c r="M25" s="309">
         <v>32.62</v>
       </c>
-      <c r="N25" s="311">
+      <c r="N25" s="303">
         <v>45.88</v>
       </c>
       <c r="O25" s="304">
@@ -11459,7 +11459,7 @@
       <c r="P25" s="312">
         <v>41.17</v>
       </c>
-      <c r="Q25" s="307">
+      <c r="Q25" s="305">
         <v>35.78</v>
       </c>
       <c r="R25" s="300">
@@ -11468,7 +11468,7 @@
       <c r="S25" s="310">
         <v>45.34</v>
       </c>
-      <c r="T25" s="308">
+      <c r="T25" s="301">
         <v>73.03</v>
       </c>
     </row>
@@ -11500,37 +11500,37 @@
       <c r="I26" s="319">
         <v>7.77</v>
       </c>
-      <c r="J26" s="314">
+      <c r="J26" s="320">
         <v>6.57</v>
       </c>
-      <c r="K26" s="315">
+      <c r="K26" s="314">
         <v>10.63</v>
       </c>
-      <c r="L26" s="320">
+      <c r="L26" s="324">
         <v>20</v>
       </c>
-      <c r="M26" s="321">
+      <c r="M26" s="315">
         <v>32</v>
       </c>
-      <c r="N26" s="322">
+      <c r="N26" s="325">
         <v>33.66</v>
       </c>
-      <c r="O26" s="316">
+      <c r="O26" s="321">
         <v>27.74</v>
       </c>
-      <c r="P26" s="323">
+      <c r="P26" s="316">
         <v>22.86</v>
       </c>
-      <c r="Q26" s="324">
+      <c r="Q26" s="317">
         <v>30.03</v>
       </c>
-      <c r="R26" s="325">
+      <c r="R26" s="313">
         <v>31.51</v>
       </c>
-      <c r="S26" s="313">
+      <c r="S26" s="322">
         <v>42.26</v>
       </c>
-      <c r="T26" s="317">
+      <c r="T26" s="323">
         <v>56.57</v>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       <c r="C27" t="str">
         <v>002149</v>
       </c>
-      <c r="D27" s="331" t="str">
+      <c r="D27" s="338" t="str">
         <v>净买: 7447.80万</v>
       </c>
       <c r="E27">
@@ -11559,40 +11559,40 @@
       <c r="H27">
         <v>0.1</v>
       </c>
-      <c r="I27" s="332">
+      <c r="I27" s="329">
         <v>9.9</v>
       </c>
-      <c r="J27" s="326">
+      <c r="J27" s="330">
         <v>11.27</v>
       </c>
-      <c r="K27" s="335">
+      <c r="K27" s="327">
         <v>6.35</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="331">
         <v>2.28</v>
       </c>
-      <c r="M27" s="327">
+      <c r="M27" s="332">
         <v>8.25</v>
       </c>
-      <c r="N27" s="337">
+      <c r="N27" s="326">
         <v>9.49</v>
       </c>
       <c r="O27" s="336">
         <v>18.43</v>
       </c>
-      <c r="P27" s="334">
+      <c r="P27" s="333">
         <v>13.87</v>
       </c>
-      <c r="Q27" s="328">
+      <c r="Q27" s="337">
         <v>17.51</v>
       </c>
-      <c r="R27" s="329">
+      <c r="R27" s="334">
         <v>20.31</v>
       </c>
-      <c r="S27" s="338">
+      <c r="S27" s="335">
         <v>22.76</v>
       </c>
-      <c r="T27" s="330">
+      <c r="T27" s="328">
         <v>30.35</v>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       <c r="C28" t="str">
         <v>301005</v>
       </c>
-      <c r="D28" s="341" t="str">
+      <c r="D28" s="344" t="str">
         <v>净买: 8304.02万</v>
       </c>
       <c r="E28">
@@ -11621,31 +11621,31 @@
       <c r="H28">
         <v>5.58</v>
       </c>
-      <c r="I28" s="342">
+      <c r="I28" s="340">
         <v>13.66</v>
       </c>
-      <c r="J28" s="343">
+      <c r="J28" s="347">
         <v>15.41</v>
       </c>
-      <c r="K28" s="344">
+      <c r="K28" s="349">
         <v>34.28</v>
       </c>
       <c r="L28" s="345">
         <v>23.58</v>
       </c>
-      <c r="M28" s="349">
+      <c r="M28" s="341">
         <v>30.8</v>
       </c>
-      <c r="N28" s="347">
+      <c r="N28" s="348">
         <v>27.1</v>
       </c>
-      <c r="O28" s="348">
+      <c r="O28" s="350">
         <v>39.67</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="342">
         <v>34.97</v>
       </c>
-      <c r="Q28" s="346">
+      <c r="Q28" s="343">
         <v>45.55</v>
       </c>
       <c r="R28" s="351">
@@ -11654,7 +11654,7 @@
       <c r="S28" s="339">
         <v>66.78</v>
       </c>
-      <c r="T28" s="340">
+      <c r="T28" s="346">
         <v>41.52</v>
       </c>
     </row>
@@ -11668,7 +11668,7 @@
       <c r="C29" t="str">
         <v>300503</v>
       </c>
-      <c r="D29" s="361" t="str">
+      <c r="D29" s="362" t="str">
         <v>净买: 6889.84万</v>
       </c>
       <c r="E29">
@@ -11683,40 +11683,40 @@
       <c r="H29">
         <v>-5.69</v>
       </c>
-      <c r="I29" s="353">
+      <c r="I29" s="355">
         <v>25.74</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="358">
         <v>25.58</v>
       </c>
-      <c r="K29" s="362">
+      <c r="K29" s="356">
         <v>19.55</v>
       </c>
-      <c r="L29" s="354">
+      <c r="L29" s="359">
         <v>22.01</v>
       </c>
-      <c r="M29" s="356">
+      <c r="M29" s="357">
         <v>17.5</v>
       </c>
-      <c r="N29" s="363">
+      <c r="N29" s="352">
         <v>19.83</v>
       </c>
-      <c r="O29" s="359">
+      <c r="O29" s="353">
         <v>27.93</v>
       </c>
-      <c r="P29" s="357">
+      <c r="P29" s="360">
         <v>36.52</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="354">
         <v>23.97</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="361">
         <v>21.09</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="363">
         <v>18.68</v>
       </c>
-      <c r="T29" s="360">
+      <c r="T29" s="364">
         <v>16.85</v>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       <c r="C30" t="str">
         <v>002565</v>
       </c>
-      <c r="D30" s="372" t="str">
+      <c r="D30" s="369" t="str">
         <v>净卖: -6558.32万</v>
       </c>
       <c r="E30">
@@ -11745,37 +11745,37 @@
       <c r="H30">
         <v>5.73</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="377">
         <v>-8.62</v>
       </c>
-      <c r="J30" s="366">
+      <c r="J30" s="374">
         <v>-4.85</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="365">
         <v>0.41</v>
       </c>
-      <c r="L30" s="375">
+      <c r="L30" s="366">
         <v>10.47</v>
       </c>
-      <c r="M30" s="367">
+      <c r="M30" s="373">
         <v>15.07</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="375">
         <v>18.11</v>
       </c>
-      <c r="O30" s="369">
+      <c r="O30" s="376">
         <v>6.3</v>
       </c>
-      <c r="P30" s="377">
+      <c r="P30" s="367">
         <v>-4.33</v>
       </c>
       <c r="Q30" s="370">
         <v>-13.88</v>
       </c>
-      <c r="R30" s="365">
+      <c r="R30" s="371">
         <v>-18.73</v>
       </c>
-      <c r="S30" s="371">
+      <c r="S30" s="372">
         <v>-18.16</v>
       </c>
       <c r="T30" s="368">
@@ -11792,7 +11792,7 @@
       <c r="C31" t="str">
         <v>002151</v>
       </c>
-      <c r="D31" s="381" t="str">
+      <c r="D31" s="385" t="str">
         <v>净买: 7582.89万</v>
       </c>
       <c r="E31">
@@ -11807,40 +11807,40 @@
       <c r="H31">
         <v>9.62</v>
       </c>
-      <c r="I31" s="388">
+      <c r="I31" s="381">
         <v>0.34</v>
       </c>
-      <c r="J31" s="382">
+      <c r="J31" s="386">
         <v>10.38</v>
       </c>
-      <c r="K31" s="383">
+      <c r="K31" s="390">
         <v>15.86</v>
       </c>
-      <c r="L31" s="384">
+      <c r="L31" s="383">
         <v>19.86</v>
       </c>
-      <c r="M31" s="389">
+      <c r="M31" s="384">
         <v>22.13</v>
       </c>
-      <c r="N31" s="390">
+      <c r="N31" s="382">
         <v>34.34</v>
       </c>
-      <c r="O31" s="385">
+      <c r="O31" s="378">
         <v>20.9</v>
       </c>
-      <c r="P31" s="378">
+      <c r="P31" s="379">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="386">
+      <c r="Q31" s="387">
         <v>5.08</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="380">
         <v>0.26</v>
       </c>
-      <c r="S31" s="379">
+      <c r="S31" s="388">
         <v>-0.74</v>
       </c>
-      <c r="T31" s="380">
+      <c r="T31" s="389">
         <v>-22.73</v>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
       <c r="C32" t="str">
         <v>601698</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 194.55万</v>
       </c>
       <c r="E32">
@@ -11869,40 +11869,40 @@
       <c r="H32">
         <v>2.6</v>
       </c>
-      <c r="I32" s="392">
+      <c r="I32" s="395">
         <v>7.2</v>
       </c>
-      <c r="J32" s="396">
+      <c r="J32" s="402">
         <v>17.92</v>
       </c>
-      <c r="K32" s="397">
+      <c r="K32" s="396">
         <v>19.67</v>
       </c>
-      <c r="L32" s="393">
+      <c r="L32" s="399">
         <v>21.47</v>
       </c>
       <c r="M32" s="403">
         <v>33.61</v>
       </c>
-      <c r="N32" s="394">
+      <c r="N32" s="391">
         <v>46.97</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="392">
         <v>32.27</v>
       </c>
-      <c r="P32" s="399">
+      <c r="P32" s="393">
         <v>19.04</v>
       </c>
       <c r="Q32" s="400">
         <v>7.15</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="394">
         <v>9.55</v>
       </c>
-      <c r="S32" s="391">
+      <c r="S32" s="401">
         <v>8.54</v>
       </c>
-      <c r="T32" s="395">
+      <c r="T32" s="397">
         <v>-7.31</v>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       <c r="C33" t="str">
         <v>603698</v>
       </c>
-      <c r="D33" s="411" t="str">
+      <c r="D33" s="410" t="str">
         <v>净买: 6020.50万</v>
       </c>
       <c r="E33">
@@ -11934,37 +11934,37 @@
       <c r="I33" s="408">
         <v>14.16</v>
       </c>
-      <c r="J33" s="414">
+      <c r="J33" s="404">
         <v>8.62</v>
       </c>
-      <c r="K33" s="416">
+      <c r="K33" s="405">
         <v>15.14</v>
       </c>
-      <c r="L33" s="404">
+      <c r="L33" s="412">
         <v>18.92</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="413">
         <v>30.81</v>
       </c>
-      <c r="N33" s="415">
+      <c r="N33" s="406">
         <v>17.73</v>
       </c>
-      <c r="O33" s="409">
+      <c r="O33" s="414">
         <v>5.95</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="407">
         <v>3.38</v>
       </c>
-      <c r="Q33" s="410">
+      <c r="Q33" s="409">
         <v>8.46</v>
       </c>
-      <c r="R33" s="413">
+      <c r="R33" s="415">
         <v>3.19</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="416">
         <v>-2.16</v>
       </c>
-      <c r="T33" s="407">
+      <c r="T33" s="411">
         <v>24.84</v>
       </c>
     </row>
@@ -11978,7 +11978,7 @@
       <c r="C34" t="str">
         <v>002202</v>
       </c>
-      <c r="D34" s="422" t="str">
+      <c r="D34" s="418" t="str">
         <v>净买: 4.15亿</v>
       </c>
       <c r="E34">
@@ -11993,40 +11993,40 @@
       <c r="H34">
         <v>9.99</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="419">
         <v>0</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="425">
         <v>9.99</v>
       </c>
-      <c r="K34" s="423">
+      <c r="K34" s="420">
         <v>6.29</v>
       </c>
-      <c r="L34" s="424">
+      <c r="L34" s="423">
         <v>4.51</v>
       </c>
-      <c r="M34" s="421">
+      <c r="M34" s="426">
         <v>-5.95</v>
       </c>
       <c r="N34" s="429">
         <v>-15.34</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="427">
         <v>-13.27</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="428">
         <v>-18.41</v>
       </c>
-      <c r="Q34" s="425">
+      <c r="Q34" s="417">
         <v>-20.32</v>
       </c>
-      <c r="R34" s="419">
+      <c r="R34" s="421">
         <v>-15.81</v>
       </c>
-      <c r="S34" s="426">
+      <c r="S34" s="424">
         <v>-7.39</v>
       </c>
-      <c r="T34" s="427">
+      <c r="T34" s="422">
         <v>-20.51</v>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       <c r="C35" t="str">
         <v>002202</v>
       </c>
-      <c r="D35" s="440" t="str">
+      <c r="D35" s="441" t="str">
         <v>净买: 3.95亿</v>
       </c>
       <c r="E35">
@@ -12055,40 +12055,40 @@
       <c r="H35">
         <v>6.42</v>
       </c>
-      <c r="I35" s="435">
+      <c r="I35" s="442">
         <v>3.35</v>
       </c>
-      <c r="J35" s="433">
+      <c r="J35" s="437">
         <v>-0.12</v>
       </c>
-      <c r="K35" s="441">
+      <c r="K35" s="438">
         <v>-1.79</v>
       </c>
-      <c r="L35" s="434">
+      <c r="L35" s="439">
         <v>-11.62</v>
       </c>
-      <c r="M35" s="436">
+      <c r="M35" s="430">
         <v>-20.45</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="435">
         <v>-18.51</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="440">
         <v>-23.33</v>
       </c>
-      <c r="P35" s="438">
+      <c r="P35" s="431">
         <v>-25.13</v>
       </c>
-      <c r="Q35" s="430">
+      <c r="Q35" s="436">
         <v>-20.89</v>
       </c>
-      <c r="R35" s="439">
+      <c r="R35" s="432">
         <v>-12.97</v>
       </c>
-      <c r="S35" s="431">
+      <c r="S35" s="433">
         <v>-16.45</v>
       </c>
-      <c r="T35" s="432">
+      <c r="T35" s="434">
         <v>-25.3</v>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       <c r="C36" t="str">
         <v>000901</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="455" t="str">
         <v>净买: 926.43万</v>
       </c>
       <c r="E36">
@@ -12120,37 +12120,37 @@
       <c r="I36" s="443">
         <v>6.61</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="447">
         <v>-4.05</v>
       </c>
       <c r="K36" s="448">
         <v>-11.42</v>
       </c>
-      <c r="L36" s="446">
+      <c r="L36" s="449">
         <v>-16.39</v>
       </c>
-      <c r="M36" s="444">
+      <c r="M36" s="452">
         <v>-14.59</v>
       </c>
-      <c r="N36" s="447">
+      <c r="N36" s="453">
         <v>-14.59</v>
       </c>
-      <c r="O36" s="453">
+      <c r="O36" s="454">
         <v>-20.53</v>
       </c>
-      <c r="P36" s="449">
+      <c r="P36" s="444">
         <v>-21.57</v>
       </c>
-      <c r="Q36" s="454">
+      <c r="Q36" s="450">
         <v>-18.98</v>
       </c>
-      <c r="R36" s="450">
+      <c r="R36" s="445">
         <v>-15.35</v>
       </c>
-      <c r="S36" s="455">
+      <c r="S36" s="446">
         <v>-23.06</v>
       </c>
-      <c r="T36" s="445">
+      <c r="T36" s="451">
         <v>-29.58</v>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       <c r="C37" t="str">
         <v>600498</v>
       </c>
-      <c r="D37" s="461" t="str">
+      <c r="D37" s="465" t="str">
         <v>净卖: -3.15亿</v>
       </c>
       <c r="E37">
@@ -12179,40 +12179,40 @@
       <c r="H37">
         <v>3.52</v>
       </c>
-      <c r="I37" s="459">
+      <c r="I37" s="466">
         <v>4.32</v>
       </c>
-      <c r="J37" s="465">
+      <c r="J37" s="458">
         <v>-6.12</v>
       </c>
-      <c r="K37" s="467">
+      <c r="K37" s="459">
         <v>-14.95</v>
       </c>
       <c r="L37" s="462">
         <v>-14.32</v>
       </c>
-      <c r="M37" s="468">
+      <c r="M37" s="460">
         <v>-19.2</v>
       </c>
-      <c r="N37" s="456">
+      <c r="N37" s="461">
         <v>-20.25</v>
       </c>
-      <c r="O37" s="460">
+      <c r="O37" s="467">
         <v>-17.13</v>
       </c>
-      <c r="P37" s="457">
+      <c r="P37" s="463">
         <v>-8.85</v>
       </c>
-      <c r="Q37" s="458">
+      <c r="Q37" s="468">
         <v>-12.45</v>
       </c>
-      <c r="R37" s="463">
+      <c r="R37" s="464">
         <v>-13.08</v>
       </c>
-      <c r="S37" s="464">
+      <c r="S37" s="456">
         <v>-11.97</v>
       </c>
-      <c r="T37" s="466">
+      <c r="T37" s="457">
         <v>7.39</v>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       <c r="C38" t="str">
         <v>002202</v>
       </c>
-      <c r="D38" s="470" t="str">
+      <c r="D38" s="473" t="str">
         <v>净卖: -1.92亿</v>
       </c>
       <c r="E38">
@@ -12241,40 +12241,40 @@
       <c r="H38">
         <v>-8.96</v>
       </c>
-      <c r="I38" s="477">
+      <c r="I38" s="474">
         <v>-1.15</v>
       </c>
-      <c r="J38" s="471">
+      <c r="J38" s="475">
         <v>-11.02</v>
       </c>
-      <c r="K38" s="472">
+      <c r="K38" s="479">
         <v>-8.85</v>
       </c>
-      <c r="L38" s="473">
+      <c r="L38" s="470">
         <v>-14.25</v>
       </c>
-      <c r="M38" s="478">
+      <c r="M38" s="480">
         <v>-16.26</v>
       </c>
-      <c r="N38" s="474">
+      <c r="N38" s="481">
         <v>-11.52</v>
       </c>
-      <c r="O38" s="475">
+      <c r="O38" s="471">
         <v>-2.67</v>
       </c>
-      <c r="P38" s="479">
+      <c r="P38" s="472">
         <v>-6.55</v>
       </c>
       <c r="Q38" s="469">
         <v>-5.92</v>
       </c>
-      <c r="R38" s="480">
+      <c r="R38" s="476">
         <v>-8.82</v>
       </c>
-      <c r="S38" s="481">
+      <c r="S38" s="477">
         <v>-11.48</v>
       </c>
-      <c r="T38" s="476">
+      <c r="T38" s="478">
         <v>-16.45</v>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       <c r="C39" t="str">
         <v>002202</v>
       </c>
-      <c r="D39" s="487" t="str">
+      <c r="D39" s="490" t="str">
         <v>净卖: -1.10亿</v>
       </c>
       <c r="E39">
@@ -12303,40 +12303,40 @@
       <c r="H39">
         <v>-9.99</v>
       </c>
-      <c r="I39" s="492">
+      <c r="I39" s="491">
         <v>0</v>
       </c>
-      <c r="J39" s="493">
+      <c r="J39" s="492">
         <v>2.44</v>
       </c>
-      <c r="K39" s="494">
+      <c r="K39" s="486">
         <v>-3.62</v>
       </c>
-      <c r="L39" s="483">
+      <c r="L39" s="493">
         <v>-5.88</v>
       </c>
-      <c r="M39" s="488">
+      <c r="M39" s="484">
         <v>-0.55</v>
       </c>
-      <c r="N39" s="489">
+      <c r="N39" s="487">
         <v>9.39</v>
       </c>
-      <c r="O39" s="490">
+      <c r="O39" s="494">
         <v>5.03</v>
       </c>
-      <c r="P39" s="484">
+      <c r="P39" s="482">
         <v>5.73</v>
       </c>
-      <c r="Q39" s="486">
+      <c r="Q39" s="488">
         <v>2.48</v>
       </c>
-      <c r="R39" s="491">
+      <c r="R39" s="485">
         <v>-0.52</v>
       </c>
-      <c r="S39" s="482">
+      <c r="S39" s="483">
         <v>-3.44</v>
       </c>
-      <c r="T39" s="485">
+      <c r="T39" s="489">
         <v>-6.1</v>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       <c r="C40" t="str">
         <v>300118</v>
       </c>
-      <c r="D40" s="507" t="str">
+      <c r="D40" s="495" t="str">
         <v>净买: 1.31亿</v>
       </c>
       <c r="E40">
@@ -12365,40 +12365,40 @@
       <c r="H40">
         <v>15.61</v>
       </c>
-      <c r="I40" s="500">
+      <c r="I40" s="498">
         <v>-6.17</v>
       </c>
-      <c r="J40" s="495">
+      <c r="J40" s="499">
         <v>-4.46</v>
       </c>
-      <c r="K40" s="496">
+      <c r="K40" s="502">
         <v>-11.42</v>
       </c>
-      <c r="L40" s="504">
+      <c r="L40" s="505">
         <v>-12.25</v>
       </c>
-      <c r="M40" s="505">
+      <c r="M40" s="503">
         <v>-16.96</v>
       </c>
-      <c r="N40" s="497">
+      <c r="N40" s="500">
         <v>-12.92</v>
       </c>
-      <c r="O40" s="501">
+      <c r="O40" s="496">
         <v>-6.46</v>
       </c>
-      <c r="P40" s="498">
+      <c r="P40" s="504">
         <v>0</v>
       </c>
-      <c r="Q40" s="502">
+      <c r="Q40" s="506">
         <v>-3.17</v>
       </c>
-      <c r="R40" s="506">
+      <c r="R40" s="497">
         <v>-6.54</v>
       </c>
-      <c r="S40" s="503">
+      <c r="S40" s="501">
         <v>-4.71</v>
       </c>
-      <c r="T40" s="499">
+      <c r="T40" s="507">
         <v>-30.75</v>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
       <c r="C41" t="str">
         <v>001337</v>
       </c>
-      <c r="D41" s="519" t="str">
+      <c r="D41" s="510" t="str">
         <v>净买: 4696.53万</v>
       </c>
       <c r="E41">
@@ -12427,40 +12427,40 @@
       <c r="H41">
         <v>5.3</v>
       </c>
-      <c r="I41" s="512">
+      <c r="I41" s="515">
         <v>4.47</v>
       </c>
-      <c r="J41" s="520">
+      <c r="J41" s="511">
         <v>14.89</v>
       </c>
-      <c r="K41" s="508">
+      <c r="K41" s="520">
         <v>3.41</v>
       </c>
-      <c r="L41" s="513">
+      <c r="L41" s="512">
         <v>-6.94</v>
       </c>
-      <c r="M41" s="509">
+      <c r="M41" s="513">
         <v>-12.41</v>
       </c>
-      <c r="N41" s="514">
+      <c r="N41" s="508">
         <v>-20.23</v>
       </c>
       <c r="O41" s="517">
         <v>-28.05</v>
       </c>
-      <c r="P41" s="515">
+      <c r="P41" s="516">
         <v>-27.52</v>
       </c>
-      <c r="Q41" s="516">
+      <c r="Q41" s="509">
         <v>-24</v>
       </c>
-      <c r="R41" s="510">
+      <c r="R41" s="518">
         <v>-27.11</v>
       </c>
-      <c r="S41" s="511">
+      <c r="S41" s="519">
         <v>-26.55</v>
       </c>
-      <c r="T41" s="518">
+      <c r="T41" s="514">
         <v>-25.28</v>
       </c>
     </row>
@@ -12489,40 +12489,40 @@
       <c r="H42">
         <v>10.01</v>
       </c>
-      <c r="I42" s="530">
+      <c r="I42" s="527">
         <v>-0.03</v>
       </c>
       <c r="J42" s="528">
         <v>-10.02</v>
       </c>
-      <c r="K42" s="522">
+      <c r="K42" s="529">
         <v>-19.02</v>
       </c>
-      <c r="L42" s="523">
+      <c r="L42" s="530">
         <v>-23.78</v>
       </c>
-      <c r="M42" s="524">
+      <c r="M42" s="531">
         <v>-30.59</v>
       </c>
-      <c r="N42" s="529">
+      <c r="N42" s="522">
         <v>-37.39</v>
       </c>
-      <c r="O42" s="531">
+      <c r="O42" s="532">
         <v>-36.93</v>
       </c>
-      <c r="P42" s="532">
+      <c r="P42" s="523">
         <v>-33.87</v>
       </c>
-      <c r="Q42" s="525">
+      <c r="Q42" s="524">
         <v>-36.57</v>
       </c>
-      <c r="R42" s="526">
+      <c r="R42" s="525">
         <v>-36.08</v>
       </c>
-      <c r="S42" s="533">
+      <c r="S42" s="526">
         <v>-36.64</v>
       </c>
-      <c r="T42" s="527">
+      <c r="T42" s="533">
         <v>-34.98</v>
       </c>
     </row>
@@ -12536,7 +12536,7 @@
       <c r="C43" t="str">
         <v>000995</v>
       </c>
-      <c r="D43" s="536" t="str">
+      <c r="D43" s="541" t="str">
         <v>净买: 1752.24万</v>
       </c>
       <c r="E43">
@@ -12551,40 +12551,40 @@
       <c r="H43">
         <v>10.01</v>
       </c>
-      <c r="I43" s="539">
+      <c r="I43" s="545">
         <v>0</v>
       </c>
-      <c r="J43" s="546">
+      <c r="J43" s="542">
         <v>9.98</v>
       </c>
-      <c r="K43" s="541">
+      <c r="K43" s="543">
         <v>20.97</v>
       </c>
       <c r="L43" s="534">
         <v>19.02</v>
       </c>
-      <c r="M43" s="542">
+      <c r="M43" s="538">
         <v>26.11</v>
       </c>
-      <c r="N43" s="537">
+      <c r="N43" s="544">
         <v>13.5</v>
       </c>
       <c r="O43" s="535">
         <v>18.02</v>
       </c>
-      <c r="P43" s="543">
+      <c r="P43" s="536">
         <v>6.91</v>
       </c>
-      <c r="Q43" s="538">
+      <c r="Q43" s="537">
         <v>4.02</v>
       </c>
-      <c r="R43" s="544">
+      <c r="R43" s="539">
         <v>0.38</v>
       </c>
-      <c r="S43" s="540">
+      <c r="S43" s="546">
         <v>-1.63</v>
       </c>
-      <c r="T43" s="545">
+      <c r="T43" s="540">
         <v>-13.68</v>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       <c r="C44" t="str">
         <v>000995</v>
       </c>
-      <c r="D44" s="551" t="str">
+      <c r="D44" s="559" t="str">
         <v>净卖: -1741.06万</v>
       </c>
       <c r="E44">
@@ -12613,7 +12613,7 @@
       <c r="H44">
         <v>-4.33</v>
       </c>
-      <c r="I44" s="552">
+      <c r="I44" s="553">
         <v>14.96</v>
       </c>
       <c r="J44" s="554">
@@ -12622,31 +12622,31 @@
       <c r="K44" s="555">
         <v>24.41</v>
       </c>
-      <c r="L44" s="556">
+      <c r="L44" s="551">
         <v>31.82</v>
       </c>
-      <c r="M44" s="549">
+      <c r="M44" s="556">
         <v>18.64</v>
       </c>
-      <c r="N44" s="553">
+      <c r="N44" s="557">
         <v>23.36</v>
       </c>
-      <c r="O44" s="559">
+      <c r="O44" s="558">
         <v>11.75</v>
       </c>
-      <c r="P44" s="557">
+      <c r="P44" s="547">
         <v>8.73</v>
       </c>
-      <c r="Q44" s="550">
+      <c r="Q44" s="548">
         <v>4.92</v>
       </c>
-      <c r="R44" s="547">
+      <c r="R44" s="552">
         <v>2.82</v>
       </c>
-      <c r="S44" s="548">
+      <c r="S44" s="549">
         <v>3.87</v>
       </c>
-      <c r="T44" s="558">
+      <c r="T44" s="550">
         <v>-9.78</v>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       <c r="C45" t="str">
         <v>301292</v>
       </c>
-      <c r="D45" s="564" t="str">
+      <c r="D45" s="565" t="str">
         <v>净买: 2923.62万</v>
       </c>
       <c r="E45">
@@ -12675,40 +12675,40 @@
       <c r="H45">
         <v>-0.29</v>
       </c>
-      <c r="I45" s="569">
+      <c r="I45" s="560">
         <v>20.35</v>
       </c>
-      <c r="J45" s="572">
+      <c r="J45" s="569">
         <v>23.96</v>
       </c>
-      <c r="K45" s="565">
+      <c r="K45" s="561">
         <v>16.61</v>
       </c>
-      <c r="L45" s="560">
+      <c r="L45" s="568">
         <v>13.75</v>
       </c>
-      <c r="M45" s="566">
+      <c r="M45" s="562">
         <v>10.84</v>
       </c>
-      <c r="N45" s="561">
+      <c r="N45" s="570">
         <v>7.09</v>
       </c>
-      <c r="O45" s="562">
+      <c r="O45" s="571">
         <v>7.44</v>
       </c>
-      <c r="P45" s="567">
+      <c r="P45" s="566">
         <v>2.1</v>
       </c>
-      <c r="Q45" s="570">
+      <c r="Q45" s="567">
         <v>1.76</v>
       </c>
-      <c r="R45" s="568">
+      <c r="R45" s="563">
         <v>6.85</v>
       </c>
-      <c r="S45" s="571">
+      <c r="S45" s="564">
         <v>11.3</v>
       </c>
-      <c r="T45" s="563">
+      <c r="T45" s="572">
         <v>15.74</v>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       <c r="C46" t="str">
         <v>301396</v>
       </c>
-      <c r="D46" s="575" t="str">
+      <c r="D46" s="573" t="str">
         <v>净买: 9469.00万</v>
       </c>
       <c r="E46">
@@ -12737,10 +12737,10 @@
       <c r="H46">
         <v>2.83</v>
       </c>
-      <c r="I46" s="576">
+      <c r="I46" s="574">
         <v>16.7</v>
       </c>
-      <c r="J46" s="573">
+      <c r="J46" s="575">
         <v>13.98</v>
       </c>
       <c r="K46" t="str"/>
@@ -12752,7 +12752,7 @@
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="574">
+      <c r="T46" s="576">
         <v>13.98</v>
       </c>
     </row>
@@ -12818,37 +12818,37 @@
       <c r="I48" s="583">
         <v>71.11</v>
       </c>
-      <c r="J48" s="584">
+      <c r="J48" s="577">
         <v>64.44</v>
       </c>
-      <c r="K48" s="585">
+      <c r="K48" s="580">
         <v>59.09</v>
       </c>
-      <c r="L48" s="578">
+      <c r="L48" s="581">
         <v>56.82</v>
       </c>
-      <c r="M48" s="588">
+      <c r="M48" s="584">
         <v>61.36</v>
       </c>
-      <c r="N48" s="579">
+      <c r="N48" s="586">
         <v>61.36</v>
       </c>
-      <c r="O48" s="587">
+      <c r="O48" s="578">
         <v>56.82</v>
       </c>
-      <c r="P48" s="580">
+      <c r="P48" s="582">
         <v>52.27</v>
       </c>
-      <c r="Q48" s="581">
+      <c r="Q48" s="587">
         <v>59.09</v>
       </c>
-      <c r="R48" s="586">
+      <c r="R48" s="579">
         <v>52.27</v>
       </c>
-      <c r="S48" s="582">
+      <c r="S48" s="585">
         <v>43.18</v>
       </c>
-      <c r="T48" s="577">
+      <c r="T48" s="588">
         <v>31.11</v>
       </c>
     </row>
@@ -12863,40 +12863,40 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="598">
+      <c r="I49" s="589">
         <v>5.74</v>
       </c>
-      <c r="J49" s="589">
+      <c r="J49" s="590">
         <v>5.25</v>
       </c>
-      <c r="K49" s="593">
+      <c r="K49" s="594">
         <v>4.02</v>
       </c>
-      <c r="L49" s="594">
+      <c r="L49" s="599">
         <v>3.64</v>
       </c>
-      <c r="M49" s="590">
+      <c r="M49" s="600">
         <v>4.36</v>
       </c>
-      <c r="N49" s="596">
+      <c r="N49" s="595">
         <v>5.31</v>
       </c>
-      <c r="O49" s="597">
+      <c r="O49" s="591">
         <v>3.86</v>
       </c>
-      <c r="P49" s="595">
+      <c r="P49" s="592">
         <v>2.82</v>
       </c>
-      <c r="Q49" s="591">
+      <c r="Q49" s="596">
         <v>3.34</v>
       </c>
-      <c r="R49" s="599">
+      <c r="R49" s="597">
         <v>3.21</v>
       </c>
-      <c r="S49" s="592">
+      <c r="S49" s="598">
         <v>3.56</v>
       </c>
-      <c r="T49" s="600">
+      <c r="T49" s="593">
         <v>-2.75</v>
       </c>
     </row>

--- a/youzi/徐晓/index.xlsx
+++ b/youzi/徐晓/index.xlsx
@@ -45,6 +45,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -111,6 +117,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
@@ -129,31 +183,1639 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9FD8AC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF60BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,54 +1827,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -255,31 +1869,697 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF99D5A6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -291,79 +2571,157 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -375,49 +2733,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -435,91 +2847,523 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD8AC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF249A3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196E2F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,31 +3375,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFEB8D96"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -567,127 +3387,217 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFAA1E2B"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -699,229 +3609,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
+        <fgColor rgb="FF22903C"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -939,2701 +3633,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -9994,7 +9994,7 @@
       <c r="C2" t="str">
         <v>600120</v>
       </c>
-      <c r="D2" s="2" t="str">
+      <c r="D2" s="3" t="str">
         <v>净卖: -1.33亿</v>
       </c>
       <c r="E2">
@@ -10009,40 +10009,40 @@
       <c r="H2">
         <v>9.97</v>
       </c>
-      <c r="I2" s="3">
+      <c r="I2" s="9">
         <v>-12.49</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="11">
         <v>-21.25</v>
       </c>
-      <c r="K2" s="9">
+      <c r="K2" s="12">
         <v>-22.96</v>
       </c>
-      <c r="L2" s="10">
+      <c r="L2" s="4">
         <v>-26.08</v>
       </c>
-      <c r="M2" s="12">
+      <c r="M2" s="7">
         <v>-20.85</v>
       </c>
-      <c r="N2" s="5">
+      <c r="N2" s="13">
         <v>-20.85</v>
       </c>
-      <c r="O2" s="13">
+      <c r="O2" s="1">
         <v>-22.16</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="2">
         <v>-26.28</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="10">
         <v>-25.48</v>
       </c>
-      <c r="R2" s="11">
+      <c r="R2" s="8">
         <v>-24.07</v>
       </c>
-      <c r="S2" s="1">
+      <c r="S2" s="5">
         <v>-25.78</v>
       </c>
-      <c r="T2" s="8">
+      <c r="T2" s="6">
         <v>-42.3</v>
       </c>
     </row>
@@ -10071,13 +10071,13 @@
       <c r="H3">
         <v>-3</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="14">
         <v>-7.22</v>
       </c>
-      <c r="J3" s="17">
+      <c r="J3" s="22">
         <v>-10.22</v>
       </c>
-      <c r="K3" s="22">
+      <c r="K3" s="17">
         <v>-4.57</v>
       </c>
       <c r="L3" s="18">
@@ -10086,25 +10086,25 @@
       <c r="M3" s="19">
         <v>-0.02</v>
       </c>
-      <c r="N3" s="20">
+      <c r="N3" s="26">
         <v>4.27</v>
       </c>
-      <c r="O3" s="21">
+      <c r="O3" s="20">
         <v>5.17</v>
       </c>
-      <c r="P3" s="14">
+      <c r="P3" s="23">
         <v>3.7</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="24">
         <v>13.88</v>
       </c>
-      <c r="R3" s="15">
+      <c r="R3" s="21">
         <v>25.27</v>
       </c>
-      <c r="S3" s="24">
+      <c r="S3" s="25">
         <v>24.52</v>
       </c>
-      <c r="T3" s="25">
+      <c r="T3" s="15">
         <v>-19.33</v>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
       <c r="C4" t="str">
         <v>002896</v>
       </c>
-      <c r="D4" s="32" t="str">
+      <c r="D4" s="31" t="str">
         <v>净买: 5162.35万</v>
       </c>
       <c r="E4">
@@ -10136,37 +10136,37 @@
       <c r="I4" s="38">
         <v>6.79</v>
       </c>
-      <c r="J4" s="29">
+      <c r="J4" s="32">
         <v>17.47</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="35">
         <v>5.82</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="36">
         <v>15.69</v>
       </c>
-      <c r="M4" s="27">
+      <c r="M4" s="29">
         <v>27.26</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="39">
         <v>39.98</v>
       </c>
       <c r="O4" s="33">
         <v>25.98</v>
       </c>
-      <c r="P4" s="34">
+      <c r="P4" s="27">
         <v>13.39</v>
       </c>
-      <c r="Q4" s="35">
+      <c r="Q4" s="28">
         <v>16.45</v>
       </c>
-      <c r="R4" s="36">
+      <c r="R4" s="34">
         <v>19.91</v>
       </c>
-      <c r="S4" s="31">
+      <c r="S4" s="37">
         <v>19.53</v>
       </c>
-      <c r="T4" s="37">
+      <c r="T4" s="30">
         <v>-10.2</v>
       </c>
     </row>
@@ -10180,7 +10180,7 @@
       <c r="C5" t="str">
         <v>600602</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="50" t="str">
         <v>净买: 1.03亿</v>
       </c>
       <c r="E5">
@@ -10195,40 +10195,40 @@
       <c r="H5">
         <v>-2.66</v>
       </c>
-      <c r="I5" s="44">
+      <c r="I5" s="51">
         <v>10.77</v>
       </c>
-      <c r="J5" s="50">
+      <c r="J5" s="43">
         <v>5.81</v>
       </c>
-      <c r="K5" s="45">
+      <c r="K5" s="47">
         <v>-3.88</v>
       </c>
-      <c r="L5" s="46">
+      <c r="L5" s="52">
         <v>-13.5</v>
       </c>
-      <c r="M5" s="51">
+      <c r="M5" s="44">
         <v>-15.88</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="48">
         <v>-14.23</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="42">
         <v>-8.5</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="45">
         <v>-5.04</v>
       </c>
-      <c r="Q5" s="48">
+      <c r="Q5" s="40">
         <v>4.46</v>
       </c>
-      <c r="R5" s="49">
+      <c r="R5" s="41">
         <v>6.31</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="49">
         <v>10.62</v>
       </c>
-      <c r="T5" s="42">
+      <c r="T5" s="46">
         <v>-7.38</v>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       <c r="C6" t="str">
         <v>003021</v>
       </c>
-      <c r="D6" s="56" t="str">
+      <c r="D6" s="58" t="str">
         <v>净买: 5581.43万</v>
       </c>
       <c r="E6">
@@ -10257,40 +10257,40 @@
       <c r="H6">
         <v>-1.3</v>
       </c>
-      <c r="I6" s="60">
+      <c r="I6" s="59">
         <v>11.45</v>
       </c>
       <c r="J6" s="57">
         <v>10.79</v>
       </c>
-      <c r="K6" s="53">
+      <c r="K6" s="60">
         <v>-0.29</v>
       </c>
-      <c r="L6" s="58">
+      <c r="L6" s="53">
         <v>-5.12</v>
       </c>
-      <c r="M6" s="59">
+      <c r="M6" s="61">
         <v>4.3</v>
       </c>
-      <c r="N6" s="61">
+      <c r="N6" s="54">
         <v>14.73</v>
       </c>
-      <c r="O6" s="54">
+      <c r="O6" s="62">
         <v>13.05</v>
       </c>
       <c r="P6" s="63">
         <v>12.06</v>
       </c>
-      <c r="Q6" s="62">
+      <c r="Q6" s="64">
         <v>13.73</v>
       </c>
-      <c r="R6" s="55">
+      <c r="R6" s="65">
         <v>10.86</v>
       </c>
-      <c r="S6" s="64">
+      <c r="S6" s="55">
         <v>10.2</v>
       </c>
-      <c r="T6" s="65">
+      <c r="T6" s="56">
         <v>-28.23</v>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
       <c r="C7" t="str">
         <v>002522</v>
       </c>
-      <c r="D7" s="66" t="str">
+      <c r="D7" s="69" t="str">
         <v>净卖: -2406.69万</v>
       </c>
       <c r="E7">
@@ -10319,40 +10319,40 @@
       <c r="H7">
         <v>-5.38</v>
       </c>
-      <c r="I7" s="69">
+      <c r="I7" s="70">
         <v>-4.11</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="71">
         <v>-13.74</v>
       </c>
-      <c r="K7" s="70">
+      <c r="K7" s="72">
         <v>-21.64</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="73">
         <v>-19.75</v>
       </c>
-      <c r="M7" s="67">
+      <c r="M7" s="78">
         <v>-18.96</v>
       </c>
-      <c r="N7" s="77">
+      <c r="N7" s="74">
         <v>-16.9</v>
       </c>
-      <c r="O7" s="78">
+      <c r="O7" s="75">
         <v>-18.64</v>
       </c>
-      <c r="P7" s="73">
+      <c r="P7" s="76">
         <v>-16.27</v>
       </c>
-      <c r="Q7" s="74">
+      <c r="Q7" s="66">
         <v>-17.06</v>
       </c>
-      <c r="R7" s="75">
+      <c r="R7" s="77">
         <v>-16.75</v>
       </c>
-      <c r="S7" s="68">
+      <c r="S7" s="67">
         <v>-19.59</v>
       </c>
-      <c r="T7" s="71">
+      <c r="T7" s="68">
         <v>-2.21</v>
       </c>
     </row>
@@ -10366,7 +10366,7 @@
       <c r="C8" t="str">
         <v>003021</v>
       </c>
-      <c r="D8" s="88" t="str">
+      <c r="D8" s="83" t="str">
         <v>净卖: -7322.64万</v>
       </c>
       <c r="E8">
@@ -10381,40 +10381,40 @@
       <c r="H8">
         <v>-1.2</v>
       </c>
-      <c r="I8" s="85">
+      <c r="I8" s="84">
         <v>11.33</v>
       </c>
       <c r="J8" s="89">
         <v>9.7</v>
       </c>
-      <c r="K8" s="82">
+      <c r="K8" s="81">
         <v>8.74</v>
       </c>
-      <c r="L8" s="83">
+      <c r="L8" s="82">
         <v>10.37</v>
       </c>
       <c r="M8" s="90">
         <v>7.58</v>
       </c>
-      <c r="N8" s="91">
+      <c r="N8" s="85">
         <v>6.94</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="87">
         <v>-0.96</v>
       </c>
-      <c r="P8" s="84">
+      <c r="P8" s="88">
         <v>1.12</v>
       </c>
-      <c r="Q8" s="86">
+      <c r="Q8" s="91">
         <v>2.48</v>
       </c>
-      <c r="R8" s="80">
+      <c r="R8" s="79">
         <v>-0.05</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="86">
         <v>-2.14</v>
       </c>
-      <c r="T8" s="87">
+      <c r="T8" s="80">
         <v>-30.35</v>
       </c>
     </row>
@@ -10443,40 +10443,40 @@
       <c r="H9">
         <v>-3.17</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="101">
         <v>-7.06</v>
       </c>
-      <c r="J9" s="104">
+      <c r="J9" s="96">
         <v>-13.04</v>
       </c>
-      <c r="K9" s="92">
+      <c r="K9" s="97">
         <v>-11.69</v>
       </c>
-      <c r="L9" s="100">
+      <c r="L9" s="98">
         <v>-10.05</v>
       </c>
-      <c r="M9" s="98">
+      <c r="M9" s="103">
         <v>-11.15</v>
       </c>
-      <c r="N9" s="93">
+      <c r="N9" s="104">
         <v>-12.48</v>
       </c>
-      <c r="O9" s="96">
+      <c r="O9" s="92">
         <v>-11.61</v>
       </c>
-      <c r="P9" s="94">
+      <c r="P9" s="93">
         <v>-10.56</v>
       </c>
-      <c r="Q9" s="97">
+      <c r="Q9" s="102">
         <v>-12.51</v>
       </c>
       <c r="R9" s="99">
         <v>-9.97</v>
       </c>
-      <c r="S9" s="101">
+      <c r="S9" s="94">
         <v>-18.06</v>
       </c>
-      <c r="T9" s="102">
+      <c r="T9" s="100">
         <v>-3.68</v>
       </c>
     </row>
@@ -10490,7 +10490,7 @@
       <c r="C10" t="str">
         <v>000799</v>
       </c>
-      <c r="D10" s="113" t="str">
+      <c r="D10" s="114" t="str">
         <v>净卖: -41.89万</v>
       </c>
       <c r="E10">
@@ -10505,40 +10505,40 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="117">
+      <c r="I10" s="108">
         <v>10.01</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="109">
         <v>9.1</v>
       </c>
-      <c r="K10" s="114">
+      <c r="K10" s="106">
         <v>8.38</v>
       </c>
-      <c r="L10" s="115">
+      <c r="L10" s="112">
         <v>7.23</v>
       </c>
-      <c r="M10" s="111">
+      <c r="M10" s="115">
         <v>5.75</v>
       </c>
-      <c r="N10" s="108">
+      <c r="N10" s="116">
         <v>5</v>
       </c>
-      <c r="O10" s="112">
+      <c r="O10" s="110">
         <v>4.96</v>
       </c>
-      <c r="P10" s="109">
+      <c r="P10" s="107">
         <v>6.34</v>
       </c>
-      <c r="Q10" s="105">
+      <c r="Q10" s="111">
         <v>5.62</v>
       </c>
-      <c r="R10" s="106">
+      <c r="R10" s="117">
         <v>4.79</v>
       </c>
-      <c r="S10" s="107">
+      <c r="S10" s="105">
         <v>1.89</v>
       </c>
-      <c r="T10" s="116">
+      <c r="T10" s="113">
         <v>-8.59</v>
       </c>
     </row>
@@ -10552,7 +10552,7 @@
       <c r="C11" t="str">
         <v>688108</v>
       </c>
-      <c r="D11" s="124" t="str">
+      <c r="D11" s="125" t="str">
         <v>净买: 3339.73万</v>
       </c>
       <c r="E11">
@@ -10567,40 +10567,40 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="129">
         <v>14.27</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="130">
         <v>11.35</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="127">
         <v>2.7</v>
       </c>
-      <c r="L11" s="126">
+      <c r="L11" s="121">
         <v>-5.73</v>
       </c>
-      <c r="M11" s="119">
+      <c r="M11" s="118">
         <v>-9.92</v>
       </c>
-      <c r="N11" s="120">
+      <c r="N11" s="122">
         <v>-8.04</v>
       </c>
-      <c r="O11" s="121">
+      <c r="O11" s="126">
         <v>-12.4</v>
       </c>
-      <c r="P11" s="127">
+      <c r="P11" s="128">
         <v>-16.72</v>
       </c>
       <c r="Q11" s="123">
         <v>-12.2</v>
       </c>
-      <c r="R11" s="122">
+      <c r="R11" s="119">
         <v>-8.57</v>
       </c>
-      <c r="S11" s="128">
+      <c r="S11" s="124">
         <v>-6.23</v>
       </c>
-      <c r="T11" s="129">
+      <c r="T11" s="120">
         <v>-40.94</v>
       </c>
     </row>
@@ -10614,7 +10614,7 @@
       <c r="C12" t="str">
         <v>300222</v>
       </c>
-      <c r="D12" s="140" t="str">
+      <c r="D12" s="142" t="str">
         <v>净卖: -6818.64万</v>
       </c>
       <c r="E12">
@@ -10629,40 +10629,40 @@
       <c r="H12">
         <v>2.15</v>
       </c>
-      <c r="I12" s="141">
+      <c r="I12" s="143">
         <v>16.68</v>
       </c>
-      <c r="J12" s="136">
+      <c r="J12" s="139">
         <v>11.46</v>
       </c>
-      <c r="K12" s="137">
+      <c r="K12" s="140">
         <v>5.46</v>
       </c>
-      <c r="L12" s="134">
+      <c r="L12" s="136">
         <v>3.27</v>
       </c>
-      <c r="M12" s="142">
+      <c r="M12" s="131">
         <v>4.13</v>
       </c>
-      <c r="N12" s="131">
+      <c r="N12" s="132">
         <v>-1.95</v>
       </c>
-      <c r="O12" s="135">
+      <c r="O12" s="141">
         <v>-3.66</v>
       </c>
-      <c r="P12" s="132">
+      <c r="P12" s="137">
         <v>-0.94</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="138">
         <v>1.56</v>
       </c>
-      <c r="R12" s="143">
+      <c r="R12" s="133">
         <v>-1.56</v>
       </c>
-      <c r="S12" s="138">
+      <c r="S12" s="134">
         <v>-0.78</v>
       </c>
-      <c r="T12" s="139">
+      <c r="T12" s="135">
         <v>-12.63</v>
       </c>
     </row>
@@ -10676,7 +10676,7 @@
       <c r="C13" t="str">
         <v>002837</v>
       </c>
-      <c r="D13" s="155" t="str">
+      <c r="D13" s="147" t="str">
         <v>净买: 1.07亿</v>
       </c>
       <c r="E13">
@@ -10691,37 +10691,37 @@
       <c r="H13">
         <v>-3.13</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="156">
         <v>13.56</v>
       </c>
-      <c r="J13" s="150">
+      <c r="J13" s="153">
         <v>14.94</v>
       </c>
-      <c r="K13" s="156">
+      <c r="K13" s="148">
         <v>15.17</v>
       </c>
-      <c r="L13" s="144">
+      <c r="L13" s="149">
         <v>3.66</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="150">
         <v>5.96</v>
       </c>
-      <c r="N13" s="145">
+      <c r="N13" s="154">
         <v>-2.76</v>
       </c>
-      <c r="O13" s="151">
+      <c r="O13" s="144">
         <v>2.11</v>
       </c>
-      <c r="P13" s="153">
+      <c r="P13" s="155">
         <v>-0.68</v>
       </c>
-      <c r="Q13" s="154">
+      <c r="Q13" s="145">
         <v>-3.52</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="151">
         <v>3.92</v>
       </c>
-      <c r="S13" s="149">
+      <c r="S13" s="152">
         <v>8.92</v>
       </c>
       <c r="T13" s="146">
@@ -10738,7 +10738,7 @@
       <c r="C14" t="str">
         <v>600521</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="165" t="str">
         <v>净买: 2288.75万</v>
       </c>
       <c r="E14">
@@ -10753,40 +10753,40 @@
       <c r="H14">
         <v>-0.63</v>
       </c>
-      <c r="I14" s="159">
+      <c r="I14" s="167">
         <v>-9.43</v>
       </c>
-      <c r="J14" s="160">
+      <c r="J14" s="168">
         <v>-8.27</v>
       </c>
-      <c r="K14" s="167">
+      <c r="K14" s="158">
         <v>-12.18</v>
       </c>
-      <c r="L14" s="161">
+      <c r="L14" s="169">
         <v>-7.04</v>
       </c>
-      <c r="M14" s="168">
+      <c r="M14" s="166">
         <v>-9.99</v>
       </c>
-      <c r="N14" s="169">
+      <c r="N14" s="159">
         <v>-12.07</v>
       </c>
-      <c r="O14" s="164">
+      <c r="O14" s="162">
         <v>-12</v>
       </c>
-      <c r="P14" s="162">
+      <c r="P14" s="157">
         <v>-13.97</v>
       </c>
-      <c r="Q14" s="157">
+      <c r="Q14" s="160">
         <v>-14.46</v>
       </c>
-      <c r="R14" s="165">
+      <c r="R14" s="163">
         <v>-16.47</v>
       </c>
-      <c r="S14" s="158">
+      <c r="S14" s="164">
         <v>-19.15</v>
       </c>
-      <c r="T14" s="166">
+      <c r="T14" s="161">
         <v>-37.11</v>
       </c>
     </row>
@@ -10800,7 +10800,7 @@
       <c r="C15" t="str">
         <v>600629</v>
       </c>
-      <c r="D15" s="170" t="str">
+      <c r="D15" s="182" t="str">
         <v>净卖: -1267.40万</v>
       </c>
       <c r="E15">
@@ -10815,40 +10815,40 @@
       <c r="H15">
         <v>7.68</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="176">
         <v>2.16</v>
       </c>
       <c r="J15" s="177">
         <v>12.36</v>
       </c>
-      <c r="K15" s="180">
+      <c r="K15" s="179">
         <v>23.61</v>
       </c>
-      <c r="L15" s="181">
+      <c r="L15" s="173">
         <v>18.97</v>
       </c>
-      <c r="M15" s="174">
+      <c r="M15" s="180">
         <v>17.66</v>
       </c>
-      <c r="N15" s="175">
+      <c r="N15" s="170">
         <v>25.9</v>
       </c>
-      <c r="O15" s="182">
+      <c r="O15" s="171">
         <v>25.51</v>
       </c>
-      <c r="P15" s="178">
+      <c r="P15" s="181">
         <v>28.19</v>
       </c>
-      <c r="Q15" s="171">
+      <c r="Q15" s="174">
         <v>28.12</v>
       </c>
       <c r="R15" s="172">
         <v>40.94</v>
       </c>
-      <c r="S15" s="173">
+      <c r="S15" s="175">
         <v>55.07</v>
       </c>
-      <c r="T15" s="176">
+      <c r="T15" s="178">
         <v>39.5</v>
       </c>
     </row>
@@ -10862,7 +10862,7 @@
       <c r="C16" t="str">
         <v>600403</v>
       </c>
-      <c r="D16" s="188" t="str">
+      <c r="D16" s="194" t="str">
         <v>净买: 1894.16万</v>
       </c>
       <c r="E16">
@@ -10877,40 +10877,40 @@
       <c r="H16">
         <v>-2.81</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="195">
         <v>9.03</v>
       </c>
-      <c r="J16" s="184">
+      <c r="J16" s="185">
         <v>-1.93</v>
       </c>
-      <c r="K16" s="189">
+      <c r="K16" s="191">
         <v>-0.24</v>
       </c>
-      <c r="L16" s="185">
+      <c r="L16" s="183">
         <v>-0.72</v>
       </c>
-      <c r="M16" s="190">
+      <c r="M16" s="184">
         <v>9.27</v>
       </c>
-      <c r="N16" s="191">
+      <c r="N16" s="192">
         <v>6.74</v>
       </c>
-      <c r="O16" s="194">
+      <c r="O16" s="193">
         <v>10.95</v>
       </c>
-      <c r="P16" s="195">
+      <c r="P16" s="187">
         <v>22.02</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="188">
         <v>34.18</v>
       </c>
-      <c r="R16" s="183">
+      <c r="R16" s="186">
         <v>23.47</v>
       </c>
-      <c r="S16" s="187">
+      <c r="S16" s="189">
         <v>11.07</v>
       </c>
-      <c r="T16" s="192">
+      <c r="T16" s="190">
         <v>-31.77</v>
       </c>
     </row>
@@ -10924,7 +10924,7 @@
       <c r="C17" t="str">
         <v>600403</v>
       </c>
-      <c r="D17" s="207" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -1651.88万</v>
       </c>
       <c r="E17">
@@ -10939,40 +10939,40 @@
       <c r="H17">
         <v>-7.84</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="201">
         <v>-2.4</v>
       </c>
-      <c r="J17" s="208">
+      <c r="J17" s="202">
         <v>-0.72</v>
       </c>
       <c r="K17" s="199">
         <v>-1.2</v>
       </c>
-      <c r="L17" s="204">
+      <c r="L17" s="196">
         <v>8.74</v>
       </c>
-      <c r="M17" s="197">
+      <c r="M17" s="205">
         <v>6.23</v>
       </c>
-      <c r="N17" s="198">
+      <c r="N17" s="206">
         <v>10.42</v>
       </c>
       <c r="O17" s="200">
         <v>21.44</v>
       </c>
-      <c r="P17" s="201">
+      <c r="P17" s="197">
         <v>33.53</v>
       </c>
-      <c r="Q17" s="202">
+      <c r="Q17" s="203">
         <v>22.87</v>
       </c>
-      <c r="R17" s="203">
+      <c r="R17" s="204">
         <v>10.54</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="207">
         <v>-0.48</v>
       </c>
-      <c r="T17" s="206">
+      <c r="T17" s="198">
         <v>-32.1</v>
       </c>
     </row>
@@ -11001,40 +11001,40 @@
       <c r="H18">
         <v>-0.22</v>
       </c>
-      <c r="I18" s="210">
+      <c r="I18" s="219">
         <v>10.23</v>
       </c>
-      <c r="J18" s="211">
+      <c r="J18" s="210">
         <v>11.19</v>
       </c>
-      <c r="K18" s="216">
+      <c r="K18" s="218">
         <v>9.73</v>
       </c>
-      <c r="L18" s="217">
+      <c r="L18" s="211">
         <v>12.16</v>
       </c>
-      <c r="M18" s="218">
+      <c r="M18" s="212">
         <v>9.55</v>
       </c>
-      <c r="N18" s="212">
+      <c r="N18" s="213">
         <v>8.7</v>
       </c>
-      <c r="O18" s="213">
+      <c r="O18" s="220">
         <v>6.71</v>
       </c>
-      <c r="P18" s="219">
+      <c r="P18" s="214">
         <v>4.16</v>
       </c>
-      <c r="Q18" s="214">
+      <c r="Q18" s="221">
         <v>2.68</v>
       </c>
-      <c r="R18" s="220">
+      <c r="R18" s="215">
         <v>-2.26</v>
       </c>
-      <c r="S18" s="215">
+      <c r="S18" s="216">
         <v>-4.4</v>
       </c>
-      <c r="T18" s="221">
+      <c r="T18" s="217">
         <v>-27.91</v>
       </c>
     </row>
@@ -11048,7 +11048,7 @@
       <c r="C19" t="str">
         <v>000069</v>
       </c>
-      <c r="D19" s="223" t="str">
+      <c r="D19" s="228" t="str">
         <v>净卖: -7553.88万</v>
       </c>
       <c r="E19">
@@ -11063,40 +11063,40 @@
       <c r="H19">
         <v>1.88</v>
       </c>
-      <c r="I19" s="233">
+      <c r="I19" s="229">
         <v>8.12</v>
       </c>
-      <c r="J19" s="227">
+      <c r="J19" s="225">
         <v>3.69</v>
       </c>
-      <c r="K19" s="224">
+      <c r="K19" s="226">
         <v>4.06</v>
       </c>
-      <c r="L19" s="228">
+      <c r="L19" s="233">
         <v>2.95</v>
       </c>
-      <c r="M19" s="234">
+      <c r="M19" s="230">
         <v>4.8</v>
       </c>
-      <c r="N19" s="225">
+      <c r="N19" s="231">
         <v>0.37</v>
       </c>
-      <c r="O19" s="229">
+      <c r="O19" s="222">
         <v>-2.95</v>
       </c>
-      <c r="P19" s="226">
+      <c r="P19" s="234">
         <v>0</v>
       </c>
-      <c r="Q19" s="231">
+      <c r="Q19" s="223">
         <v>-1.11</v>
       </c>
-      <c r="R19" s="230">
+      <c r="R19" s="232">
         <v>-1.85</v>
       </c>
-      <c r="S19" s="232">
+      <c r="S19" s="227">
         <v>0</v>
       </c>
-      <c r="T19" s="222">
+      <c r="T19" s="224">
         <v>-17.71</v>
       </c>
     </row>
@@ -11110,7 +11110,7 @@
       <c r="C20" t="str">
         <v>002709</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="242" t="str">
         <v>净买: 1.65亿</v>
       </c>
       <c r="E20">
@@ -11125,40 +11125,40 @@
       <c r="H20">
         <v>1.37</v>
       </c>
-      <c r="I20" s="238">
+      <c r="I20" s="236">
         <v>8.51</v>
       </c>
-      <c r="J20" s="247">
+      <c r="J20" s="243">
         <v>7.15</v>
       </c>
-      <c r="K20" s="235">
+      <c r="K20" s="244">
         <v>9.4</v>
       </c>
-      <c r="L20" s="242">
+      <c r="L20" s="238">
         <v>-1.54</v>
       </c>
-      <c r="M20" s="236">
+      <c r="M20" s="245">
         <v>3.1</v>
       </c>
-      <c r="N20" s="237">
+      <c r="N20" s="239">
         <v>1.91</v>
       </c>
-      <c r="O20" s="243">
+      <c r="O20" s="237">
         <v>-8.25</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="235">
         <v>-11.49</v>
       </c>
-      <c r="Q20" s="239">
+      <c r="Q20" s="246">
         <v>-7.63</v>
       </c>
-      <c r="R20" s="246">
+      <c r="R20" s="240">
         <v>-9.03</v>
       </c>
-      <c r="S20" s="240">
+      <c r="S20" s="241">
         <v>-6.57</v>
       </c>
-      <c r="T20" s="241">
+      <c r="T20" s="247">
         <v>12.16</v>
       </c>
     </row>
@@ -11190,37 +11190,37 @@
       <c r="I21" s="253">
         <v>8.46</v>
       </c>
-      <c r="J21" s="249">
+      <c r="J21" s="256">
         <v>-7.74</v>
       </c>
-      <c r="K21" s="251">
+      <c r="K21" s="248">
         <v>-6.92</v>
       </c>
-      <c r="L21" s="250">
+      <c r="L21" s="254">
         <v>-6.67</v>
       </c>
-      <c r="M21" s="256">
+      <c r="M21" s="257">
         <v>-20</v>
       </c>
-      <c r="N21" s="257">
+      <c r="N21" s="249">
         <v>-17.49</v>
       </c>
-      <c r="O21" s="252">
+      <c r="O21" s="250">
         <v>-15.9</v>
       </c>
-      <c r="P21" s="258">
+      <c r="P21" s="251">
         <v>-19.69</v>
       </c>
       <c r="Q21" s="259">
         <v>-16.56</v>
       </c>
-      <c r="R21" s="260">
+      <c r="R21" s="252">
         <v>-17.03</v>
       </c>
-      <c r="S21" s="248">
+      <c r="S21" s="258">
         <v>-17.59</v>
       </c>
-      <c r="T21" s="254">
+      <c r="T21" s="260">
         <v>-3.38</v>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
       <c r="C22" t="str">
         <v>600343</v>
       </c>
-      <c r="D22" s="264" t="str">
+      <c r="D22" s="263" t="str">
         <v>净卖: -1.50亿</v>
       </c>
       <c r="E22">
@@ -11249,37 +11249,37 @@
       <c r="H22">
         <v>-2.42</v>
       </c>
-      <c r="I22" s="263">
+      <c r="I22" s="264">
         <v>5.68</v>
       </c>
-      <c r="J22" s="272">
+      <c r="J22" s="269">
         <v>9.44</v>
       </c>
-      <c r="K22" s="268">
+      <c r="K22" s="267">
         <v>20.4</v>
       </c>
-      <c r="L22" s="273">
+      <c r="L22" s="270">
         <v>32.45</v>
       </c>
-      <c r="M22" s="265">
+      <c r="M22" s="268">
         <v>25.78</v>
       </c>
-      <c r="N22" s="269">
+      <c r="N22" s="272">
         <v>29.91</v>
       </c>
-      <c r="O22" s="261">
+      <c r="O22" s="273">
         <v>19.51</v>
       </c>
-      <c r="P22" s="266">
+      <c r="P22" s="265">
         <v>20.5</v>
       </c>
-      <c r="Q22" s="262">
+      <c r="Q22" s="261">
         <v>27.5</v>
       </c>
-      <c r="R22" s="267">
+      <c r="R22" s="266">
         <v>22.58</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="262">
         <v>25.45</v>
       </c>
       <c r="T22" s="271">
@@ -11296,7 +11296,7 @@
       <c r="C23" t="str">
         <v>600151</v>
       </c>
-      <c r="D23" s="276" t="str">
+      <c r="D23" s="283" t="str">
         <v>净买: 9889.49万</v>
       </c>
       <c r="E23">
@@ -11311,40 +11311,40 @@
       <c r="H23">
         <v>3.9</v>
       </c>
-      <c r="I23" s="281">
+      <c r="I23" s="274">
         <v>5.88</v>
       </c>
-      <c r="J23" s="278">
+      <c r="J23" s="284">
         <v>7.37</v>
       </c>
-      <c r="K23" s="279">
+      <c r="K23" s="277">
         <v>13.25</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="278">
         <v>18.63</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="282">
         <v>18</v>
       </c>
-      <c r="N23" s="286">
+      <c r="N23" s="285">
         <v>11.5</v>
       </c>
-      <c r="O23" s="280">
+      <c r="O23" s="275">
         <v>0.37</v>
       </c>
-      <c r="P23" s="274">
+      <c r="P23" s="279">
         <v>-0.62</v>
       </c>
-      <c r="Q23" s="284">
+      <c r="Q23" s="280">
         <v>2.81</v>
       </c>
-      <c r="R23" s="275">
+      <c r="R23" s="276">
         <v>3.94</v>
       </c>
-      <c r="S23" s="285">
+      <c r="S23" s="281">
         <v>14.31</v>
       </c>
-      <c r="T23" s="277">
+      <c r="T23" s="286">
         <v>-8.63</v>
       </c>
     </row>
@@ -11373,40 +11373,40 @@
       <c r="H24">
         <v>-5.05</v>
       </c>
-      <c r="I24" s="290">
+      <c r="I24" s="287">
         <v>6.05</v>
       </c>
-      <c r="J24" s="298">
+      <c r="J24" s="295">
         <v>-4.33</v>
       </c>
-      <c r="K24" s="295">
+      <c r="K24" s="296">
         <v>-4.4</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="298">
         <v>5.17</v>
       </c>
-      <c r="M24" s="299">
+      <c r="M24" s="288">
         <v>7.66</v>
       </c>
-      <c r="N24" s="293">
+      <c r="N24" s="297">
         <v>18.42</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="289">
         <v>30.25</v>
       </c>
-      <c r="P24" s="291">
+      <c r="P24" s="292">
         <v>43.26</v>
       </c>
-      <c r="Q24" s="292">
+      <c r="Q24" s="290">
         <v>50.8</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="293">
         <v>42.08</v>
       </c>
-      <c r="S24" s="288">
+      <c r="S24" s="291">
         <v>40.89</v>
       </c>
-      <c r="T24" s="289">
+      <c r="T24" s="299">
         <v>76.84</v>
       </c>
     </row>
@@ -11420,7 +11420,7 @@
       <c r="C25" t="str">
         <v>002149</v>
       </c>
-      <c r="D25" s="306" t="str">
+      <c r="D25" s="301" t="str">
         <v>净买: 8459.47万</v>
       </c>
       <c r="E25">
@@ -11435,40 +11435,40 @@
       <c r="H25">
         <v>1.6</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="308">
         <v>8.27</v>
       </c>
-      <c r="J25" s="311">
+      <c r="J25" s="309">
         <v>19.1</v>
       </c>
       <c r="K25" s="302">
         <v>17.78</v>
       </c>
-      <c r="L25" s="308">
+      <c r="L25" s="303">
         <v>22.26</v>
       </c>
-      <c r="M25" s="309">
+      <c r="M25" s="305">
         <v>32.62</v>
       </c>
-      <c r="N25" s="303">
+      <c r="N25" s="304">
         <v>45.88</v>
       </c>
-      <c r="O25" s="304">
+      <c r="O25" s="310">
         <v>47.71</v>
       </c>
-      <c r="P25" s="312">
+      <c r="P25" s="311">
         <v>41.17</v>
       </c>
-      <c r="Q25" s="305">
+      <c r="Q25" s="306">
         <v>35.78</v>
       </c>
-      <c r="R25" s="300">
+      <c r="R25" s="307">
         <v>43.7</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="312">
         <v>45.34</v>
       </c>
-      <c r="T25" s="301">
+      <c r="T25" s="300">
         <v>73.03</v>
       </c>
     </row>
@@ -11482,7 +11482,7 @@
       <c r="C26" t="str">
         <v>002149</v>
       </c>
-      <c r="D26" s="318" t="str">
+      <c r="D26" s="320" t="str">
         <v>净卖: -9064.32万</v>
       </c>
       <c r="E26">
@@ -11497,40 +11497,40 @@
       <c r="H26">
         <v>2.07</v>
       </c>
-      <c r="I26" s="319">
+      <c r="I26" s="316">
         <v>7.77</v>
       </c>
-      <c r="J26" s="320">
+      <c r="J26" s="317">
         <v>6.57</v>
       </c>
-      <c r="K26" s="314">
+      <c r="K26" s="324">
         <v>10.63</v>
       </c>
-      <c r="L26" s="324">
+      <c r="L26" s="321">
         <v>20</v>
       </c>
-      <c r="M26" s="315">
+      <c r="M26" s="322">
         <v>32</v>
       </c>
-      <c r="N26" s="325">
+      <c r="N26" s="314">
         <v>33.66</v>
       </c>
-      <c r="O26" s="321">
+      <c r="O26" s="323">
         <v>27.74</v>
       </c>
-      <c r="P26" s="316">
+      <c r="P26" s="315">
         <v>22.86</v>
       </c>
-      <c r="Q26" s="317">
+      <c r="Q26" s="318">
         <v>30.03</v>
       </c>
-      <c r="R26" s="313">
+      <c r="R26" s="319">
         <v>31.51</v>
       </c>
-      <c r="S26" s="322">
+      <c r="S26" s="325">
         <v>42.26</v>
       </c>
-      <c r="T26" s="323">
+      <c r="T26" s="313">
         <v>56.57</v>
       </c>
     </row>
@@ -11544,7 +11544,7 @@
       <c r="C27" t="str">
         <v>002149</v>
       </c>
-      <c r="D27" s="338" t="str">
+      <c r="D27" s="334" t="str">
         <v>净买: 7447.80万</v>
       </c>
       <c r="E27">
@@ -11565,34 +11565,34 @@
       <c r="J27" s="330">
         <v>11.27</v>
       </c>
-      <c r="K27" s="327">
+      <c r="K27" s="331">
         <v>6.35</v>
       </c>
-      <c r="L27" s="331">
+      <c r="L27" s="335">
         <v>2.28</v>
       </c>
-      <c r="M27" s="332">
+      <c r="M27" s="338">
         <v>8.25</v>
       </c>
-      <c r="N27" s="326">
+      <c r="N27" s="332">
         <v>9.49</v>
       </c>
-      <c r="O27" s="336">
+      <c r="O27" s="326">
         <v>18.43</v>
       </c>
-      <c r="P27" s="333">
+      <c r="P27" s="327">
         <v>13.87</v>
       </c>
-      <c r="Q27" s="337">
+      <c r="Q27" s="333">
         <v>17.51</v>
       </c>
-      <c r="R27" s="334">
+      <c r="R27" s="336">
         <v>20.31</v>
       </c>
-      <c r="S27" s="335">
+      <c r="S27" s="328">
         <v>22.76</v>
       </c>
-      <c r="T27" s="328">
+      <c r="T27" s="337">
         <v>30.35</v>
       </c>
     </row>
@@ -11606,7 +11606,7 @@
       <c r="C28" t="str">
         <v>301005</v>
       </c>
-      <c r="D28" s="344" t="str">
+      <c r="D28" s="346" t="str">
         <v>净买: 8304.02万</v>
       </c>
       <c r="E28">
@@ -11621,40 +11621,40 @@
       <c r="H28">
         <v>5.58</v>
       </c>
-      <c r="I28" s="340">
+      <c r="I28" s="347">
         <v>13.66</v>
       </c>
-      <c r="J28" s="347">
+      <c r="J28" s="342">
         <v>15.41</v>
       </c>
-      <c r="K28" s="349">
+      <c r="K28" s="343">
         <v>34.28</v>
       </c>
-      <c r="L28" s="345">
+      <c r="L28" s="344">
         <v>23.58</v>
       </c>
-      <c r="M28" s="341">
+      <c r="M28" s="350">
         <v>30.8</v>
       </c>
-      <c r="N28" s="348">
+      <c r="N28" s="351">
         <v>27.1</v>
       </c>
-      <c r="O28" s="350">
+      <c r="O28" s="339">
         <v>39.67</v>
       </c>
-      <c r="P28" s="342">
+      <c r="P28" s="348">
         <v>34.97</v>
       </c>
-      <c r="Q28" s="343">
+      <c r="Q28" s="340">
         <v>45.55</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="341">
         <v>49.76</v>
       </c>
-      <c r="S28" s="339">
+      <c r="S28" s="349">
         <v>66.78</v>
       </c>
-      <c r="T28" s="346">
+      <c r="T28" s="345">
         <v>41.52</v>
       </c>
     </row>
@@ -11668,7 +11668,7 @@
       <c r="C29" t="str">
         <v>300503</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="355" t="str">
         <v>净买: 6889.84万</v>
       </c>
       <c r="E29">
@@ -11683,40 +11683,40 @@
       <c r="H29">
         <v>-5.69</v>
       </c>
-      <c r="I29" s="355">
+      <c r="I29" s="356">
         <v>25.74</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="360">
         <v>25.58</v>
       </c>
-      <c r="K29" s="356">
+      <c r="K29" s="358">
         <v>19.55</v>
       </c>
-      <c r="L29" s="359">
+      <c r="L29" s="361">
         <v>22.01</v>
       </c>
       <c r="M29" s="357">
         <v>17.5</v>
       </c>
-      <c r="N29" s="352">
+      <c r="N29" s="362">
         <v>19.83</v>
       </c>
       <c r="O29" s="353">
         <v>27.93</v>
       </c>
-      <c r="P29" s="360">
+      <c r="P29" s="363">
         <v>36.52</v>
       </c>
-      <c r="Q29" s="354">
+      <c r="Q29" s="364">
         <v>23.97</v>
       </c>
-      <c r="R29" s="361">
+      <c r="R29" s="352">
         <v>21.09</v>
       </c>
-      <c r="S29" s="363">
+      <c r="S29" s="354">
         <v>18.68</v>
       </c>
-      <c r="T29" s="364">
+      <c r="T29" s="359">
         <v>16.85</v>
       </c>
     </row>
@@ -11730,7 +11730,7 @@
       <c r="C30" t="str">
         <v>002565</v>
       </c>
-      <c r="D30" s="369" t="str">
+      <c r="D30" s="376" t="str">
         <v>净卖: -6558.32万</v>
       </c>
       <c r="E30">
@@ -11745,40 +11745,40 @@
       <c r="H30">
         <v>5.73</v>
       </c>
-      <c r="I30" s="377">
+      <c r="I30" s="368">
         <v>-8.62</v>
       </c>
-      <c r="J30" s="374">
+      <c r="J30" s="369">
         <v>-4.85</v>
       </c>
-      <c r="K30" s="365">
+      <c r="K30" s="370">
         <v>0.41</v>
       </c>
-      <c r="L30" s="366">
+      <c r="L30" s="373">
         <v>10.47</v>
       </c>
-      <c r="M30" s="373">
+      <c r="M30" s="371">
         <v>15.07</v>
       </c>
-      <c r="N30" s="375">
+      <c r="N30" s="365">
         <v>18.11</v>
       </c>
-      <c r="O30" s="376">
+      <c r="O30" s="366">
         <v>6.3</v>
       </c>
-      <c r="P30" s="367">
+      <c r="P30" s="374">
         <v>-4.33</v>
       </c>
-      <c r="Q30" s="370">
+      <c r="Q30" s="375">
         <v>-13.88</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="372">
         <v>-18.73</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="367">
         <v>-18.16</v>
       </c>
-      <c r="T30" s="368">
+      <c r="T30" s="377">
         <v>-2.37</v>
       </c>
     </row>
@@ -11807,40 +11807,40 @@
       <c r="H31">
         <v>9.62</v>
       </c>
-      <c r="I31" s="381">
+      <c r="I31" s="382">
         <v>0.34</v>
       </c>
-      <c r="J31" s="386">
+      <c r="J31" s="389">
         <v>10.38</v>
       </c>
-      <c r="K31" s="390">
+      <c r="K31" s="379">
         <v>15.86</v>
       </c>
-      <c r="L31" s="383">
+      <c r="L31" s="390">
         <v>19.86</v>
       </c>
-      <c r="M31" s="384">
+      <c r="M31" s="380">
         <v>22.13</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="378">
         <v>34.34</v>
       </c>
-      <c r="O31" s="378">
+      <c r="O31" s="386">
         <v>20.9</v>
       </c>
-      <c r="P31" s="379">
+      <c r="P31" s="383">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="387">
+      <c r="Q31" s="381">
         <v>5.08</v>
       </c>
-      <c r="R31" s="380">
+      <c r="R31" s="387">
         <v>0.26</v>
       </c>
       <c r="S31" s="388">
         <v>-0.74</v>
       </c>
-      <c r="T31" s="389">
+      <c r="T31" s="384">
         <v>-22.73</v>
       </c>
     </row>
@@ -11854,7 +11854,7 @@
       <c r="C32" t="str">
         <v>601698</v>
       </c>
-      <c r="D32" s="398" t="str">
+      <c r="D32" s="402" t="str">
         <v>净买: 194.55万</v>
       </c>
       <c r="E32">
@@ -11869,40 +11869,40 @@
       <c r="H32">
         <v>2.6</v>
       </c>
-      <c r="I32" s="395">
+      <c r="I32" s="393">
         <v>7.2</v>
       </c>
-      <c r="J32" s="402">
+      <c r="J32" s="403">
         <v>17.92</v>
       </c>
-      <c r="K32" s="396">
+      <c r="K32" s="399">
         <v>19.67</v>
       </c>
-      <c r="L32" s="399">
+      <c r="L32" s="394">
         <v>21.47</v>
       </c>
-      <c r="M32" s="403">
+      <c r="M32" s="395">
         <v>33.61</v>
       </c>
-      <c r="N32" s="391">
+      <c r="N32" s="396">
         <v>46.97</v>
       </c>
-      <c r="O32" s="392">
+      <c r="O32" s="391">
         <v>32.27</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="392">
         <v>19.04</v>
       </c>
-      <c r="Q32" s="400">
+      <c r="Q32" s="397">
         <v>7.15</v>
       </c>
-      <c r="R32" s="394">
+      <c r="R32" s="400">
         <v>9.55</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="398">
         <v>8.54</v>
       </c>
-      <c r="T32" s="397">
+      <c r="T32" s="401">
         <v>-7.31</v>
       </c>
     </row>
@@ -11916,7 +11916,7 @@
       <c r="C33" t="str">
         <v>603698</v>
       </c>
-      <c r="D33" s="410" t="str">
+      <c r="D33" s="404" t="str">
         <v>净买: 6020.50万</v>
       </c>
       <c r="E33">
@@ -11931,40 +11931,40 @@
       <c r="H33">
         <v>-3.65</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="412">
         <v>14.16</v>
       </c>
-      <c r="J33" s="404">
+      <c r="J33" s="406">
         <v>8.62</v>
       </c>
-      <c r="K33" s="405">
+      <c r="K33" s="407">
         <v>15.14</v>
       </c>
-      <c r="L33" s="412">
+      <c r="L33" s="413">
         <v>18.92</v>
       </c>
-      <c r="M33" s="413">
+      <c r="M33" s="405">
         <v>30.81</v>
       </c>
-      <c r="N33" s="406">
+      <c r="N33" s="408">
         <v>17.73</v>
       </c>
       <c r="O33" s="414">
         <v>5.95</v>
       </c>
-      <c r="P33" s="407">
+      <c r="P33" s="415">
         <v>3.38</v>
       </c>
       <c r="Q33" s="409">
         <v>8.46</v>
       </c>
-      <c r="R33" s="415">
+      <c r="R33" s="410">
         <v>3.19</v>
       </c>
-      <c r="S33" s="416">
+      <c r="S33" s="411">
         <v>-2.16</v>
       </c>
-      <c r="T33" s="411">
+      <c r="T33" s="416">
         <v>24.84</v>
       </c>
     </row>
@@ -11993,40 +11993,40 @@
       <c r="H34">
         <v>9.99</v>
       </c>
-      <c r="I34" s="419">
+      <c r="I34" s="428">
         <v>0</v>
       </c>
-      <c r="J34" s="425">
+      <c r="J34" s="429">
         <v>9.99</v>
       </c>
-      <c r="K34" s="420">
+      <c r="K34" s="424">
         <v>6.29</v>
       </c>
-      <c r="L34" s="423">
+      <c r="L34" s="419">
         <v>4.51</v>
       </c>
-      <c r="M34" s="426">
+      <c r="M34" s="417">
         <v>-5.95</v>
       </c>
-      <c r="N34" s="429">
+      <c r="N34" s="420">
         <v>-15.34</v>
       </c>
-      <c r="O34" s="427">
+      <c r="O34" s="426">
         <v>-13.27</v>
       </c>
-      <c r="P34" s="428">
+      <c r="P34" s="425">
         <v>-18.41</v>
       </c>
-      <c r="Q34" s="417">
+      <c r="Q34" s="427">
         <v>-20.32</v>
       </c>
       <c r="R34" s="421">
         <v>-15.81</v>
       </c>
-      <c r="S34" s="424">
+      <c r="S34" s="422">
         <v>-7.39</v>
       </c>
-      <c r="T34" s="422">
+      <c r="T34" s="423">
         <v>-20.51</v>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       <c r="C35" t="str">
         <v>002202</v>
       </c>
-      <c r="D35" s="441" t="str">
+      <c r="D35" s="442" t="str">
         <v>净买: 3.95亿</v>
       </c>
       <c r="E35">
@@ -12055,40 +12055,40 @@
       <c r="H35">
         <v>6.42</v>
       </c>
-      <c r="I35" s="442">
+      <c r="I35" s="434">
         <v>3.35</v>
       </c>
-      <c r="J35" s="437">
+      <c r="J35" s="435">
         <v>-0.12</v>
       </c>
-      <c r="K35" s="438">
+      <c r="K35" s="436">
         <v>-1.79</v>
       </c>
-      <c r="L35" s="439">
+      <c r="L35" s="441">
         <v>-11.62</v>
       </c>
-      <c r="M35" s="430">
+      <c r="M35" s="437">
         <v>-20.45</v>
       </c>
-      <c r="N35" s="435">
+      <c r="N35" s="430">
         <v>-18.51</v>
       </c>
-      <c r="O35" s="440">
+      <c r="O35" s="438">
         <v>-23.33</v>
       </c>
-      <c r="P35" s="431">
+      <c r="P35" s="439">
         <v>-25.13</v>
       </c>
-      <c r="Q35" s="436">
+      <c r="Q35" s="431">
         <v>-20.89</v>
       </c>
       <c r="R35" s="432">
         <v>-12.97</v>
       </c>
-      <c r="S35" s="433">
+      <c r="S35" s="440">
         <v>-16.45</v>
       </c>
-      <c r="T35" s="434">
+      <c r="T35" s="433">
         <v>-25.3</v>
       </c>
     </row>
@@ -12102,7 +12102,7 @@
       <c r="C36" t="str">
         <v>000901</v>
       </c>
-      <c r="D36" s="455" t="str">
+      <c r="D36" s="449" t="str">
         <v>净买: 926.43万</v>
       </c>
       <c r="E36">
@@ -12117,40 +12117,40 @@
       <c r="H36">
         <v>1.96</v>
       </c>
-      <c r="I36" s="443">
+      <c r="I36" s="453">
         <v>6.61</v>
       </c>
       <c r="J36" s="447">
         <v>-4.05</v>
       </c>
-      <c r="K36" s="448">
+      <c r="K36" s="450">
         <v>-11.42</v>
       </c>
-      <c r="L36" s="449">
+      <c r="L36" s="451">
         <v>-16.39</v>
       </c>
-      <c r="M36" s="452">
+      <c r="M36" s="448">
         <v>-14.59</v>
       </c>
-      <c r="N36" s="453">
+      <c r="N36" s="454">
         <v>-14.59</v>
       </c>
-      <c r="O36" s="454">
+      <c r="O36" s="443">
         <v>-20.53</v>
       </c>
-      <c r="P36" s="444">
+      <c r="P36" s="455">
         <v>-21.57</v>
       </c>
-      <c r="Q36" s="450">
+      <c r="Q36" s="444">
         <v>-18.98</v>
       </c>
       <c r="R36" s="445">
         <v>-15.35</v>
       </c>
-      <c r="S36" s="446">
+      <c r="S36" s="452">
         <v>-23.06</v>
       </c>
-      <c r="T36" s="451">
+      <c r="T36" s="446">
         <v>-29.58</v>
       </c>
     </row>
@@ -12164,7 +12164,7 @@
       <c r="C37" t="str">
         <v>600498</v>
       </c>
-      <c r="D37" s="465" t="str">
+      <c r="D37" s="468" t="str">
         <v>净卖: -3.15亿</v>
       </c>
       <c r="E37">
@@ -12179,40 +12179,40 @@
       <c r="H37">
         <v>3.52</v>
       </c>
-      <c r="I37" s="466">
+      <c r="I37" s="463">
         <v>4.32</v>
       </c>
-      <c r="J37" s="458">
+      <c r="J37" s="456">
         <v>-6.12</v>
       </c>
-      <c r="K37" s="459">
+      <c r="K37" s="457">
         <v>-14.95</v>
       </c>
-      <c r="L37" s="462">
+      <c r="L37" s="460">
         <v>-14.32</v>
       </c>
-      <c r="M37" s="460">
+      <c r="M37" s="466">
         <v>-19.2</v>
       </c>
-      <c r="N37" s="461">
+      <c r="N37" s="458">
         <v>-20.25</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="464">
         <v>-17.13</v>
       </c>
-      <c r="P37" s="463">
+      <c r="P37" s="461">
         <v>-8.85</v>
       </c>
-      <c r="Q37" s="468">
+      <c r="Q37" s="462">
         <v>-12.45</v>
       </c>
-      <c r="R37" s="464">
+      <c r="R37" s="465">
         <v>-13.08</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="467">
         <v>-11.97</v>
       </c>
-      <c r="T37" s="457">
+      <c r="T37" s="459">
         <v>7.39</v>
       </c>
     </row>
@@ -12226,7 +12226,7 @@
       <c r="C38" t="str">
         <v>002202</v>
       </c>
-      <c r="D38" s="473" t="str">
+      <c r="D38" s="477" t="str">
         <v>净卖: -1.92亿</v>
       </c>
       <c r="E38">
@@ -12241,40 +12241,40 @@
       <c r="H38">
         <v>-8.96</v>
       </c>
-      <c r="I38" s="474">
+      <c r="I38" s="469">
         <v>-1.15</v>
       </c>
-      <c r="J38" s="475">
+      <c r="J38" s="470">
         <v>-11.02</v>
       </c>
-      <c r="K38" s="479">
+      <c r="K38" s="478">
         <v>-8.85</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="471">
         <v>-14.25</v>
       </c>
-      <c r="M38" s="480">
+      <c r="M38" s="472">
         <v>-16.26</v>
       </c>
-      <c r="N38" s="481">
+      <c r="N38" s="479">
         <v>-11.52</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="480">
         <v>-2.67</v>
       </c>
-      <c r="P38" s="472">
+      <c r="P38" s="481">
         <v>-6.55</v>
       </c>
-      <c r="Q38" s="469">
+      <c r="Q38" s="473">
         <v>-5.92</v>
       </c>
-      <c r="R38" s="476">
+      <c r="R38" s="474">
         <v>-8.82</v>
       </c>
-      <c r="S38" s="477">
+      <c r="S38" s="475">
         <v>-11.48</v>
       </c>
-      <c r="T38" s="478">
+      <c r="T38" s="476">
         <v>-16.45</v>
       </c>
     </row>
@@ -12288,7 +12288,7 @@
       <c r="C39" t="str">
         <v>002202</v>
       </c>
-      <c r="D39" s="490" t="str">
+      <c r="D39" s="487" t="str">
         <v>净卖: -1.10亿</v>
       </c>
       <c r="E39">
@@ -12303,40 +12303,40 @@
       <c r="H39">
         <v>-9.99</v>
       </c>
-      <c r="I39" s="491">
+      <c r="I39" s="488">
         <v>0</v>
       </c>
-      <c r="J39" s="492">
+      <c r="J39" s="489">
         <v>2.44</v>
       </c>
-      <c r="K39" s="486">
+      <c r="K39" s="490">
         <v>-3.62</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="482">
         <v>-5.88</v>
       </c>
-      <c r="M39" s="484">
+      <c r="M39" s="485">
         <v>-0.55</v>
       </c>
-      <c r="N39" s="487">
+      <c r="N39" s="483">
         <v>9.39</v>
       </c>
-      <c r="O39" s="494">
+      <c r="O39" s="484">
         <v>5.03</v>
       </c>
-      <c r="P39" s="482">
+      <c r="P39" s="493">
         <v>5.73</v>
       </c>
-      <c r="Q39" s="488">
+      <c r="Q39" s="491">
         <v>2.48</v>
       </c>
-      <c r="R39" s="485">
+      <c r="R39" s="486">
         <v>-0.52</v>
       </c>
-      <c r="S39" s="483">
+      <c r="S39" s="492">
         <v>-3.44</v>
       </c>
-      <c r="T39" s="489">
+      <c r="T39" s="494">
         <v>-6.1</v>
       </c>
     </row>
@@ -12350,7 +12350,7 @@
       <c r="C40" t="str">
         <v>300118</v>
       </c>
-      <c r="D40" s="495" t="str">
+      <c r="D40" s="498" t="str">
         <v>净买: 1.31亿</v>
       </c>
       <c r="E40">
@@ -12365,40 +12365,40 @@
       <c r="H40">
         <v>15.61</v>
       </c>
-      <c r="I40" s="498">
+      <c r="I40" s="496">
         <v>-6.17</v>
       </c>
-      <c r="J40" s="499">
+      <c r="J40" s="503">
         <v>-4.46</v>
       </c>
-      <c r="K40" s="502">
+      <c r="K40" s="497">
         <v>-11.42</v>
       </c>
-      <c r="L40" s="505">
+      <c r="L40" s="504">
         <v>-12.25</v>
       </c>
-      <c r="M40" s="503">
+      <c r="M40" s="499">
         <v>-16.96</v>
       </c>
-      <c r="N40" s="500">
+      <c r="N40" s="507">
         <v>-12.92</v>
       </c>
-      <c r="O40" s="496">
+      <c r="O40" s="505">
         <v>-6.46</v>
       </c>
-      <c r="P40" s="504">
+      <c r="P40" s="500">
         <v>0</v>
       </c>
-      <c r="Q40" s="506">
+      <c r="Q40" s="501">
         <v>-3.17</v>
       </c>
-      <c r="R40" s="497">
+      <c r="R40" s="495">
         <v>-6.54</v>
       </c>
-      <c r="S40" s="501">
+      <c r="S40" s="506">
         <v>-4.71</v>
       </c>
-      <c r="T40" s="507">
+      <c r="T40" s="502">
         <v>-30.75</v>
       </c>
     </row>
@@ -12412,7 +12412,7 @@
       <c r="C41" t="str">
         <v>001337</v>
       </c>
-      <c r="D41" s="510" t="str">
+      <c r="D41" s="512" t="str">
         <v>净买: 4696.53万</v>
       </c>
       <c r="E41">
@@ -12427,40 +12427,40 @@
       <c r="H41">
         <v>5.3</v>
       </c>
-      <c r="I41" s="515">
+      <c r="I41" s="520">
         <v>4.47</v>
       </c>
-      <c r="J41" s="511">
+      <c r="J41" s="513">
         <v>14.89</v>
       </c>
-      <c r="K41" s="520">
+      <c r="K41" s="517">
         <v>3.41</v>
       </c>
-      <c r="L41" s="512">
+      <c r="L41" s="518">
         <v>-6.94</v>
       </c>
-      <c r="M41" s="513">
+      <c r="M41" s="514">
         <v>-12.41</v>
       </c>
-      <c r="N41" s="508">
+      <c r="N41" s="509">
         <v>-20.23</v>
       </c>
-      <c r="O41" s="517">
+      <c r="O41" s="519">
         <v>-28.05</v>
       </c>
-      <c r="P41" s="516">
+      <c r="P41" s="515">
         <v>-27.52</v>
       </c>
-      <c r="Q41" s="509">
+      <c r="Q41" s="516">
         <v>-24</v>
       </c>
-      <c r="R41" s="518">
+      <c r="R41" s="510">
         <v>-27.11</v>
       </c>
-      <c r="S41" s="519">
+      <c r="S41" s="511">
         <v>-26.55</v>
       </c>
-      <c r="T41" s="514">
+      <c r="T41" s="508">
         <v>-25.28</v>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       <c r="C42" t="str">
         <v>001337</v>
       </c>
-      <c r="D42" s="521" t="str">
+      <c r="D42" s="532" t="str">
         <v>净卖: -5018.84万</v>
       </c>
       <c r="E42">
@@ -12489,40 +12489,40 @@
       <c r="H42">
         <v>10.01</v>
       </c>
-      <c r="I42" s="527">
+      <c r="I42" s="533">
         <v>-0.03</v>
       </c>
-      <c r="J42" s="528">
+      <c r="J42" s="530">
         <v>-10.02</v>
       </c>
-      <c r="K42" s="529">
+      <c r="K42" s="525">
         <v>-19.02</v>
       </c>
-      <c r="L42" s="530">
+      <c r="L42" s="521">
         <v>-23.78</v>
       </c>
-      <c r="M42" s="531">
+      <c r="M42" s="522">
         <v>-30.59</v>
       </c>
-      <c r="N42" s="522">
+      <c r="N42" s="526">
         <v>-37.39</v>
       </c>
-      <c r="O42" s="532">
+      <c r="O42" s="528">
         <v>-36.93</v>
       </c>
       <c r="P42" s="523">
         <v>-33.87</v>
       </c>
-      <c r="Q42" s="524">
+      <c r="Q42" s="529">
         <v>-36.57</v>
       </c>
-      <c r="R42" s="525">
+      <c r="R42" s="531">
         <v>-36.08</v>
       </c>
-      <c r="S42" s="526">
+      <c r="S42" s="527">
         <v>-36.64</v>
       </c>
-      <c r="T42" s="533">
+      <c r="T42" s="524">
         <v>-34.98</v>
       </c>
     </row>
@@ -12551,40 +12551,40 @@
       <c r="H43">
         <v>10.01</v>
       </c>
-      <c r="I43" s="545">
+      <c r="I43" s="542">
         <v>0</v>
       </c>
-      <c r="J43" s="542">
+      <c r="J43" s="543">
         <v>9.98</v>
       </c>
-      <c r="K43" s="543">
+      <c r="K43" s="538">
         <v>20.97</v>
       </c>
       <c r="L43" s="534">
         <v>19.02</v>
       </c>
-      <c r="M43" s="538">
+      <c r="M43" s="544">
         <v>26.11</v>
       </c>
-      <c r="N43" s="544">
+      <c r="N43" s="539">
         <v>13.5</v>
       </c>
-      <c r="O43" s="535">
+      <c r="O43" s="546">
         <v>18.02</v>
       </c>
-      <c r="P43" s="536">
+      <c r="P43" s="545">
         <v>6.91</v>
       </c>
-      <c r="Q43" s="537">
+      <c r="Q43" s="535">
         <v>4.02</v>
       </c>
-      <c r="R43" s="539">
+      <c r="R43" s="536">
         <v>0.38</v>
       </c>
-      <c r="S43" s="546">
+      <c r="S43" s="540">
         <v>-1.63</v>
       </c>
-      <c r="T43" s="540">
+      <c r="T43" s="537">
         <v>-13.68</v>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       <c r="C44" t="str">
         <v>000995</v>
       </c>
-      <c r="D44" s="559" t="str">
+      <c r="D44" s="558" t="str">
         <v>净卖: -1741.06万</v>
       </c>
       <c r="E44">
@@ -12613,40 +12613,40 @@
       <c r="H44">
         <v>-4.33</v>
       </c>
-      <c r="I44" s="553">
+      <c r="I44" s="549">
         <v>14.96</v>
       </c>
-      <c r="J44" s="554">
+      <c r="J44" s="550">
         <v>26.44</v>
       </c>
-      <c r="K44" s="555">
+      <c r="K44" s="559">
         <v>24.41</v>
       </c>
-      <c r="L44" s="551">
+      <c r="L44" s="555">
         <v>31.82</v>
       </c>
-      <c r="M44" s="556">
+      <c r="M44" s="553">
         <v>18.64</v>
       </c>
-      <c r="N44" s="557">
+      <c r="N44" s="551">
         <v>23.36</v>
       </c>
-      <c r="O44" s="558">
+      <c r="O44" s="547">
         <v>11.75</v>
       </c>
-      <c r="P44" s="547">
+      <c r="P44" s="556">
         <v>8.73</v>
       </c>
-      <c r="Q44" s="548">
+      <c r="Q44" s="552">
         <v>4.92</v>
       </c>
-      <c r="R44" s="552">
+      <c r="R44" s="557">
         <v>2.82</v>
       </c>
-      <c r="S44" s="549">
+      <c r="S44" s="554">
         <v>3.87</v>
       </c>
-      <c r="T44" s="550">
+      <c r="T44" s="548">
         <v>-9.78</v>
       </c>
     </row>
@@ -12660,7 +12660,7 @@
       <c r="C45" t="str">
         <v>301292</v>
       </c>
-      <c r="D45" s="565" t="str">
+      <c r="D45" s="572" t="str">
         <v>净买: 2923.62万</v>
       </c>
       <c r="E45">
@@ -12675,40 +12675,40 @@
       <c r="H45">
         <v>-0.29</v>
       </c>
-      <c r="I45" s="560">
+      <c r="I45" s="564">
         <v>20.35</v>
       </c>
-      <c r="J45" s="569">
+      <c r="J45" s="565">
         <v>23.96</v>
       </c>
-      <c r="K45" s="561">
+      <c r="K45" s="560">
         <v>16.61</v>
       </c>
-      <c r="L45" s="568">
+      <c r="L45" s="566">
         <v>13.75</v>
       </c>
-      <c r="M45" s="562">
+      <c r="M45" s="561">
         <v>10.84</v>
       </c>
-      <c r="N45" s="570">
+      <c r="N45" s="567">
         <v>7.09</v>
       </c>
-      <c r="O45" s="571">
+      <c r="O45" s="570">
         <v>7.44</v>
       </c>
-      <c r="P45" s="566">
+      <c r="P45" s="562">
         <v>2.1</v>
       </c>
-      <c r="Q45" s="567">
+      <c r="Q45" s="568">
         <v>1.76</v>
       </c>
-      <c r="R45" s="563">
+      <c r="R45" s="571">
         <v>6.85</v>
       </c>
-      <c r="S45" s="564">
+      <c r="S45" s="569">
         <v>11.3</v>
       </c>
-      <c r="T45" s="572">
+      <c r="T45" s="563">
         <v>15.74</v>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       <c r="C46" t="str">
         <v>301396</v>
       </c>
-      <c r="D46" s="573" t="str">
+      <c r="D46" s="575" t="str">
         <v>净买: 9469.00万</v>
       </c>
       <c r="E46">
@@ -12737,10 +12737,10 @@
       <c r="H46">
         <v>2.83</v>
       </c>
-      <c r="I46" s="574">
+      <c r="I46" s="576">
         <v>16.7</v>
       </c>
-      <c r="J46" s="575">
+      <c r="J46" s="573">
         <v>13.98</v>
       </c>
       <c r="K46" t="str"/>
@@ -12752,7 +12752,7 @@
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="576">
+      <c r="T46" s="574">
         <v>13.98</v>
       </c>
     </row>
@@ -12815,40 +12815,40 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="583">
+      <c r="I48" s="585">
         <v>71.11</v>
       </c>
-      <c r="J48" s="577">
+      <c r="J48" s="579">
         <v>64.44</v>
       </c>
       <c r="K48" s="580">
         <v>59.09</v>
       </c>
-      <c r="L48" s="581">
+      <c r="L48" s="586">
         <v>56.82</v>
       </c>
-      <c r="M48" s="584">
+      <c r="M48" s="581">
         <v>61.36</v>
       </c>
-      <c r="N48" s="586">
+      <c r="N48" s="588">
         <v>61.36</v>
       </c>
-      <c r="O48" s="578">
+      <c r="O48" s="582">
         <v>56.82</v>
       </c>
-      <c r="P48" s="582">
+      <c r="P48" s="584">
         <v>52.27</v>
       </c>
-      <c r="Q48" s="587">
+      <c r="Q48" s="583">
         <v>59.09</v>
       </c>
-      <c r="R48" s="579">
+      <c r="R48" s="577">
         <v>52.27</v>
       </c>
-      <c r="S48" s="585">
+      <c r="S48" s="578">
         <v>43.18</v>
       </c>
-      <c r="T48" s="588">
+      <c r="T48" s="587">
         <v>31.11</v>
       </c>
     </row>
@@ -12866,19 +12866,19 @@
       <c r="I49" s="589">
         <v>5.74</v>
       </c>
-      <c r="J49" s="590">
+      <c r="J49" s="593">
         <v>5.25</v>
       </c>
       <c r="K49" s="594">
         <v>4.02</v>
       </c>
-      <c r="L49" s="599">
+      <c r="L49" s="595">
         <v>3.64</v>
       </c>
-      <c r="M49" s="600">
+      <c r="M49" s="590">
         <v>4.36</v>
       </c>
-      <c r="N49" s="595">
+      <c r="N49" s="599">
         <v>5.31</v>
       </c>
       <c r="O49" s="591">
@@ -12890,13 +12890,13 @@
       <c r="Q49" s="596">
         <v>3.34</v>
       </c>
-      <c r="R49" s="597">
+      <c r="R49" s="600">
         <v>3.21</v>
       </c>
       <c r="S49" s="598">
         <v>3.56</v>
       </c>
-      <c r="T49" s="593">
+      <c r="T49" s="597">
         <v>-2.75</v>
       </c>
     </row>

--- a/youzi/徐晓/index.xlsx
+++ b/youzi/徐晓/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="602">
+  <fills count="603">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -51,6 +51,54 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -69,49 +117,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -123,7 +159,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,19 +183,1627 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6DC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24973E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -165,55 +1821,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -243,37 +1875,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDE4150"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -285,25 +2301,283 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1AFB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -315,19 +2589,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,43 +2625,97 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -387,61 +2727,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9FD8AC"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -453,67 +2817,523 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB7E1C1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -525,6 +3345,30 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -537,31 +3381,205 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -573,97 +3591,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF60BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
+        <fgColor rgb="FFC62B39"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -675,271 +3603,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
+        <fgColor rgb="FFBB2634"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -957,2688 +3621,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF99D5A6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF249A3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196E2F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFAE6E8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="601">
+  <borders count="602">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7850,7 +7863,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="601">
+  <cellXfs count="602">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9650,6 +9663,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="600" fillId="601" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="601" fillId="602" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -9994,7 +10010,7 @@
       <c r="C2" t="str">
         <v>600120</v>
       </c>
-      <c r="D2" s="3" t="str">
+      <c r="D2" s="11" t="str">
         <v>净卖: -1.33亿</v>
       </c>
       <c r="E2">
@@ -10009,41 +10025,41 @@
       <c r="H2">
         <v>9.97</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="12">
         <v>-12.49</v>
       </c>
-      <c r="J2" s="11">
+      <c r="J2" s="9">
         <v>-21.25</v>
       </c>
-      <c r="K2" s="12">
+      <c r="K2" s="2">
         <v>-22.96</v>
       </c>
-      <c r="L2" s="4">
+      <c r="L2" s="3">
         <v>-26.08</v>
       </c>
-      <c r="M2" s="7">
+      <c r="M2" s="4">
         <v>-20.85</v>
       </c>
-      <c r="N2" s="13">
+      <c r="N2" s="10">
         <v>-20.85</v>
       </c>
-      <c r="O2" s="1">
+      <c r="O2" s="5">
         <v>-22.16</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="6">
         <v>-26.28</v>
       </c>
-      <c r="Q2" s="10">
+      <c r="Q2" s="7">
         <v>-25.48</v>
       </c>
-      <c r="R2" s="8">
+      <c r="R2" s="13">
         <v>-24.07</v>
       </c>
-      <c r="S2" s="5">
+      <c r="S2" s="1">
         <v>-25.78</v>
       </c>
-      <c r="T2" s="6">
-        <v>-42.3</v>
+      <c r="T2" s="8">
+        <v>-42.4</v>
       </c>
     </row>
     <row r="3">
@@ -10056,7 +10072,7 @@
       <c r="C3" t="str">
         <v>003021</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="24" t="str">
         <v>净卖: -3895.40万</v>
       </c>
       <c r="E3">
@@ -10071,41 +10087,41 @@
       <c r="H3">
         <v>-3</v>
       </c>
-      <c r="I3" s="14">
+      <c r="I3" s="20">
         <v>-7.22</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="25">
         <v>-10.22</v>
       </c>
-      <c r="K3" s="17">
+      <c r="K3" s="18">
         <v>-4.57</v>
       </c>
-      <c r="L3" s="18">
+      <c r="L3" s="16">
         <v>-7.52</v>
       </c>
-      <c r="M3" s="19">
+      <c r="M3" s="21">
         <v>-0.02</v>
       </c>
-      <c r="N3" s="26">
+      <c r="N3" s="17">
         <v>4.27</v>
       </c>
-      <c r="O3" s="20">
+      <c r="O3" s="22">
         <v>5.17</v>
       </c>
-      <c r="P3" s="23">
+      <c r="P3" s="19">
         <v>3.7</v>
       </c>
-      <c r="Q3" s="24">
+      <c r="Q3" s="26">
         <v>13.88</v>
       </c>
-      <c r="R3" s="21">
+      <c r="R3" s="14">
         <v>25.27</v>
       </c>
-      <c r="S3" s="25">
+      <c r="S3" s="23">
         <v>24.52</v>
       </c>
       <c r="T3" s="15">
-        <v>-19.33</v>
+        <v>-19.46</v>
       </c>
     </row>
     <row r="4">
@@ -10118,7 +10134,7 @@
       <c r="C4" t="str">
         <v>002896</v>
       </c>
-      <c r="D4" s="31" t="str">
+      <c r="D4" s="35" t="str">
         <v>净买: 5162.35万</v>
       </c>
       <c r="E4">
@@ -10133,22 +10149,22 @@
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="38">
+      <c r="I4" s="29">
         <v>6.79</v>
       </c>
-      <c r="J4" s="32">
+      <c r="J4" s="38">
         <v>17.47</v>
       </c>
-      <c r="K4" s="35">
+      <c r="K4" s="39">
         <v>5.82</v>
       </c>
       <c r="L4" s="36">
         <v>15.69</v>
       </c>
-      <c r="M4" s="29">
+      <c r="M4" s="32">
         <v>27.26</v>
       </c>
-      <c r="N4" s="39">
+      <c r="N4" s="37">
         <v>39.98</v>
       </c>
       <c r="O4" s="33">
@@ -10157,17 +10173,17 @@
       <c r="P4" s="27">
         <v>13.39</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="34">
         <v>16.45</v>
       </c>
-      <c r="R4" s="34">
+      <c r="R4" s="30">
         <v>19.91</v>
       </c>
-      <c r="S4" s="37">
+      <c r="S4" s="28">
         <v>19.53</v>
       </c>
-      <c r="T4" s="30">
-        <v>-10.2</v>
+      <c r="T4" s="31">
+        <v>-12.26</v>
       </c>
     </row>
     <row r="5">
@@ -10180,7 +10196,7 @@
       <c r="C5" t="str">
         <v>600602</v>
       </c>
-      <c r="D5" s="50" t="str">
+      <c r="D5" s="45" t="str">
         <v>净买: 1.03亿</v>
       </c>
       <c r="E5">
@@ -10195,41 +10211,41 @@
       <c r="H5">
         <v>-2.66</v>
       </c>
-      <c r="I5" s="51">
+      <c r="I5" s="46">
         <v>10.77</v>
       </c>
-      <c r="J5" s="43">
+      <c r="J5" s="47">
         <v>5.81</v>
       </c>
-      <c r="K5" s="47">
+      <c r="K5" s="50">
         <v>-3.88</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="51">
         <v>-13.5</v>
       </c>
-      <c r="M5" s="44">
+      <c r="M5" s="43">
         <v>-15.88</v>
       </c>
       <c r="N5" s="48">
         <v>-14.23</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="52">
         <v>-8.5</v>
       </c>
-      <c r="P5" s="45">
+      <c r="P5" s="40">
         <v>-5.04</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="41">
         <v>4.46</v>
       </c>
-      <c r="R5" s="41">
+      <c r="R5" s="42">
         <v>6.31</v>
       </c>
-      <c r="S5" s="49">
+      <c r="S5" s="44">
         <v>10.62</v>
       </c>
-      <c r="T5" s="46">
-        <v>-7.38</v>
+      <c r="T5" s="49">
+        <v>-8.77</v>
       </c>
     </row>
     <row r="6">
@@ -10242,7 +10258,7 @@
       <c r="C6" t="str">
         <v>003021</v>
       </c>
-      <c r="D6" s="58" t="str">
+      <c r="D6" s="55" t="str">
         <v>净买: 5581.43万</v>
       </c>
       <c r="E6">
@@ -10257,10 +10273,10 @@
       <c r="H6">
         <v>-1.3</v>
       </c>
-      <c r="I6" s="59">
+      <c r="I6" s="56">
         <v>11.45</v>
       </c>
-      <c r="J6" s="57">
+      <c r="J6" s="59">
         <v>10.79</v>
       </c>
       <c r="K6" s="60">
@@ -10269,29 +10285,29 @@
       <c r="L6" s="53">
         <v>-5.12</v>
       </c>
-      <c r="M6" s="61">
+      <c r="M6" s="62">
         <v>4.3</v>
       </c>
       <c r="N6" s="54">
         <v>14.73</v>
       </c>
-      <c r="O6" s="62">
+      <c r="O6" s="63">
         <v>13.05</v>
       </c>
-      <c r="P6" s="63">
+      <c r="P6" s="61">
         <v>12.06</v>
       </c>
-      <c r="Q6" s="64">
+      <c r="Q6" s="57">
         <v>13.73</v>
       </c>
-      <c r="R6" s="65">
+      <c r="R6" s="64">
         <v>10.86</v>
       </c>
-      <c r="S6" s="55">
+      <c r="S6" s="58">
         <v>10.2</v>
       </c>
-      <c r="T6" s="56">
-        <v>-28.23</v>
+      <c r="T6" s="65">
+        <v>-28.34</v>
       </c>
     </row>
     <row r="7">
@@ -10304,7 +10320,7 @@
       <c r="C7" t="str">
         <v>002522</v>
       </c>
-      <c r="D7" s="69" t="str">
+      <c r="D7" s="71" t="str">
         <v>净卖: -2406.69万</v>
       </c>
       <c r="E7">
@@ -10319,41 +10335,41 @@
       <c r="H7">
         <v>-5.38</v>
       </c>
-      <c r="I7" s="70">
+      <c r="I7" s="76">
         <v>-4.11</v>
       </c>
-      <c r="J7" s="71">
+      <c r="J7" s="77">
         <v>-13.74</v>
       </c>
-      <c r="K7" s="72">
+      <c r="K7" s="78">
         <v>-21.64</v>
       </c>
-      <c r="L7" s="73">
+      <c r="L7" s="68">
         <v>-19.75</v>
       </c>
-      <c r="M7" s="78">
+      <c r="M7" s="66">
         <v>-18.96</v>
       </c>
-      <c r="N7" s="74">
+      <c r="N7" s="72">
         <v>-16.9</v>
       </c>
-      <c r="O7" s="75">
+      <c r="O7" s="67">
         <v>-18.64</v>
       </c>
-      <c r="P7" s="76">
+      <c r="P7" s="69">
         <v>-16.27</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="70">
         <v>-17.06</v>
       </c>
-      <c r="R7" s="77">
+      <c r="R7" s="73">
         <v>-16.75</v>
       </c>
-      <c r="S7" s="67">
+      <c r="S7" s="74">
         <v>-19.59</v>
       </c>
-      <c r="T7" s="68">
-        <v>-2.21</v>
+      <c r="T7" s="75">
+        <v>-0.79</v>
       </c>
     </row>
     <row r="8">
@@ -10366,7 +10382,7 @@
       <c r="C8" t="str">
         <v>003021</v>
       </c>
-      <c r="D8" s="83" t="str">
+      <c r="D8" s="90" t="str">
         <v>净卖: -7322.64万</v>
       </c>
       <c r="E8">
@@ -10381,41 +10397,41 @@
       <c r="H8">
         <v>-1.2</v>
       </c>
-      <c r="I8" s="84">
+      <c r="I8" s="87">
         <v>11.33</v>
       </c>
-      <c r="J8" s="89">
+      <c r="J8" s="82">
         <v>9.7</v>
       </c>
-      <c r="K8" s="81">
+      <c r="K8" s="91">
         <v>8.74</v>
       </c>
-      <c r="L8" s="82">
+      <c r="L8" s="88">
         <v>10.37</v>
       </c>
-      <c r="M8" s="90">
+      <c r="M8" s="89">
         <v>7.58</v>
       </c>
-      <c r="N8" s="85">
+      <c r="N8" s="83">
         <v>6.94</v>
       </c>
-      <c r="O8" s="87">
+      <c r="O8" s="79">
         <v>-0.96</v>
       </c>
-      <c r="P8" s="88">
+      <c r="P8" s="80">
         <v>1.12</v>
       </c>
-      <c r="Q8" s="91">
+      <c r="Q8" s="84">
         <v>2.48</v>
       </c>
-      <c r="R8" s="79">
+      <c r="R8" s="81">
         <v>-0.05</v>
       </c>
-      <c r="S8" s="86">
+      <c r="S8" s="85">
         <v>-2.14</v>
       </c>
-      <c r="T8" s="80">
-        <v>-30.35</v>
+      <c r="T8" s="86">
+        <v>-30.46</v>
       </c>
     </row>
     <row r="9">
@@ -10428,7 +10444,7 @@
       <c r="C9" t="str">
         <v>002261</v>
       </c>
-      <c r="D9" s="95" t="str">
+      <c r="D9" s="103" t="str">
         <v>净卖: -1.12亿</v>
       </c>
       <c r="E9">
@@ -10443,7 +10459,7 @@
       <c r="H9">
         <v>-3.17</v>
       </c>
-      <c r="I9" s="101">
+      <c r="I9" s="94">
         <v>-7.06</v>
       </c>
       <c r="J9" s="96">
@@ -10452,32 +10468,32 @@
       <c r="K9" s="97">
         <v>-11.69</v>
       </c>
-      <c r="L9" s="98">
+      <c r="L9" s="95">
         <v>-10.05</v>
       </c>
-      <c r="M9" s="103">
+      <c r="M9" s="101">
         <v>-11.15</v>
       </c>
-      <c r="N9" s="104">
+      <c r="N9" s="102">
         <v>-12.48</v>
       </c>
-      <c r="O9" s="92">
+      <c r="O9" s="104">
         <v>-11.61</v>
       </c>
-      <c r="P9" s="93">
+      <c r="P9" s="92">
         <v>-10.56</v>
       </c>
-      <c r="Q9" s="102">
+      <c r="Q9" s="98">
         <v>-12.51</v>
       </c>
-      <c r="R9" s="99">
+      <c r="R9" s="93">
         <v>-9.97</v>
       </c>
-      <c r="S9" s="94">
+      <c r="S9" s="99">
         <v>-18.06</v>
       </c>
       <c r="T9" s="100">
-        <v>-3.68</v>
+        <v>-3.66</v>
       </c>
     </row>
     <row r="10">
@@ -10490,7 +10506,7 @@
       <c r="C10" t="str">
         <v>000799</v>
       </c>
-      <c r="D10" s="114" t="str">
+      <c r="D10" s="109" t="str">
         <v>净卖: -41.89万</v>
       </c>
       <c r="E10">
@@ -10505,41 +10521,41 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="108">
+      <c r="I10" s="116">
         <v>10.01</v>
       </c>
-      <c r="J10" s="109">
+      <c r="J10" s="110">
         <v>9.1</v>
       </c>
-      <c r="K10" s="106">
+      <c r="K10" s="117">
         <v>8.38</v>
       </c>
-      <c r="L10" s="112">
+      <c r="L10" s="111">
         <v>7.23</v>
       </c>
-      <c r="M10" s="115">
+      <c r="M10" s="112">
         <v>5.75</v>
       </c>
-      <c r="N10" s="116">
+      <c r="N10" s="105">
         <v>5</v>
       </c>
-      <c r="O10" s="110">
+      <c r="O10" s="113">
         <v>4.96</v>
       </c>
-      <c r="P10" s="107">
+      <c r="P10" s="114">
         <v>6.34</v>
       </c>
-      <c r="Q10" s="111">
+      <c r="Q10" s="106">
         <v>5.62</v>
       </c>
-      <c r="R10" s="117">
+      <c r="R10" s="115">
         <v>4.79</v>
       </c>
-      <c r="S10" s="105">
+      <c r="S10" s="108">
         <v>1.89</v>
       </c>
-      <c r="T10" s="113">
-        <v>-8.59</v>
+      <c r="T10" s="107">
+        <v>-7.72</v>
       </c>
     </row>
     <row r="11">
@@ -10552,7 +10568,7 @@
       <c r="C11" t="str">
         <v>688108</v>
       </c>
-      <c r="D11" s="125" t="str">
+      <c r="D11" s="123" t="str">
         <v>净买: 3339.73万</v>
       </c>
       <c r="E11">
@@ -10567,41 +10583,41 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="129">
+      <c r="I11" s="124">
         <v>14.27</v>
       </c>
-      <c r="J11" s="130">
+      <c r="J11" s="127">
         <v>11.35</v>
       </c>
-      <c r="K11" s="127">
+      <c r="K11" s="125">
         <v>2.7</v>
       </c>
-      <c r="L11" s="121">
+      <c r="L11" s="128">
         <v>-5.73</v>
       </c>
-      <c r="M11" s="118">
+      <c r="M11" s="121">
         <v>-9.92</v>
       </c>
-      <c r="N11" s="122">
+      <c r="N11" s="130">
         <v>-8.04</v>
       </c>
-      <c r="O11" s="126">
+      <c r="O11" s="118">
         <v>-12.4</v>
       </c>
-      <c r="P11" s="128">
+      <c r="P11" s="129">
         <v>-16.72</v>
       </c>
-      <c r="Q11" s="123">
+      <c r="Q11" s="126">
         <v>-12.2</v>
       </c>
       <c r="R11" s="119">
         <v>-8.57</v>
       </c>
-      <c r="S11" s="124">
+      <c r="S11" s="122">
         <v>-6.23</v>
       </c>
       <c r="T11" s="120">
-        <v>-40.94</v>
+        <v>-40.83</v>
       </c>
     </row>
     <row r="12">
@@ -10614,7 +10630,7 @@
       <c r="C12" t="str">
         <v>300222</v>
       </c>
-      <c r="D12" s="142" t="str">
+      <c r="D12" s="139" t="str">
         <v>净卖: -6818.64万</v>
       </c>
       <c r="E12">
@@ -10629,25 +10645,25 @@
       <c r="H12">
         <v>2.15</v>
       </c>
-      <c r="I12" s="143">
+      <c r="I12" s="131">
         <v>16.68</v>
       </c>
-      <c r="J12" s="139">
+      <c r="J12" s="135">
         <v>11.46</v>
       </c>
-      <c r="K12" s="140">
+      <c r="K12" s="142">
         <v>5.46</v>
       </c>
       <c r="L12" s="136">
         <v>3.27</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="132">
         <v>4.13</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="133">
         <v>-1.95</v>
       </c>
-      <c r="O12" s="141">
+      <c r="O12" s="143">
         <v>-3.66</v>
       </c>
       <c r="P12" s="137">
@@ -10656,14 +10672,14 @@
       <c r="Q12" s="138">
         <v>1.56</v>
       </c>
-      <c r="R12" s="133">
+      <c r="R12" s="140">
         <v>-1.56</v>
       </c>
       <c r="S12" s="134">
         <v>-0.78</v>
       </c>
-      <c r="T12" s="135">
-        <v>-12.63</v>
+      <c r="T12" s="141">
+        <v>-12</v>
       </c>
     </row>
     <row r="13">
@@ -10676,7 +10692,7 @@
       <c r="C13" t="str">
         <v>002837</v>
       </c>
-      <c r="D13" s="147" t="str">
+      <c r="D13" s="146" t="str">
         <v>净买: 1.07亿</v>
       </c>
       <c r="E13">
@@ -10691,10 +10707,10 @@
       <c r="H13">
         <v>-3.13</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="147">
         <v>13.56</v>
       </c>
-      <c r="J13" s="153">
+      <c r="J13" s="154">
         <v>14.94</v>
       </c>
       <c r="K13" s="148">
@@ -10706,26 +10722,26 @@
       <c r="M13" s="150">
         <v>5.96</v>
       </c>
-      <c r="N13" s="154">
+      <c r="N13" s="155">
         <v>-2.76</v>
       </c>
-      <c r="O13" s="144">
+      <c r="O13" s="156">
         <v>2.11</v>
       </c>
-      <c r="P13" s="155">
+      <c r="P13" s="144">
         <v>-0.68</v>
       </c>
-      <c r="Q13" s="145">
+      <c r="Q13" s="151">
         <v>-3.52</v>
       </c>
-      <c r="R13" s="151">
+      <c r="R13" s="152">
         <v>3.92</v>
       </c>
-      <c r="S13" s="152">
+      <c r="S13" s="145">
         <v>8.92</v>
       </c>
-      <c r="T13" s="146">
-        <v>59.01</v>
+      <c r="T13" s="153">
+        <v>73.97</v>
       </c>
     </row>
     <row r="14">
@@ -10738,7 +10754,7 @@
       <c r="C14" t="str">
         <v>600521</v>
       </c>
-      <c r="D14" s="165" t="str">
+      <c r="D14" s="168" t="str">
         <v>净买: 2288.75万</v>
       </c>
       <c r="E14">
@@ -10753,41 +10769,41 @@
       <c r="H14">
         <v>-0.63</v>
       </c>
-      <c r="I14" s="167">
+      <c r="I14" s="169">
         <v>-9.43</v>
       </c>
-      <c r="J14" s="168">
+      <c r="J14" s="165">
         <v>-8.27</v>
       </c>
       <c r="K14" s="158">
         <v>-12.18</v>
       </c>
-      <c r="L14" s="169">
+      <c r="L14" s="157">
         <v>-7.04</v>
       </c>
-      <c r="M14" s="166">
+      <c r="M14" s="159">
         <v>-9.99</v>
       </c>
-      <c r="N14" s="159">
+      <c r="N14" s="162">
         <v>-12.07</v>
       </c>
-      <c r="O14" s="162">
+      <c r="O14" s="160">
         <v>-12</v>
       </c>
-      <c r="P14" s="157">
+      <c r="P14" s="166">
         <v>-13.97</v>
       </c>
-      <c r="Q14" s="160">
+      <c r="Q14" s="163">
         <v>-14.46</v>
       </c>
-      <c r="R14" s="163">
+      <c r="R14" s="164">
         <v>-16.47</v>
       </c>
-      <c r="S14" s="164">
+      <c r="S14" s="167">
         <v>-19.15</v>
       </c>
       <c r="T14" s="161">
-        <v>-37.11</v>
+        <v>-38.79</v>
       </c>
     </row>
     <row r="15">
@@ -10800,7 +10816,7 @@
       <c r="C15" t="str">
         <v>600629</v>
       </c>
-      <c r="D15" s="182" t="str">
+      <c r="D15" s="178" t="str">
         <v>净卖: -1267.40万</v>
       </c>
       <c r="E15">
@@ -10815,41 +10831,41 @@
       <c r="H15">
         <v>7.68</v>
       </c>
-      <c r="I15" s="176">
+      <c r="I15" s="179">
         <v>2.16</v>
       </c>
-      <c r="J15" s="177">
+      <c r="J15" s="176">
         <v>12.36</v>
       </c>
-      <c r="K15" s="179">
+      <c r="K15" s="171">
         <v>23.61</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="182">
         <v>18.97</v>
       </c>
-      <c r="M15" s="180">
+      <c r="M15" s="170">
         <v>17.66</v>
       </c>
-      <c r="N15" s="170">
+      <c r="N15" s="180">
         <v>25.9</v>
       </c>
-      <c r="O15" s="171">
+      <c r="O15" s="172">
         <v>25.51</v>
       </c>
-      <c r="P15" s="181">
+      <c r="P15" s="173">
         <v>28.19</v>
       </c>
-      <c r="Q15" s="174">
+      <c r="Q15" s="177">
         <v>28.12</v>
       </c>
-      <c r="R15" s="172">
+      <c r="R15" s="174">
         <v>40.94</v>
       </c>
       <c r="S15" s="175">
         <v>55.07</v>
       </c>
-      <c r="T15" s="178">
-        <v>39.5</v>
+      <c r="T15" s="181">
+        <v>37.8</v>
       </c>
     </row>
     <row r="16">
@@ -10862,7 +10878,7 @@
       <c r="C16" t="str">
         <v>600403</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="192" t="str">
         <v>净买: 1894.16万</v>
       </c>
       <c r="E16">
@@ -10877,41 +10893,41 @@
       <c r="H16">
         <v>-2.81</v>
       </c>
-      <c r="I16" s="195">
+      <c r="I16" s="193">
         <v>9.03</v>
       </c>
-      <c r="J16" s="185">
+      <c r="J16" s="194">
         <v>-1.93</v>
       </c>
-      <c r="K16" s="191">
+      <c r="K16" s="195">
         <v>-0.24</v>
       </c>
-      <c r="L16" s="183">
+      <c r="L16" s="186">
         <v>-0.72</v>
       </c>
-      <c r="M16" s="184">
+      <c r="M16" s="188">
         <v>9.27</v>
       </c>
-      <c r="N16" s="192">
+      <c r="N16" s="183">
         <v>6.74</v>
       </c>
-      <c r="O16" s="193">
+      <c r="O16" s="189">
         <v>10.95</v>
       </c>
-      <c r="P16" s="187">
+      <c r="P16" s="184">
         <v>22.02</v>
       </c>
-      <c r="Q16" s="188">
+      <c r="Q16" s="187">
         <v>34.18</v>
       </c>
-      <c r="R16" s="186">
+      <c r="R16" s="185">
         <v>23.47</v>
       </c>
-      <c r="S16" s="189">
+      <c r="S16" s="190">
         <v>11.07</v>
       </c>
-      <c r="T16" s="190">
-        <v>-31.77</v>
+      <c r="T16" s="191">
+        <v>-30.69</v>
       </c>
     </row>
     <row r="17">
@@ -10924,7 +10940,7 @@
       <c r="C17" t="str">
         <v>600403</v>
       </c>
-      <c r="D17" s="208" t="str">
+      <c r="D17" s="204" t="str">
         <v>净卖: -1651.88万</v>
       </c>
       <c r="E17">
@@ -10939,41 +10955,41 @@
       <c r="H17">
         <v>-7.84</v>
       </c>
-      <c r="I17" s="201">
+      <c r="I17" s="205">
         <v>-2.4</v>
       </c>
-      <c r="J17" s="202">
+      <c r="J17" s="197">
         <v>-0.72</v>
       </c>
-      <c r="K17" s="199">
+      <c r="K17" s="208">
         <v>-1.2</v>
       </c>
-      <c r="L17" s="196">
+      <c r="L17" s="200">
         <v>8.74</v>
       </c>
-      <c r="M17" s="205">
+      <c r="M17" s="201">
         <v>6.23</v>
       </c>
-      <c r="N17" s="206">
+      <c r="N17" s="202">
         <v>10.42</v>
       </c>
-      <c r="O17" s="200">
+      <c r="O17" s="198">
         <v>21.44</v>
       </c>
-      <c r="P17" s="197">
+      <c r="P17" s="199">
         <v>33.53</v>
       </c>
-      <c r="Q17" s="203">
+      <c r="Q17" s="206">
         <v>22.87</v>
       </c>
-      <c r="R17" s="204">
+      <c r="R17" s="207">
         <v>10.54</v>
       </c>
-      <c r="S17" s="207">
+      <c r="S17" s="203">
         <v>-0.48</v>
       </c>
-      <c r="T17" s="198">
-        <v>-32.1</v>
+      <c r="T17" s="196">
+        <v>-31.02</v>
       </c>
     </row>
     <row r="18">
@@ -10986,7 +11002,7 @@
       <c r="C18" t="str">
         <v>000799</v>
       </c>
-      <c r="D18" s="209" t="str">
+      <c r="D18" s="219" t="str">
         <v>净卖: -4574.20万</v>
       </c>
       <c r="E18">
@@ -11001,25 +11017,25 @@
       <c r="H18">
         <v>-0.22</v>
       </c>
-      <c r="I18" s="219">
+      <c r="I18" s="216">
         <v>10.23</v>
       </c>
-      <c r="J18" s="210">
+      <c r="J18" s="220">
         <v>11.19</v>
       </c>
-      <c r="K18" s="218">
+      <c r="K18" s="211">
         <v>9.73</v>
       </c>
-      <c r="L18" s="211">
+      <c r="L18" s="212">
         <v>12.16</v>
       </c>
-      <c r="M18" s="212">
+      <c r="M18" s="217">
         <v>9.55</v>
       </c>
       <c r="N18" s="213">
         <v>8.7</v>
       </c>
-      <c r="O18" s="220">
+      <c r="O18" s="218">
         <v>6.71</v>
       </c>
       <c r="P18" s="214">
@@ -11031,11 +11047,11 @@
       <c r="R18" s="215">
         <v>-2.26</v>
       </c>
-      <c r="S18" s="216">
+      <c r="S18" s="210">
         <v>-4.4</v>
       </c>
-      <c r="T18" s="217">
-        <v>-27.91</v>
+      <c r="T18" s="209">
+        <v>-27.22</v>
       </c>
     </row>
     <row r="19">
@@ -11048,7 +11064,7 @@
       <c r="C19" t="str">
         <v>000069</v>
       </c>
-      <c r="D19" s="228" t="str">
+      <c r="D19" s="225" t="str">
         <v>净卖: -7553.88万</v>
       </c>
       <c r="E19">
@@ -11063,41 +11079,41 @@
       <c r="H19">
         <v>1.88</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="222">
         <v>8.12</v>
       </c>
-      <c r="J19" s="225">
+      <c r="J19" s="226">
         <v>3.69</v>
       </c>
-      <c r="K19" s="226">
+      <c r="K19" s="227">
         <v>4.06</v>
       </c>
-      <c r="L19" s="233">
+      <c r="L19" s="234">
         <v>2.95</v>
       </c>
-      <c r="M19" s="230">
+      <c r="M19" s="228">
         <v>4.8</v>
       </c>
-      <c r="N19" s="231">
+      <c r="N19" s="229">
         <v>0.37</v>
       </c>
-      <c r="O19" s="222">
+      <c r="O19" s="231">
         <v>-2.95</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="232">
         <v>0</v>
       </c>
       <c r="Q19" s="223">
         <v>-1.11</v>
       </c>
-      <c r="R19" s="232">
+      <c r="R19" s="224">
         <v>-1.85</v>
       </c>
-      <c r="S19" s="227">
+      <c r="S19" s="230">
         <v>0</v>
       </c>
-      <c r="T19" s="224">
-        <v>-17.71</v>
+      <c r="T19" s="233">
+        <v>-18.08</v>
       </c>
     </row>
     <row r="20">
@@ -11110,7 +11126,7 @@
       <c r="C20" t="str">
         <v>002709</v>
       </c>
-      <c r="D20" s="242" t="str">
+      <c r="D20" s="239" t="str">
         <v>净买: 1.65亿</v>
       </c>
       <c r="E20">
@@ -11125,41 +11141,41 @@
       <c r="H20">
         <v>1.37</v>
       </c>
-      <c r="I20" s="236">
+      <c r="I20" s="244">
         <v>8.51</v>
       </c>
-      <c r="J20" s="243">
+      <c r="J20" s="235">
         <v>7.15</v>
       </c>
-      <c r="K20" s="244">
+      <c r="K20" s="240">
         <v>9.4</v>
       </c>
-      <c r="L20" s="238">
+      <c r="L20" s="236">
         <v>-1.54</v>
       </c>
-      <c r="M20" s="245">
+      <c r="M20" s="237">
         <v>3.1</v>
       </c>
-      <c r="N20" s="239">
+      <c r="N20" s="241">
         <v>1.91</v>
       </c>
-      <c r="O20" s="237">
+      <c r="O20" s="238">
         <v>-8.25</v>
       </c>
-      <c r="P20" s="235">
+      <c r="P20" s="245">
         <v>-11.49</v>
       </c>
       <c r="Q20" s="246">
         <v>-7.63</v>
       </c>
-      <c r="R20" s="240">
+      <c r="R20" s="247">
         <v>-9.03</v>
       </c>
-      <c r="S20" s="241">
+      <c r="S20" s="242">
         <v>-6.57</v>
       </c>
-      <c r="T20" s="247">
-        <v>12.16</v>
+      <c r="T20" s="243">
+        <v>14.14</v>
       </c>
     </row>
     <row r="21">
@@ -11172,7 +11188,7 @@
       <c r="C21" t="str">
         <v>300497</v>
       </c>
-      <c r="D21" s="255" t="str">
+      <c r="D21" s="256" t="str">
         <v>净买: 4667.27万</v>
       </c>
       <c r="E21">
@@ -11187,40 +11203,40 @@
       <c r="H21">
         <v>3.39</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="257">
         <v>8.46</v>
       </c>
-      <c r="J21" s="256">
+      <c r="J21" s="252">
         <v>-7.74</v>
       </c>
-      <c r="K21" s="248">
+      <c r="K21" s="253">
         <v>-6.92</v>
       </c>
-      <c r="L21" s="254">
+      <c r="L21" s="260">
         <v>-6.67</v>
       </c>
-      <c r="M21" s="257">
+      <c r="M21" s="258">
         <v>-20</v>
       </c>
-      <c r="N21" s="249">
+      <c r="N21" s="259">
         <v>-17.49</v>
       </c>
-      <c r="O21" s="250">
+      <c r="O21" s="248">
         <v>-15.9</v>
       </c>
-      <c r="P21" s="251">
+      <c r="P21" s="250">
         <v>-19.69</v>
       </c>
-      <c r="Q21" s="259">
+      <c r="Q21" s="249">
         <v>-16.56</v>
       </c>
-      <c r="R21" s="252">
+      <c r="R21" s="251">
         <v>-17.03</v>
       </c>
-      <c r="S21" s="258">
+      <c r="S21" s="254">
         <v>-17.59</v>
       </c>
-      <c r="T21" s="260">
+      <c r="T21" s="255">
         <v>-3.38</v>
       </c>
     </row>
@@ -11234,7 +11250,7 @@
       <c r="C22" t="str">
         <v>600343</v>
       </c>
-      <c r="D22" s="263" t="str">
+      <c r="D22" s="270" t="str">
         <v>净卖: -1.50亿</v>
       </c>
       <c r="E22">
@@ -11249,41 +11265,41 @@
       <c r="H22">
         <v>-2.42</v>
       </c>
-      <c r="I22" s="264">
+      <c r="I22" s="267">
         <v>5.68</v>
       </c>
-      <c r="J22" s="269">
+      <c r="J22" s="263">
         <v>9.44</v>
       </c>
-      <c r="K22" s="267">
+      <c r="K22" s="271">
         <v>20.4</v>
       </c>
-      <c r="L22" s="270">
+      <c r="L22" s="264">
         <v>32.45</v>
       </c>
       <c r="M22" s="268">
         <v>25.78</v>
       </c>
-      <c r="N22" s="272">
+      <c r="N22" s="265">
         <v>29.91</v>
       </c>
-      <c r="O22" s="273">
+      <c r="O22" s="269">
         <v>19.51</v>
       </c>
-      <c r="P22" s="265">
+      <c r="P22" s="272">
         <v>20.5</v>
       </c>
-      <c r="Q22" s="261">
+      <c r="Q22" s="273">
         <v>27.5</v>
       </c>
-      <c r="R22" s="266">
+      <c r="R22" s="262">
         <v>22.58</v>
       </c>
-      <c r="S22" s="262">
+      <c r="S22" s="266">
         <v>25.45</v>
       </c>
-      <c r="T22" s="271">
-        <v>17.76</v>
+      <c r="T22" s="261">
+        <v>23.44</v>
       </c>
     </row>
     <row r="23">
@@ -11296,7 +11312,7 @@
       <c r="C23" t="str">
         <v>600151</v>
       </c>
-      <c r="D23" s="283" t="str">
+      <c r="D23" s="275" t="str">
         <v>净买: 9889.49万</v>
       </c>
       <c r="E23">
@@ -11311,41 +11327,41 @@
       <c r="H23">
         <v>3.9</v>
       </c>
-      <c r="I23" s="274">
+      <c r="I23" s="278">
         <v>5.88</v>
       </c>
       <c r="J23" s="284">
         <v>7.37</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="285">
         <v>13.25</v>
       </c>
-      <c r="L23" s="278">
+      <c r="L23" s="281">
         <v>18.63</v>
       </c>
-      <c r="M23" s="282">
+      <c r="M23" s="276">
         <v>18</v>
       </c>
-      <c r="N23" s="285">
+      <c r="N23" s="277">
         <v>11.5</v>
       </c>
-      <c r="O23" s="275">
+      <c r="O23" s="279">
         <v>0.37</v>
       </c>
-      <c r="P23" s="279">
+      <c r="P23" s="282">
         <v>-0.62</v>
       </c>
-      <c r="Q23" s="280">
+      <c r="Q23" s="286">
         <v>2.81</v>
       </c>
-      <c r="R23" s="276">
+      <c r="R23" s="283">
         <v>3.94</v>
       </c>
-      <c r="S23" s="281">
+      <c r="S23" s="280">
         <v>14.31</v>
       </c>
-      <c r="T23" s="286">
-        <v>-8.63</v>
+      <c r="T23" s="274">
+        <v>-6.31</v>
       </c>
     </row>
     <row r="24">
@@ -11358,7 +11374,7 @@
       <c r="C24" t="str">
         <v>603698</v>
       </c>
-      <c r="D24" s="294" t="str">
+      <c r="D24" s="295" t="str">
         <v>净卖: -4244.39万</v>
       </c>
       <c r="E24">
@@ -11373,41 +11389,41 @@
       <c r="H24">
         <v>-5.05</v>
       </c>
-      <c r="I24" s="287">
+      <c r="I24" s="288">
         <v>6.05</v>
       </c>
-      <c r="J24" s="295">
+      <c r="J24" s="293">
         <v>-4.33</v>
       </c>
-      <c r="K24" s="296">
+      <c r="K24" s="294">
         <v>-4.4</v>
       </c>
-      <c r="L24" s="298">
+      <c r="L24" s="296">
         <v>5.17</v>
       </c>
-      <c r="M24" s="288">
+      <c r="M24" s="298">
         <v>7.66</v>
       </c>
-      <c r="N24" s="297">
+      <c r="N24" s="299">
         <v>18.42</v>
       </c>
       <c r="O24" s="289">
         <v>30.25</v>
       </c>
-      <c r="P24" s="292">
+      <c r="P24" s="297">
         <v>43.26</v>
       </c>
       <c r="Q24" s="290">
         <v>50.8</v>
       </c>
-      <c r="R24" s="293">
+      <c r="R24" s="287">
         <v>42.08</v>
       </c>
       <c r="S24" s="291">
         <v>40.89</v>
       </c>
-      <c r="T24" s="299">
-        <v>76.84</v>
+      <c r="T24" s="292">
+        <v>74.96</v>
       </c>
     </row>
     <row r="25">
@@ -11420,7 +11436,7 @@
       <c r="C25" t="str">
         <v>002149</v>
       </c>
-      <c r="D25" s="301" t="str">
+      <c r="D25" s="303" t="str">
         <v>净买: 8459.47万</v>
       </c>
       <c r="E25">
@@ -11435,41 +11451,41 @@
       <c r="H25">
         <v>1.6</v>
       </c>
-      <c r="I25" s="308">
+      <c r="I25" s="300">
         <v>8.27</v>
       </c>
-      <c r="J25" s="309">
+      <c r="J25" s="306">
         <v>19.1</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="307">
         <v>17.78</v>
       </c>
-      <c r="L25" s="303">
+      <c r="L25" s="301">
         <v>22.26</v>
       </c>
-      <c r="M25" s="305">
+      <c r="M25" s="308">
         <v>32.62</v>
       </c>
       <c r="N25" s="304">
         <v>45.88</v>
       </c>
-      <c r="O25" s="310">
+      <c r="O25" s="305">
         <v>47.71</v>
       </c>
-      <c r="P25" s="311">
+      <c r="P25" s="310">
         <v>41.17</v>
       </c>
-      <c r="Q25" s="306">
+      <c r="Q25" s="311">
         <v>35.78</v>
       </c>
-      <c r="R25" s="307">
+      <c r="R25" s="302">
         <v>43.7</v>
       </c>
       <c r="S25" s="312">
         <v>45.34</v>
       </c>
-      <c r="T25" s="300">
-        <v>73.03</v>
+      <c r="T25" s="309">
+        <v>90.34</v>
       </c>
     </row>
     <row r="26">
@@ -11482,7 +11498,7 @@
       <c r="C26" t="str">
         <v>002149</v>
       </c>
-      <c r="D26" s="320" t="str">
+      <c r="D26" s="321" t="str">
         <v>净卖: -9064.32万</v>
       </c>
       <c r="E26">
@@ -11497,41 +11513,41 @@
       <c r="H26">
         <v>2.07</v>
       </c>
-      <c r="I26" s="316">
+      <c r="I26" s="322">
         <v>7.77</v>
       </c>
-      <c r="J26" s="317">
+      <c r="J26" s="316">
         <v>6.57</v>
       </c>
-      <c r="K26" s="324">
+      <c r="K26" s="317">
         <v>10.63</v>
       </c>
-      <c r="L26" s="321">
+      <c r="L26" s="323">
         <v>20</v>
       </c>
-      <c r="M26" s="322">
+      <c r="M26" s="324">
         <v>32</v>
       </c>
-      <c r="N26" s="314">
+      <c r="N26" s="325">
         <v>33.66</v>
       </c>
-      <c r="O26" s="323">
+      <c r="O26" s="313">
         <v>27.74</v>
       </c>
-      <c r="P26" s="315">
+      <c r="P26" s="314">
         <v>22.86</v>
       </c>
-      <c r="Q26" s="318">
+      <c r="Q26" s="320">
         <v>30.03</v>
       </c>
-      <c r="R26" s="319">
+      <c r="R26" s="315">
         <v>31.51</v>
       </c>
-      <c r="S26" s="325">
+      <c r="S26" s="318">
         <v>42.26</v>
       </c>
-      <c r="T26" s="313">
-        <v>56.57</v>
+      <c r="T26" s="319">
+        <v>72.23</v>
       </c>
     </row>
     <row r="27">
@@ -11544,7 +11560,7 @@
       <c r="C27" t="str">
         <v>002149</v>
       </c>
-      <c r="D27" s="334" t="str">
+      <c r="D27" s="330" t="str">
         <v>净买: 7447.80万</v>
       </c>
       <c r="E27">
@@ -11559,41 +11575,41 @@
       <c r="H27">
         <v>0.1</v>
       </c>
-      <c r="I27" s="329">
+      <c r="I27" s="327">
         <v>9.9</v>
       </c>
-      <c r="J27" s="330">
+      <c r="J27" s="334">
         <v>11.27</v>
       </c>
-      <c r="K27" s="331">
+      <c r="K27" s="335">
         <v>6.35</v>
       </c>
-      <c r="L27" s="335">
+      <c r="L27" s="333">
         <v>2.28</v>
       </c>
-      <c r="M27" s="338">
+      <c r="M27" s="328">
         <v>8.25</v>
       </c>
-      <c r="N27" s="332">
+      <c r="N27" s="336">
         <v>9.49</v>
       </c>
-      <c r="O27" s="326">
+      <c r="O27" s="337">
         <v>18.43</v>
       </c>
-      <c r="P27" s="327">
+      <c r="P27" s="338">
         <v>13.87</v>
       </c>
-      <c r="Q27" s="333">
+      <c r="Q27" s="331">
         <v>17.51</v>
       </c>
-      <c r="R27" s="336">
+      <c r="R27" s="332">
         <v>20.31</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="326">
         <v>22.76</v>
       </c>
-      <c r="T27" s="337">
-        <v>30.35</v>
+      <c r="T27" s="329">
+        <v>43.39</v>
       </c>
     </row>
     <row r="28">
@@ -11606,7 +11622,7 @@
       <c r="C28" t="str">
         <v>301005</v>
       </c>
-      <c r="D28" s="346" t="str">
+      <c r="D28" s="345" t="str">
         <v>净买: 8304.02万</v>
       </c>
       <c r="E28">
@@ -11621,41 +11637,41 @@
       <c r="H28">
         <v>5.58</v>
       </c>
-      <c r="I28" s="347">
+      <c r="I28" s="348">
         <v>13.66</v>
       </c>
-      <c r="J28" s="342">
+      <c r="J28" s="339">
         <v>15.41</v>
       </c>
-      <c r="K28" s="343">
+      <c r="K28" s="340">
         <v>34.28</v>
       </c>
-      <c r="L28" s="344">
+      <c r="L28" s="349">
         <v>23.58</v>
       </c>
-      <c r="M28" s="350">
+      <c r="M28" s="346">
         <v>30.8</v>
       </c>
-      <c r="N28" s="351">
+      <c r="N28" s="341">
         <v>27.1</v>
       </c>
-      <c r="O28" s="339">
+      <c r="O28" s="342">
         <v>39.67</v>
       </c>
-      <c r="P28" s="348">
+      <c r="P28" s="350">
         <v>34.97</v>
       </c>
-      <c r="Q28" s="340">
+      <c r="Q28" s="347">
         <v>45.55</v>
       </c>
-      <c r="R28" s="341">
+      <c r="R28" s="351">
         <v>49.76</v>
       </c>
-      <c r="S28" s="349">
+      <c r="S28" s="343">
         <v>66.78</v>
       </c>
-      <c r="T28" s="345">
-        <v>41.52</v>
+      <c r="T28" s="344">
+        <v>50.16</v>
       </c>
     </row>
     <row r="29">
@@ -11668,7 +11684,7 @@
       <c r="C29" t="str">
         <v>300503</v>
       </c>
-      <c r="D29" s="355" t="str">
+      <c r="D29" s="352" t="str">
         <v>净买: 6889.84万</v>
       </c>
       <c r="E29">
@@ -11683,41 +11699,41 @@
       <c r="H29">
         <v>-5.69</v>
       </c>
-      <c r="I29" s="356">
+      <c r="I29" s="357">
         <v>25.74</v>
       </c>
-      <c r="J29" s="360">
+      <c r="J29" s="358">
         <v>25.58</v>
       </c>
-      <c r="K29" s="358">
+      <c r="K29" s="361">
         <v>19.55</v>
       </c>
-      <c r="L29" s="361">
+      <c r="L29" s="353">
         <v>22.01</v>
       </c>
-      <c r="M29" s="357">
+      <c r="M29" s="362">
         <v>17.5</v>
       </c>
-      <c r="N29" s="362">
+      <c r="N29" s="359">
         <v>19.83</v>
       </c>
-      <c r="O29" s="353">
+      <c r="O29" s="354">
         <v>27.93</v>
       </c>
-      <c r="P29" s="363">
+      <c r="P29" s="356">
         <v>36.52</v>
       </c>
-      <c r="Q29" s="364">
+      <c r="Q29" s="355">
         <v>23.97</v>
       </c>
-      <c r="R29" s="352">
+      <c r="R29" s="363">
         <v>21.09</v>
       </c>
-      <c r="S29" s="354">
+      <c r="S29" s="364">
         <v>18.68</v>
       </c>
-      <c r="T29" s="359">
-        <v>16.85</v>
+      <c r="T29" s="360">
+        <v>23.06</v>
       </c>
     </row>
     <row r="30">
@@ -11730,7 +11746,7 @@
       <c r="C30" t="str">
         <v>002565</v>
       </c>
-      <c r="D30" s="376" t="str">
+      <c r="D30" s="369" t="str">
         <v>净卖: -6558.32万</v>
       </c>
       <c r="E30">
@@ -11745,41 +11761,41 @@
       <c r="H30">
         <v>5.73</v>
       </c>
-      <c r="I30" s="368">
+      <c r="I30" s="373">
         <v>-8.62</v>
       </c>
-      <c r="J30" s="369">
+      <c r="J30" s="365">
         <v>-4.85</v>
       </c>
-      <c r="K30" s="370">
+      <c r="K30" s="374">
         <v>0.41</v>
       </c>
-      <c r="L30" s="373">
+      <c r="L30" s="375">
         <v>10.47</v>
       </c>
-      <c r="M30" s="371">
+      <c r="M30" s="366">
         <v>15.07</v>
       </c>
-      <c r="N30" s="365">
+      <c r="N30" s="376">
         <v>18.11</v>
       </c>
-      <c r="O30" s="366">
+      <c r="O30" s="377">
         <v>6.3</v>
       </c>
-      <c r="P30" s="374">
+      <c r="P30" s="370">
         <v>-4.33</v>
       </c>
-      <c r="Q30" s="375">
+      <c r="Q30" s="367">
         <v>-13.88</v>
       </c>
-      <c r="R30" s="372">
+      <c r="R30" s="371">
         <v>-18.73</v>
       </c>
-      <c r="S30" s="367">
+      <c r="S30" s="372">
         <v>-18.16</v>
       </c>
-      <c r="T30" s="377">
-        <v>-2.37</v>
+      <c r="T30" s="368">
+        <v>4.7</v>
       </c>
     </row>
     <row r="31">
@@ -11792,7 +11808,7 @@
       <c r="C31" t="str">
         <v>002151</v>
       </c>
-      <c r="D31" s="385" t="str">
+      <c r="D31" s="389" t="str">
         <v>净买: 7582.89万</v>
       </c>
       <c r="E31">
@@ -11807,41 +11823,41 @@
       <c r="H31">
         <v>9.62</v>
       </c>
-      <c r="I31" s="382">
+      <c r="I31" s="380">
         <v>0.34</v>
       </c>
-      <c r="J31" s="389">
+      <c r="J31" s="384">
         <v>10.38</v>
       </c>
-      <c r="K31" s="379">
+      <c r="K31" s="381">
         <v>15.86</v>
       </c>
-      <c r="L31" s="390">
+      <c r="L31" s="385">
         <v>19.86</v>
       </c>
-      <c r="M31" s="380">
+      <c r="M31" s="390">
         <v>22.13</v>
       </c>
-      <c r="N31" s="378">
+      <c r="N31" s="382">
         <v>34.34</v>
       </c>
       <c r="O31" s="386">
         <v>20.9</v>
       </c>
-      <c r="P31" s="383">
+      <c r="P31" s="387">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="381">
+      <c r="Q31" s="378">
         <v>5.08</v>
       </c>
-      <c r="R31" s="387">
+      <c r="R31" s="379">
         <v>0.26</v>
       </c>
       <c r="S31" s="388">
         <v>-0.74</v>
       </c>
-      <c r="T31" s="384">
-        <v>-22.73</v>
+      <c r="T31" s="383">
+        <v>-19.44</v>
       </c>
     </row>
     <row r="32">
@@ -11869,41 +11885,41 @@
       <c r="H32">
         <v>2.6</v>
       </c>
-      <c r="I32" s="393">
+      <c r="I32" s="396">
         <v>7.2</v>
       </c>
       <c r="J32" s="403">
         <v>17.92</v>
       </c>
-      <c r="K32" s="399">
+      <c r="K32" s="397">
         <v>19.67</v>
       </c>
-      <c r="L32" s="394">
+      <c r="L32" s="392">
         <v>21.47</v>
       </c>
-      <c r="M32" s="395">
+      <c r="M32" s="391">
         <v>33.61</v>
       </c>
-      <c r="N32" s="396">
+      <c r="N32" s="398">
         <v>46.97</v>
       </c>
-      <c r="O32" s="391">
+      <c r="O32" s="399">
         <v>32.27</v>
       </c>
-      <c r="P32" s="392">
+      <c r="P32" s="393">
         <v>19.04</v>
       </c>
-      <c r="Q32" s="397">
+      <c r="Q32" s="394">
         <v>7.15</v>
       </c>
       <c r="R32" s="400">
         <v>9.55</v>
       </c>
-      <c r="S32" s="398">
+      <c r="S32" s="401">
         <v>8.54</v>
       </c>
-      <c r="T32" s="401">
-        <v>-7.31</v>
+      <c r="T32" s="395">
+        <v>1.96</v>
       </c>
     </row>
     <row r="33">
@@ -11916,7 +11932,7 @@
       <c r="C33" t="str">
         <v>603698</v>
       </c>
-      <c r="D33" s="404" t="str">
+      <c r="D33" s="407" t="str">
         <v>净买: 6020.50万</v>
       </c>
       <c r="E33">
@@ -11931,41 +11947,41 @@
       <c r="H33">
         <v>-3.65</v>
       </c>
-      <c r="I33" s="412">
+      <c r="I33" s="408">
         <v>14.16</v>
       </c>
-      <c r="J33" s="406">
+      <c r="J33" s="409">
         <v>8.62</v>
       </c>
-      <c r="K33" s="407">
+      <c r="K33" s="415">
         <v>15.14</v>
       </c>
-      <c r="L33" s="413">
+      <c r="L33" s="410">
         <v>18.92</v>
       </c>
-      <c r="M33" s="405">
+      <c r="M33" s="416">
         <v>30.81</v>
       </c>
-      <c r="N33" s="408">
+      <c r="N33" s="411">
         <v>17.73</v>
       </c>
-      <c r="O33" s="414">
+      <c r="O33" s="404">
         <v>5.95</v>
       </c>
-      <c r="P33" s="415">
+      <c r="P33" s="412">
         <v>3.38</v>
       </c>
-      <c r="Q33" s="409">
+      <c r="Q33" s="413">
         <v>8.46</v>
       </c>
-      <c r="R33" s="410">
+      <c r="R33" s="405">
         <v>3.19</v>
       </c>
-      <c r="S33" s="411">
+      <c r="S33" s="406">
         <v>-2.16</v>
       </c>
-      <c r="T33" s="416">
-        <v>24.84</v>
+      <c r="T33" s="414">
+        <v>23.51</v>
       </c>
     </row>
     <row r="34">
@@ -11978,7 +11994,7 @@
       <c r="C34" t="str">
         <v>002202</v>
       </c>
-      <c r="D34" s="418" t="str">
+      <c r="D34" s="419" t="str">
         <v>净买: 4.15亿</v>
       </c>
       <c r="E34">
@@ -11993,41 +12009,41 @@
       <c r="H34">
         <v>9.99</v>
       </c>
-      <c r="I34" s="428">
+      <c r="I34" s="427">
         <v>0</v>
       </c>
-      <c r="J34" s="429">
+      <c r="J34" s="420">
         <v>9.99</v>
       </c>
-      <c r="K34" s="424">
+      <c r="K34" s="428">
         <v>6.29</v>
       </c>
-      <c r="L34" s="419">
+      <c r="L34" s="429">
         <v>4.51</v>
       </c>
-      <c r="M34" s="417">
+      <c r="M34" s="422">
         <v>-5.95</v>
       </c>
-      <c r="N34" s="420">
+      <c r="N34" s="421">
         <v>-15.34</v>
       </c>
-      <c r="O34" s="426">
+      <c r="O34" s="417">
         <v>-13.27</v>
       </c>
-      <c r="P34" s="425">
+      <c r="P34" s="418">
         <v>-18.41</v>
       </c>
-      <c r="Q34" s="427">
+      <c r="Q34" s="423">
         <v>-20.32</v>
       </c>
-      <c r="R34" s="421">
+      <c r="R34" s="424">
         <v>-15.81</v>
       </c>
-      <c r="S34" s="422">
+      <c r="S34" s="425">
         <v>-7.39</v>
       </c>
-      <c r="T34" s="423">
-        <v>-20.51</v>
+      <c r="T34" s="426">
+        <v>-16.75</v>
       </c>
     </row>
     <row r="35">
@@ -12040,7 +12056,7 @@
       <c r="C35" t="str">
         <v>002202</v>
       </c>
-      <c r="D35" s="442" t="str">
+      <c r="D35" s="431" t="str">
         <v>净买: 3.95亿</v>
       </c>
       <c r="E35">
@@ -12055,41 +12071,41 @@
       <c r="H35">
         <v>6.42</v>
       </c>
-      <c r="I35" s="434">
+      <c r="I35" s="439">
         <v>3.35</v>
       </c>
-      <c r="J35" s="435">
+      <c r="J35" s="438">
         <v>-0.12</v>
       </c>
-      <c r="K35" s="436">
+      <c r="K35" s="440">
         <v>-1.79</v>
       </c>
       <c r="L35" s="441">
         <v>-11.62</v>
       </c>
-      <c r="M35" s="437">
+      <c r="M35" s="432">
         <v>-20.45</v>
       </c>
-      <c r="N35" s="430">
+      <c r="N35" s="433">
         <v>-18.51</v>
       </c>
-      <c r="O35" s="438">
+      <c r="O35" s="434">
         <v>-23.33</v>
       </c>
-      <c r="P35" s="439">
+      <c r="P35" s="435">
         <v>-25.13</v>
       </c>
-      <c r="Q35" s="431">
+      <c r="Q35" s="436">
         <v>-20.89</v>
       </c>
-      <c r="R35" s="432">
+      <c r="R35" s="442">
         <v>-12.97</v>
       </c>
-      <c r="S35" s="440">
+      <c r="S35" s="437">
         <v>-16.45</v>
       </c>
-      <c r="T35" s="433">
-        <v>-25.3</v>
+      <c r="T35" s="430">
+        <v>-21.77</v>
       </c>
     </row>
     <row r="36">
@@ -12102,7 +12118,7 @@
       <c r="C36" t="str">
         <v>000901</v>
       </c>
-      <c r="D36" s="449" t="str">
+      <c r="D36" s="448" t="str">
         <v>净买: 926.43万</v>
       </c>
       <c r="E36">
@@ -12117,41 +12133,41 @@
       <c r="H36">
         <v>1.96</v>
       </c>
-      <c r="I36" s="453">
+      <c r="I36" s="443">
         <v>6.61</v>
       </c>
-      <c r="J36" s="447">
+      <c r="J36" s="450">
         <v>-4.05</v>
       </c>
-      <c r="K36" s="450">
+      <c r="K36" s="447">
         <v>-11.42</v>
       </c>
-      <c r="L36" s="451">
+      <c r="L36" s="444">
         <v>-16.39</v>
       </c>
-      <c r="M36" s="448">
+      <c r="M36" s="451">
         <v>-14.59</v>
       </c>
-      <c r="N36" s="454">
+      <c r="N36" s="452">
         <v>-14.59</v>
       </c>
-      <c r="O36" s="443">
+      <c r="O36" s="453">
         <v>-20.53</v>
       </c>
-      <c r="P36" s="455">
+      <c r="P36" s="445">
         <v>-21.57</v>
       </c>
-      <c r="Q36" s="444">
+      <c r="Q36" s="454">
         <v>-18.98</v>
       </c>
-      <c r="R36" s="445">
+      <c r="R36" s="449">
         <v>-15.35</v>
       </c>
-      <c r="S36" s="452">
+      <c r="S36" s="446">
         <v>-23.06</v>
       </c>
-      <c r="T36" s="446">
-        <v>-29.58</v>
+      <c r="T36" s="455">
+        <v>-27.11</v>
       </c>
     </row>
     <row r="37">
@@ -12164,7 +12180,7 @@
       <c r="C37" t="str">
         <v>600498</v>
       </c>
-      <c r="D37" s="468" t="str">
+      <c r="D37" s="463" t="str">
         <v>净卖: -3.15亿</v>
       </c>
       <c r="E37">
@@ -12179,41 +12195,41 @@
       <c r="H37">
         <v>3.52</v>
       </c>
-      <c r="I37" s="463">
+      <c r="I37" s="464">
         <v>4.32</v>
       </c>
-      <c r="J37" s="456">
+      <c r="J37" s="459">
         <v>-6.12</v>
       </c>
-      <c r="K37" s="457">
+      <c r="K37" s="460">
         <v>-14.95</v>
       </c>
-      <c r="L37" s="460">
+      <c r="L37" s="465">
         <v>-14.32</v>
       </c>
-      <c r="M37" s="466">
+      <c r="M37" s="461">
         <v>-19.2</v>
       </c>
-      <c r="N37" s="458">
+      <c r="N37" s="466">
         <v>-20.25</v>
       </c>
-      <c r="O37" s="464">
+      <c r="O37" s="467">
         <v>-17.13</v>
       </c>
-      <c r="P37" s="461">
+      <c r="P37" s="468">
         <v>-8.85</v>
       </c>
-      <c r="Q37" s="462">
+      <c r="Q37" s="457">
         <v>-12.45</v>
       </c>
-      <c r="R37" s="465">
+      <c r="R37" s="462">
         <v>-13.08</v>
       </c>
-      <c r="S37" s="467">
+      <c r="S37" s="456">
         <v>-11.97</v>
       </c>
-      <c r="T37" s="459">
-        <v>7.39</v>
+      <c r="T37" s="458">
+        <v>15.45</v>
       </c>
     </row>
     <row r="38">
@@ -12226,7 +12242,7 @@
       <c r="C38" t="str">
         <v>002202</v>
       </c>
-      <c r="D38" s="477" t="str">
+      <c r="D38" s="475" t="str">
         <v>净卖: -1.92亿</v>
       </c>
       <c r="E38">
@@ -12241,41 +12257,41 @@
       <c r="H38">
         <v>-8.96</v>
       </c>
-      <c r="I38" s="469">
+      <c r="I38" s="481">
         <v>-1.15</v>
       </c>
-      <c r="J38" s="470">
+      <c r="J38" s="473">
         <v>-11.02</v>
       </c>
-      <c r="K38" s="478">
+      <c r="K38" s="469">
         <v>-8.85</v>
       </c>
-      <c r="L38" s="471">
+      <c r="L38" s="470">
         <v>-14.25</v>
       </c>
-      <c r="M38" s="472">
+      <c r="M38" s="476">
         <v>-16.26</v>
       </c>
-      <c r="N38" s="479">
+      <c r="N38" s="477">
         <v>-11.52</v>
       </c>
-      <c r="O38" s="480">
+      <c r="O38" s="471">
         <v>-2.67</v>
       </c>
-      <c r="P38" s="481">
+      <c r="P38" s="472">
         <v>-6.55</v>
       </c>
-      <c r="Q38" s="473">
+      <c r="Q38" s="474">
         <v>-5.92</v>
       </c>
-      <c r="R38" s="474">
+      <c r="R38" s="478">
         <v>-8.82</v>
       </c>
-      <c r="S38" s="475">
+      <c r="S38" s="479">
         <v>-11.48</v>
       </c>
-      <c r="T38" s="476">
-        <v>-16.45</v>
+      <c r="T38" s="480">
+        <v>-12.5</v>
       </c>
     </row>
     <row r="39">
@@ -12288,7 +12304,7 @@
       <c r="C39" t="str">
         <v>002202</v>
       </c>
-      <c r="D39" s="487" t="str">
+      <c r="D39" s="482" t="str">
         <v>净卖: -1.10亿</v>
       </c>
       <c r="E39">
@@ -12303,41 +12319,41 @@
       <c r="H39">
         <v>-9.99</v>
       </c>
-      <c r="I39" s="488">
+      <c r="I39" s="483">
         <v>0</v>
       </c>
-      <c r="J39" s="489">
+      <c r="J39" s="484">
         <v>2.44</v>
       </c>
-      <c r="K39" s="490">
+      <c r="K39" s="494">
         <v>-3.62</v>
       </c>
-      <c r="L39" s="482">
+      <c r="L39" s="485">
         <v>-5.88</v>
       </c>
-      <c r="M39" s="485">
+      <c r="M39" s="488">
         <v>-0.55</v>
       </c>
-      <c r="N39" s="483">
+      <c r="N39" s="486">
         <v>9.39</v>
       </c>
-      <c r="O39" s="484">
+      <c r="O39" s="489">
         <v>5.03</v>
       </c>
-      <c r="P39" s="493">
+      <c r="P39" s="490">
         <v>5.73</v>
       </c>
       <c r="Q39" s="491">
         <v>2.48</v>
       </c>
-      <c r="R39" s="486">
+      <c r="R39" s="492">
         <v>-0.52</v>
       </c>
-      <c r="S39" s="492">
+      <c r="S39" s="493">
         <v>-3.44</v>
       </c>
-      <c r="T39" s="494">
-        <v>-6.1</v>
+      <c r="T39" s="487">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="40">
@@ -12350,7 +12366,7 @@
       <c r="C40" t="str">
         <v>300118</v>
       </c>
-      <c r="D40" s="498" t="str">
+      <c r="D40" s="503" t="str">
         <v>净买: 1.31亿</v>
       </c>
       <c r="E40">
@@ -12365,10 +12381,10 @@
       <c r="H40">
         <v>15.61</v>
       </c>
-      <c r="I40" s="496">
+      <c r="I40" s="501">
         <v>-6.17</v>
       </c>
-      <c r="J40" s="503">
+      <c r="J40" s="496">
         <v>-4.46</v>
       </c>
       <c r="K40" s="497">
@@ -12377,29 +12393,29 @@
       <c r="L40" s="504">
         <v>-12.25</v>
       </c>
-      <c r="M40" s="499">
+      <c r="M40" s="505">
         <v>-16.96</v>
       </c>
-      <c r="N40" s="507">
+      <c r="N40" s="498">
         <v>-12.92</v>
       </c>
-      <c r="O40" s="505">
+      <c r="O40" s="507">
         <v>-6.46</v>
       </c>
-      <c r="P40" s="500">
+      <c r="P40" s="499">
         <v>0</v>
       </c>
-      <c r="Q40" s="501">
+      <c r="Q40" s="500">
         <v>-3.17</v>
       </c>
-      <c r="R40" s="495">
+      <c r="R40" s="506">
         <v>-6.54</v>
       </c>
-      <c r="S40" s="506">
+      <c r="S40" s="495">
         <v>-4.71</v>
       </c>
       <c r="T40" s="502">
-        <v>-30.75</v>
+        <v>-27.75</v>
       </c>
     </row>
     <row r="41">
@@ -12412,7 +12428,7 @@
       <c r="C41" t="str">
         <v>001337</v>
       </c>
-      <c r="D41" s="512" t="str">
+      <c r="D41" s="516" t="str">
         <v>净买: 4696.53万</v>
       </c>
       <c r="E41">
@@ -12427,41 +12443,41 @@
       <c r="H41">
         <v>5.3</v>
       </c>
-      <c r="I41" s="520">
+      <c r="I41" s="509">
         <v>4.47</v>
       </c>
       <c r="J41" s="513">
         <v>14.89</v>
       </c>
-      <c r="K41" s="517">
+      <c r="K41" s="514">
         <v>3.41</v>
       </c>
-      <c r="L41" s="518">
+      <c r="L41" s="517">
         <v>-6.94</v>
       </c>
-      <c r="M41" s="514">
+      <c r="M41" s="510">
         <v>-12.41</v>
       </c>
-      <c r="N41" s="509">
+      <c r="N41" s="518">
         <v>-20.23</v>
       </c>
-      <c r="O41" s="519">
+      <c r="O41" s="515">
         <v>-28.05</v>
       </c>
-      <c r="P41" s="515">
+      <c r="P41" s="511">
         <v>-27.52</v>
       </c>
-      <c r="Q41" s="516">
+      <c r="Q41" s="519">
         <v>-24</v>
       </c>
-      <c r="R41" s="510">
+      <c r="R41" s="512">
         <v>-27.11</v>
       </c>
-      <c r="S41" s="511">
+      <c r="S41" s="520">
         <v>-26.55</v>
       </c>
       <c r="T41" s="508">
-        <v>-25.28</v>
+        <v>-24.28</v>
       </c>
     </row>
     <row r="42">
@@ -12474,7 +12490,7 @@
       <c r="C42" t="str">
         <v>001337</v>
       </c>
-      <c r="D42" s="532" t="str">
+      <c r="D42" s="526" t="str">
         <v>净卖: -5018.84万</v>
       </c>
       <c r="E42">
@@ -12489,41 +12505,41 @@
       <c r="H42">
         <v>10.01</v>
       </c>
-      <c r="I42" s="533">
+      <c r="I42" s="527">
         <v>-0.03</v>
       </c>
-      <c r="J42" s="530">
+      <c r="J42" s="531">
         <v>-10.02</v>
       </c>
-      <c r="K42" s="525">
+      <c r="K42" s="528">
         <v>-19.02</v>
       </c>
-      <c r="L42" s="521">
+      <c r="L42" s="523">
         <v>-23.78</v>
       </c>
-      <c r="M42" s="522">
+      <c r="M42" s="532">
         <v>-30.59</v>
       </c>
-      <c r="N42" s="526">
+      <c r="N42" s="533">
         <v>-37.39</v>
       </c>
-      <c r="O42" s="528">
+      <c r="O42" s="524">
         <v>-36.93</v>
       </c>
-      <c r="P42" s="523">
+      <c r="P42" s="529">
         <v>-33.87</v>
       </c>
-      <c r="Q42" s="529">
+      <c r="Q42" s="525">
         <v>-36.57</v>
       </c>
-      <c r="R42" s="531">
+      <c r="R42" s="522">
         <v>-36.08</v>
       </c>
-      <c r="S42" s="527">
+      <c r="S42" s="530">
         <v>-36.64</v>
       </c>
-      <c r="T42" s="524">
-        <v>-34.98</v>
+      <c r="T42" s="521">
+        <v>-34.11</v>
       </c>
     </row>
     <row r="43">
@@ -12536,7 +12552,7 @@
       <c r="C43" t="str">
         <v>000995</v>
       </c>
-      <c r="D43" s="541" t="str">
+      <c r="D43" s="542" t="str">
         <v>净买: 1752.24万</v>
       </c>
       <c r="E43">
@@ -12551,41 +12567,41 @@
       <c r="H43">
         <v>10.01</v>
       </c>
-      <c r="I43" s="542">
+      <c r="I43" s="540">
         <v>0</v>
       </c>
       <c r="J43" s="543">
         <v>9.98</v>
       </c>
-      <c r="K43" s="538">
+      <c r="K43" s="544">
         <v>20.97</v>
       </c>
-      <c r="L43" s="534">
+      <c r="L43" s="537">
         <v>19.02</v>
       </c>
-      <c r="M43" s="544">
+      <c r="M43" s="538">
         <v>26.11</v>
       </c>
-      <c r="N43" s="539">
+      <c r="N43" s="545">
         <v>13.5</v>
       </c>
-      <c r="O43" s="546">
+      <c r="O43" s="535">
         <v>18.02</v>
       </c>
-      <c r="P43" s="545">
+      <c r="P43" s="541">
         <v>6.91</v>
       </c>
-      <c r="Q43" s="535">
+      <c r="Q43" s="546">
         <v>4.02</v>
       </c>
-      <c r="R43" s="536">
+      <c r="R43" s="534">
         <v>0.38</v>
       </c>
-      <c r="S43" s="540">
+      <c r="S43" s="536">
         <v>-1.63</v>
       </c>
-      <c r="T43" s="537">
-        <v>-13.68</v>
+      <c r="T43" s="539">
+        <v>-12.74</v>
       </c>
     </row>
     <row r="44">
@@ -12598,7 +12614,7 @@
       <c r="C44" t="str">
         <v>000995</v>
       </c>
-      <c r="D44" s="558" t="str">
+      <c r="D44" s="557" t="str">
         <v>净卖: -1741.06万</v>
       </c>
       <c r="E44">
@@ -12613,41 +12629,41 @@
       <c r="H44">
         <v>-4.33</v>
       </c>
-      <c r="I44" s="549">
+      <c r="I44" s="559">
         <v>14.96</v>
       </c>
-      <c r="J44" s="550">
+      <c r="J44" s="548">
         <v>26.44</v>
       </c>
-      <c r="K44" s="559">
+      <c r="K44" s="549">
         <v>24.41</v>
       </c>
-      <c r="L44" s="555">
+      <c r="L44" s="547">
         <v>31.82</v>
       </c>
-      <c r="M44" s="553">
+      <c r="M44" s="550">
         <v>18.64</v>
       </c>
-      <c r="N44" s="551">
+      <c r="N44" s="555">
         <v>23.36</v>
       </c>
-      <c r="O44" s="547">
+      <c r="O44" s="556">
         <v>11.75</v>
       </c>
-      <c r="P44" s="556">
+      <c r="P44" s="551">
         <v>8.73</v>
       </c>
-      <c r="Q44" s="552">
+      <c r="Q44" s="558">
         <v>4.92</v>
       </c>
-      <c r="R44" s="557">
+      <c r="R44" s="552">
         <v>2.82</v>
       </c>
-      <c r="S44" s="554">
+      <c r="S44" s="553">
         <v>3.87</v>
       </c>
-      <c r="T44" s="548">
-        <v>-9.78</v>
+      <c r="T44" s="554">
+        <v>-8.79</v>
       </c>
     </row>
     <row r="45">
@@ -12660,7 +12676,7 @@
       <c r="C45" t="str">
         <v>301292</v>
       </c>
-      <c r="D45" s="572" t="str">
+      <c r="D45" s="570" t="str">
         <v>净买: 2923.62万</v>
       </c>
       <c r="E45">
@@ -12675,41 +12691,41 @@
       <c r="H45">
         <v>-0.29</v>
       </c>
-      <c r="I45" s="564">
+      <c r="I45" s="571">
         <v>20.35</v>
       </c>
-      <c r="J45" s="565">
+      <c r="J45" s="563">
         <v>23.96</v>
       </c>
-      <c r="K45" s="560">
+      <c r="K45" s="567">
         <v>16.61</v>
       </c>
-      <c r="L45" s="566">
+      <c r="L45" s="564">
         <v>13.75</v>
       </c>
-      <c r="M45" s="561">
+      <c r="M45" s="572">
         <v>10.84</v>
       </c>
-      <c r="N45" s="567">
+      <c r="N45" s="561">
         <v>7.09</v>
       </c>
-      <c r="O45" s="570">
+      <c r="O45" s="568">
         <v>7.44</v>
       </c>
-      <c r="P45" s="562">
+      <c r="P45" s="565">
         <v>2.1</v>
       </c>
-      <c r="Q45" s="568">
+      <c r="Q45" s="562">
         <v>1.76</v>
       </c>
-      <c r="R45" s="571">
+      <c r="R45" s="560">
         <v>6.85</v>
       </c>
-      <c r="S45" s="569">
+      <c r="S45" s="566">
         <v>11.3</v>
       </c>
-      <c r="T45" s="563">
-        <v>15.74</v>
+      <c r="T45" s="569">
+        <v>14.36</v>
       </c>
     </row>
     <row r="46">
@@ -12722,7 +12738,7 @@
       <c r="C46" t="str">
         <v>301396</v>
       </c>
-      <c r="D46" s="575" t="str">
+      <c r="D46" s="573" t="str">
         <v>净买: 9469.00万</v>
       </c>
       <c r="E46">
@@ -12737,13 +12753,15 @@
       <c r="H46">
         <v>2.83</v>
       </c>
-      <c r="I46" s="576">
+      <c r="I46" s="574">
         <v>16.7</v>
       </c>
-      <c r="J46" s="573">
+      <c r="J46" s="575">
         <v>13.98</v>
       </c>
-      <c r="K46" t="str"/>
+      <c r="K46" s="576">
+        <v>16.53</v>
+      </c>
       <c r="L46" t="str"/>
       <c r="M46" t="str"/>
       <c r="N46" t="str"/>
@@ -12752,8 +12770,8 @@
       <c r="Q46" t="str"/>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="574">
-        <v>13.98</v>
+      <c r="T46" s="577">
+        <v>16.53</v>
       </c>
     </row>
     <row r="47">
@@ -12774,7 +12792,7 @@
         <v>45</v>
       </c>
       <c r="K47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="L47">
         <v>44</v>
@@ -12815,41 +12833,41 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="585">
+      <c r="I48" s="582">
         <v>71.11</v>
       </c>
-      <c r="J48" s="579">
+      <c r="J48" s="585">
         <v>64.44</v>
       </c>
-      <c r="K48" s="580">
+      <c r="K48" s="589">
+        <v>60</v>
+      </c>
+      <c r="L48" s="578">
+        <v>56.82</v>
+      </c>
+      <c r="M48" s="579">
+        <v>61.36</v>
+      </c>
+      <c r="N48" s="586">
+        <v>61.36</v>
+      </c>
+      <c r="O48" s="587">
+        <v>56.82</v>
+      </c>
+      <c r="P48" s="583">
+        <v>52.27</v>
+      </c>
+      <c r="Q48" s="584">
         <v>59.09</v>
       </c>
-      <c r="L48" s="586">
-        <v>56.82</v>
-      </c>
-      <c r="M48" s="581">
-        <v>61.36</v>
-      </c>
-      <c r="N48" s="588">
-        <v>61.36</v>
-      </c>
-      <c r="O48" s="582">
-        <v>56.82</v>
-      </c>
-      <c r="P48" s="584">
+      <c r="R48" s="580">
         <v>52.27</v>
       </c>
-      <c r="Q48" s="583">
-        <v>59.09</v>
-      </c>
-      <c r="R48" s="577">
-        <v>52.27</v>
-      </c>
-      <c r="S48" s="578">
+      <c r="S48" s="588">
         <v>43.18</v>
       </c>
-      <c r="T48" s="587">
-        <v>31.11</v>
+      <c r="T48" s="581">
+        <v>35.56</v>
       </c>
     </row>
     <row r="49">
@@ -12863,41 +12881,41 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="589">
+      <c r="I49" s="597">
         <v>5.74</v>
       </c>
-      <c r="J49" s="593">
+      <c r="J49" s="598">
         <v>5.25</v>
       </c>
-      <c r="K49" s="594">
-        <v>4.02</v>
-      </c>
-      <c r="L49" s="595">
+      <c r="K49" s="601">
+        <v>4.3</v>
+      </c>
+      <c r="L49" s="590">
         <v>3.64</v>
       </c>
-      <c r="M49" s="590">
+      <c r="M49" s="591">
         <v>4.36</v>
       </c>
       <c r="N49" s="599">
         <v>5.31</v>
       </c>
-      <c r="O49" s="591">
+      <c r="O49" s="592">
         <v>3.86</v>
       </c>
-      <c r="P49" s="592">
+      <c r="P49" s="593">
         <v>2.82</v>
       </c>
-      <c r="Q49" s="596">
+      <c r="Q49" s="594">
         <v>3.34</v>
       </c>
-      <c r="R49" s="600">
+      <c r="R49" s="595">
         <v>3.21</v>
       </c>
-      <c r="S49" s="598">
+      <c r="S49" s="596">
         <v>3.56</v>
       </c>
-      <c r="T49" s="597">
-        <v>-2.75</v>
+      <c r="T49" s="600">
+        <v>0.24</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/徐晓/index.xlsx
+++ b/youzi/徐晓/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="603">
+  <fills count="604">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -87,18 +87,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -117,13 +105,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -135,13 +171,1231 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFEFEFE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFE15260"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218C3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7A33"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -153,90 +1407,2166 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23963E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF26A142"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6EC381"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4755"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF218C3A"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFEFEFE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
@@ -249,277 +3579,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1E2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC62B39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFEFBFC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -531,199 +3627,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -739,2912 +3649,15 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6DC381"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24973E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDE4150"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1AFB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB7E1C1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7A33"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC62B39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFAE6E8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="602">
+  <borders count="603">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7863,7 +7876,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="602">
+  <cellXfs count="603">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9666,6 +9679,9 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="601" fillId="602" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="602" fillId="603" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -10010,7 +10026,7 @@
       <c r="C2" t="str">
         <v>600120</v>
       </c>
-      <c r="D2" s="11" t="str">
+      <c r="D2" s="9" t="str">
         <v>净卖: -1.33亿</v>
       </c>
       <c r="E2">
@@ -10025,41 +10041,41 @@
       <c r="H2">
         <v>9.97</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="6">
         <v>-12.49</v>
       </c>
-      <c r="J2" s="9">
+      <c r="J2" s="13">
         <v>-21.25</v>
       </c>
       <c r="K2" s="2">
         <v>-22.96</v>
       </c>
-      <c r="L2" s="3">
+      <c r="L2" s="7">
         <v>-26.08</v>
       </c>
-      <c r="M2" s="4">
+      <c r="M2" s="3">
         <v>-20.85</v>
       </c>
-      <c r="N2" s="10">
+      <c r="N2" s="4">
         <v>-20.85</v>
       </c>
       <c r="O2" s="5">
         <v>-22.16</v>
       </c>
-      <c r="P2" s="6">
+      <c r="P2" s="8">
         <v>-26.28</v>
       </c>
-      <c r="Q2" s="7">
+      <c r="Q2" s="10">
         <v>-25.48</v>
       </c>
-      <c r="R2" s="13">
+      <c r="R2" s="11">
         <v>-24.07</v>
       </c>
       <c r="S2" s="1">
         <v>-25.78</v>
       </c>
-      <c r="T2" s="8">
-        <v>-42.4</v>
+      <c r="T2" s="12">
+        <v>-43.61</v>
       </c>
     </row>
     <row r="3">
@@ -10072,7 +10088,7 @@
       <c r="C3" t="str">
         <v>003021</v>
       </c>
-      <c r="D3" s="24" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -3895.40万</v>
       </c>
       <c r="E3">
@@ -10087,41 +10103,41 @@
       <c r="H3">
         <v>-3</v>
       </c>
-      <c r="I3" s="20">
+      <c r="I3" s="26">
         <v>-7.22</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="14">
         <v>-10.22</v>
       </c>
-      <c r="K3" s="18">
+      <c r="K3" s="19">
         <v>-4.57</v>
       </c>
-      <c r="L3" s="16">
+      <c r="L3" s="22">
         <v>-7.52</v>
       </c>
-      <c r="M3" s="21">
+      <c r="M3" s="23">
         <v>-0.02</v>
       </c>
-      <c r="N3" s="17">
+      <c r="N3" s="24">
         <v>4.27</v>
       </c>
-      <c r="O3" s="22">
+      <c r="O3" s="18">
         <v>5.17</v>
       </c>
-      <c r="P3" s="19">
+      <c r="P3" s="20">
         <v>3.7</v>
       </c>
-      <c r="Q3" s="26">
+      <c r="Q3" s="15">
         <v>13.88</v>
       </c>
-      <c r="R3" s="14">
+      <c r="R3" s="16">
         <v>25.27</v>
       </c>
-      <c r="S3" s="23">
+      <c r="S3" s="25">
         <v>24.52</v>
       </c>
-      <c r="T3" s="15">
-        <v>-19.46</v>
+      <c r="T3" s="17">
+        <v>-20.46</v>
       </c>
     </row>
     <row r="4">
@@ -10134,7 +10150,7 @@
       <c r="C4" t="str">
         <v>002896</v>
       </c>
-      <c r="D4" s="35" t="str">
+      <c r="D4" s="34" t="str">
         <v>净买: 5162.35万</v>
       </c>
       <c r="E4">
@@ -10149,41 +10165,41 @@
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="29">
+      <c r="I4" s="38">
         <v>6.79</v>
       </c>
-      <c r="J4" s="38">
+      <c r="J4" s="35">
         <v>17.47</v>
       </c>
-      <c r="K4" s="39">
+      <c r="K4" s="28">
         <v>5.82</v>
       </c>
       <c r="L4" s="36">
         <v>15.69</v>
       </c>
-      <c r="M4" s="32">
+      <c r="M4" s="29">
         <v>27.26</v>
       </c>
-      <c r="N4" s="37">
+      <c r="N4" s="30">
         <v>39.98</v>
       </c>
-      <c r="O4" s="33">
+      <c r="O4" s="37">
         <v>25.98</v>
       </c>
-      <c r="P4" s="27">
+      <c r="P4" s="31">
         <v>13.39</v>
       </c>
-      <c r="Q4" s="34">
+      <c r="Q4" s="32">
         <v>16.45</v>
       </c>
-      <c r="R4" s="30">
+      <c r="R4" s="33">
         <v>19.91</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="39">
         <v>19.53</v>
       </c>
-      <c r="T4" s="31">
-        <v>-12.26</v>
+      <c r="T4" s="27">
+        <v>-12.59</v>
       </c>
     </row>
     <row r="5">
@@ -10196,7 +10212,7 @@
       <c r="C5" t="str">
         <v>600602</v>
       </c>
-      <c r="D5" s="45" t="str">
+      <c r="D5" s="51" t="str">
         <v>净买: 1.03亿</v>
       </c>
       <c r="E5">
@@ -10211,41 +10227,41 @@
       <c r="H5">
         <v>-2.66</v>
       </c>
-      <c r="I5" s="46">
+      <c r="I5" s="47">
         <v>10.77</v>
       </c>
-      <c r="J5" s="47">
+      <c r="J5" s="42">
         <v>5.81</v>
       </c>
-      <c r="K5" s="50">
+      <c r="K5" s="40">
         <v>-3.88</v>
       </c>
-      <c r="L5" s="51">
+      <c r="L5" s="48">
         <v>-13.5</v>
       </c>
-      <c r="M5" s="43">
+      <c r="M5" s="52">
         <v>-15.88</v>
       </c>
-      <c r="N5" s="48">
+      <c r="N5" s="41">
         <v>-14.23</v>
       </c>
-      <c r="O5" s="52">
+      <c r="O5" s="43">
         <v>-8.5</v>
       </c>
-      <c r="P5" s="40">
+      <c r="P5" s="44">
         <v>-5.04</v>
       </c>
-      <c r="Q5" s="41">
+      <c r="Q5" s="49">
         <v>4.46</v>
       </c>
-      <c r="R5" s="42">
+      <c r="R5" s="45">
         <v>6.31</v>
       </c>
-      <c r="S5" s="44">
+      <c r="S5" s="46">
         <v>10.62</v>
       </c>
-      <c r="T5" s="49">
-        <v>-8.77</v>
+      <c r="T5" s="50">
+        <v>-11.46</v>
       </c>
     </row>
     <row r="6">
@@ -10258,7 +10274,7 @@
       <c r="C6" t="str">
         <v>003021</v>
       </c>
-      <c r="D6" s="55" t="str">
+      <c r="D6" s="60" t="str">
         <v>净买: 5581.43万</v>
       </c>
       <c r="E6">
@@ -10273,16 +10289,16 @@
       <c r="H6">
         <v>-1.3</v>
       </c>
-      <c r="I6" s="56">
+      <c r="I6" s="61">
         <v>11.45</v>
       </c>
-      <c r="J6" s="59">
+      <c r="J6" s="57">
         <v>10.79</v>
       </c>
-      <c r="K6" s="60">
+      <c r="K6" s="55">
         <v>-0.29</v>
       </c>
-      <c r="L6" s="53">
+      <c r="L6" s="58">
         <v>-5.12</v>
       </c>
       <c r="M6" s="62">
@@ -10291,23 +10307,23 @@
       <c r="N6" s="54">
         <v>14.73</v>
       </c>
-      <c r="O6" s="63">
+      <c r="O6" s="56">
         <v>13.05</v>
       </c>
-      <c r="P6" s="61">
+      <c r="P6" s="63">
         <v>12.06</v>
       </c>
-      <c r="Q6" s="57">
+      <c r="Q6" s="64">
         <v>13.73</v>
       </c>
-      <c r="R6" s="64">
+      <c r="R6" s="65">
         <v>10.86</v>
       </c>
-      <c r="S6" s="58">
+      <c r="S6" s="53">
         <v>10.2</v>
       </c>
-      <c r="T6" s="65">
-        <v>-28.34</v>
+      <c r="T6" s="59">
+        <v>-29.24</v>
       </c>
     </row>
     <row r="7">
@@ -10320,7 +10336,7 @@
       <c r="C7" t="str">
         <v>002522</v>
       </c>
-      <c r="D7" s="71" t="str">
+      <c r="D7" s="76" t="str">
         <v>净卖: -2406.69万</v>
       </c>
       <c r="E7">
@@ -10335,40 +10351,40 @@
       <c r="H7">
         <v>-5.38</v>
       </c>
-      <c r="I7" s="76">
+      <c r="I7" s="69">
         <v>-4.11</v>
       </c>
-      <c r="J7" s="77">
+      <c r="J7" s="72">
         <v>-13.74</v>
       </c>
-      <c r="K7" s="78">
+      <c r="K7" s="77">
         <v>-21.64</v>
       </c>
-      <c r="L7" s="68">
+      <c r="L7" s="75">
         <v>-19.75</v>
       </c>
-      <c r="M7" s="66">
+      <c r="M7" s="78">
         <v>-18.96</v>
       </c>
-      <c r="N7" s="72">
+      <c r="N7" s="73">
         <v>-16.9</v>
       </c>
-      <c r="O7" s="67">
+      <c r="O7" s="70">
         <v>-18.64</v>
       </c>
-      <c r="P7" s="69">
+      <c r="P7" s="74">
         <v>-16.27</v>
       </c>
-      <c r="Q7" s="70">
+      <c r="Q7" s="71">
         <v>-17.06</v>
       </c>
-      <c r="R7" s="73">
+      <c r="R7" s="66">
         <v>-16.75</v>
       </c>
-      <c r="S7" s="74">
+      <c r="S7" s="67">
         <v>-19.59</v>
       </c>
-      <c r="T7" s="75">
+      <c r="T7" s="68">
         <v>-0.79</v>
       </c>
     </row>
@@ -10382,7 +10398,7 @@
       <c r="C8" t="str">
         <v>003021</v>
       </c>
-      <c r="D8" s="90" t="str">
+      <c r="D8" s="79" t="str">
         <v>净卖: -7322.64万</v>
       </c>
       <c r="E8">
@@ -10397,41 +10413,41 @@
       <c r="H8">
         <v>-1.2</v>
       </c>
-      <c r="I8" s="87">
+      <c r="I8" s="80">
         <v>11.33</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="86">
         <v>9.7</v>
       </c>
-      <c r="K8" s="91">
+      <c r="K8" s="87">
         <v>8.74</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="84">
         <v>10.37</v>
       </c>
-      <c r="M8" s="89">
+      <c r="M8" s="81">
         <v>7.58</v>
       </c>
-      <c r="N8" s="83">
+      <c r="N8" s="82">
         <v>6.94</v>
       </c>
-      <c r="O8" s="79">
+      <c r="O8" s="88">
         <v>-0.96</v>
       </c>
-      <c r="P8" s="80">
+      <c r="P8" s="83">
         <v>1.12</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="89">
         <v>2.48</v>
       </c>
-      <c r="R8" s="81">
+      <c r="R8" s="90">
         <v>-0.05</v>
       </c>
-      <c r="S8" s="85">
+      <c r="S8" s="91">
         <v>-2.14</v>
       </c>
-      <c r="T8" s="86">
-        <v>-30.46</v>
+      <c r="T8" s="85">
+        <v>-31.33</v>
       </c>
     </row>
     <row r="9">
@@ -10444,7 +10460,7 @@
       <c r="C9" t="str">
         <v>002261</v>
       </c>
-      <c r="D9" s="103" t="str">
+      <c r="D9" s="96" t="str">
         <v>净卖: -1.12亿</v>
       </c>
       <c r="E9">
@@ -10459,41 +10475,41 @@
       <c r="H9">
         <v>-3.17</v>
       </c>
-      <c r="I9" s="94">
+      <c r="I9" s="97">
         <v>-7.06</v>
       </c>
-      <c r="J9" s="96">
+      <c r="J9" s="104">
         <v>-13.04</v>
       </c>
-      <c r="K9" s="97">
+      <c r="K9" s="94">
         <v>-11.69</v>
       </c>
-      <c r="L9" s="95">
+      <c r="L9" s="100">
         <v>-10.05</v>
       </c>
-      <c r="M9" s="101">
+      <c r="M9" s="92">
         <v>-11.15</v>
       </c>
-      <c r="N9" s="102">
+      <c r="N9" s="98">
         <v>-12.48</v>
       </c>
-      <c r="O9" s="104">
+      <c r="O9" s="101">
         <v>-11.61</v>
       </c>
-      <c r="P9" s="92">
+      <c r="P9" s="102">
         <v>-10.56</v>
       </c>
-      <c r="Q9" s="98">
+      <c r="Q9" s="103">
         <v>-12.51</v>
       </c>
       <c r="R9" s="93">
         <v>-9.97</v>
       </c>
-      <c r="S9" s="99">
+      <c r="S9" s="95">
         <v>-18.06</v>
       </c>
-      <c r="T9" s="100">
-        <v>-3.66</v>
+      <c r="T9" s="99">
+        <v>-7.54</v>
       </c>
     </row>
     <row r="10">
@@ -10506,7 +10522,7 @@
       <c r="C10" t="str">
         <v>000799</v>
       </c>
-      <c r="D10" s="109" t="str">
+      <c r="D10" s="116" t="str">
         <v>净卖: -41.89万</v>
       </c>
       <c r="E10">
@@ -10521,41 +10537,41 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="113">
         <v>10.01</v>
       </c>
-      <c r="J10" s="110">
+      <c r="J10" s="117">
         <v>9.1</v>
       </c>
-      <c r="K10" s="117">
+      <c r="K10" s="105">
         <v>8.38</v>
       </c>
-      <c r="L10" s="111">
+      <c r="L10" s="106">
         <v>7.23</v>
       </c>
-      <c r="M10" s="112">
+      <c r="M10" s="107">
         <v>5.75</v>
       </c>
-      <c r="N10" s="105">
+      <c r="N10" s="109">
         <v>5</v>
       </c>
-      <c r="O10" s="113">
+      <c r="O10" s="115">
         <v>4.96</v>
       </c>
-      <c r="P10" s="114">
+      <c r="P10" s="110">
         <v>6.34</v>
       </c>
-      <c r="Q10" s="106">
+      <c r="Q10" s="108">
         <v>5.62</v>
       </c>
-      <c r="R10" s="115">
+      <c r="R10" s="114">
         <v>4.79</v>
       </c>
-      <c r="S10" s="108">
+      <c r="S10" s="111">
         <v>1.89</v>
       </c>
-      <c r="T10" s="107">
-        <v>-7.72</v>
+      <c r="T10" s="112">
+        <v>-8.76</v>
       </c>
     </row>
     <row r="11">
@@ -10568,7 +10584,7 @@
       <c r="C11" t="str">
         <v>688108</v>
       </c>
-      <c r="D11" s="123" t="str">
+      <c r="D11" s="128" t="str">
         <v>净买: 3339.73万</v>
       </c>
       <c r="E11">
@@ -10583,41 +10599,41 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="124">
+      <c r="I11" s="126">
         <v>14.27</v>
       </c>
       <c r="J11" s="127">
         <v>11.35</v>
       </c>
-      <c r="K11" s="125">
+      <c r="K11" s="129">
         <v>2.7</v>
       </c>
-      <c r="L11" s="128">
+      <c r="L11" s="121">
         <v>-5.73</v>
       </c>
-      <c r="M11" s="121">
+      <c r="M11" s="123">
         <v>-9.92</v>
       </c>
-      <c r="N11" s="130">
+      <c r="N11" s="124">
         <v>-8.04</v>
       </c>
-      <c r="O11" s="118">
+      <c r="O11" s="130">
         <v>-12.4</v>
       </c>
-      <c r="P11" s="129">
+      <c r="P11" s="118">
         <v>-16.72</v>
       </c>
-      <c r="Q11" s="126">
+      <c r="Q11" s="122">
         <v>-12.2</v>
       </c>
       <c r="R11" s="119">
         <v>-8.57</v>
       </c>
-      <c r="S11" s="122">
+      <c r="S11" s="120">
         <v>-6.23</v>
       </c>
-      <c r="T11" s="120">
-        <v>-40.83</v>
+      <c r="T11" s="125">
+        <v>-41.6</v>
       </c>
     </row>
     <row r="12">
@@ -10630,7 +10646,7 @@
       <c r="C12" t="str">
         <v>300222</v>
       </c>
-      <c r="D12" s="139" t="str">
+      <c r="D12" s="132" t="str">
         <v>净卖: -6818.64万</v>
       </c>
       <c r="E12">
@@ -10645,41 +10661,41 @@
       <c r="H12">
         <v>2.15</v>
       </c>
-      <c r="I12" s="131">
+      <c r="I12" s="138">
         <v>16.68</v>
       </c>
-      <c r="J12" s="135">
+      <c r="J12" s="136">
         <v>11.46</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="143">
         <v>5.46</v>
       </c>
-      <c r="L12" s="136">
+      <c r="L12" s="133">
         <v>3.27</v>
       </c>
-      <c r="M12" s="132">
+      <c r="M12" s="139">
         <v>4.13</v>
       </c>
-      <c r="N12" s="133">
+      <c r="N12" s="134">
         <v>-1.95</v>
       </c>
-      <c r="O12" s="143">
+      <c r="O12" s="131">
         <v>-3.66</v>
       </c>
       <c r="P12" s="137">
         <v>-0.94</v>
       </c>
-      <c r="Q12" s="138">
+      <c r="Q12" s="140">
         <v>1.56</v>
       </c>
-      <c r="R12" s="140">
+      <c r="R12" s="141">
         <v>-1.56</v>
       </c>
-      <c r="S12" s="134">
+      <c r="S12" s="142">
         <v>-0.78</v>
       </c>
-      <c r="T12" s="141">
-        <v>-12</v>
+      <c r="T12" s="135">
+        <v>-13.64</v>
       </c>
     </row>
     <row r="13">
@@ -10692,7 +10708,7 @@
       <c r="C13" t="str">
         <v>002837</v>
       </c>
-      <c r="D13" s="146" t="str">
+      <c r="D13" s="150" t="str">
         <v>净买: 1.07亿</v>
       </c>
       <c r="E13">
@@ -10707,41 +10723,41 @@
       <c r="H13">
         <v>-3.13</v>
       </c>
-      <c r="I13" s="147">
+      <c r="I13" s="151">
         <v>13.56</v>
       </c>
-      <c r="J13" s="154">
+      <c r="J13" s="152">
         <v>14.94</v>
       </c>
-      <c r="K13" s="148">
+      <c r="K13" s="147">
         <v>15.17</v>
       </c>
-      <c r="L13" s="149">
+      <c r="L13" s="144">
         <v>3.66</v>
       </c>
-      <c r="M13" s="150">
+      <c r="M13" s="148">
         <v>5.96</v>
       </c>
-      <c r="N13" s="155">
+      <c r="N13" s="153">
         <v>-2.76</v>
       </c>
-      <c r="O13" s="156">
+      <c r="O13" s="154">
         <v>2.11</v>
       </c>
-      <c r="P13" s="144">
+      <c r="P13" s="145">
         <v>-0.68</v>
       </c>
-      <c r="Q13" s="151">
+      <c r="Q13" s="149">
         <v>-3.52</v>
       </c>
-      <c r="R13" s="152">
+      <c r="R13" s="146">
         <v>3.92</v>
       </c>
-      <c r="S13" s="145">
+      <c r="S13" s="155">
         <v>8.92</v>
       </c>
-      <c r="T13" s="153">
-        <v>73.97</v>
+      <c r="T13" s="156">
+        <v>56.57</v>
       </c>
     </row>
     <row r="14">
@@ -10754,7 +10770,7 @@
       <c r="C14" t="str">
         <v>600521</v>
       </c>
-      <c r="D14" s="168" t="str">
+      <c r="D14" s="169" t="str">
         <v>净买: 2288.75万</v>
       </c>
       <c r="E14">
@@ -10769,41 +10785,41 @@
       <c r="H14">
         <v>-0.63</v>
       </c>
-      <c r="I14" s="169">
+      <c r="I14" s="163">
         <v>-9.43</v>
       </c>
-      <c r="J14" s="165">
+      <c r="J14" s="160">
         <v>-8.27</v>
       </c>
-      <c r="K14" s="158">
+      <c r="K14" s="157">
         <v>-12.18</v>
       </c>
-      <c r="L14" s="157">
+      <c r="L14" s="158">
         <v>-7.04</v>
       </c>
-      <c r="M14" s="159">
+      <c r="M14" s="161">
         <v>-9.99</v>
       </c>
-      <c r="N14" s="162">
+      <c r="N14" s="159">
         <v>-12.07</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="166">
         <v>-12</v>
       </c>
-      <c r="P14" s="166">
+      <c r="P14" s="167">
         <v>-13.97</v>
       </c>
-      <c r="Q14" s="163">
+      <c r="Q14" s="164">
         <v>-14.46</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="168">
         <v>-16.47</v>
       </c>
-      <c r="S14" s="167">
+      <c r="S14" s="165">
         <v>-19.15</v>
       </c>
-      <c r="T14" s="161">
-        <v>-38.79</v>
+      <c r="T14" s="162">
+        <v>-39.46</v>
       </c>
     </row>
     <row r="15">
@@ -10831,41 +10847,41 @@
       <c r="H15">
         <v>7.68</v>
       </c>
-      <c r="I15" s="179">
+      <c r="I15" s="176">
         <v>2.16</v>
       </c>
-      <c r="J15" s="176">
+      <c r="J15" s="172">
         <v>12.36</v>
       </c>
-      <c r="K15" s="171">
+      <c r="K15" s="177">
         <v>23.61</v>
       </c>
-      <c r="L15" s="182">
+      <c r="L15" s="181">
         <v>18.97</v>
       </c>
-      <c r="M15" s="170">
+      <c r="M15" s="173">
         <v>17.66</v>
       </c>
-      <c r="N15" s="180">
+      <c r="N15" s="174">
         <v>25.9</v>
       </c>
-      <c r="O15" s="172">
+      <c r="O15" s="182">
         <v>25.51</v>
       </c>
-      <c r="P15" s="173">
+      <c r="P15" s="175">
         <v>28.19</v>
       </c>
-      <c r="Q15" s="177">
+      <c r="Q15" s="179">
         <v>28.12</v>
       </c>
-      <c r="R15" s="174">
+      <c r="R15" s="170">
         <v>40.94</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="171">
         <v>55.07</v>
       </c>
-      <c r="T15" s="181">
-        <v>37.8</v>
+      <c r="T15" s="180">
+        <v>40.03</v>
       </c>
     </row>
     <row r="16">
@@ -10878,7 +10894,7 @@
       <c r="C16" t="str">
         <v>600403</v>
       </c>
-      <c r="D16" s="192" t="str">
+      <c r="D16" s="183" t="str">
         <v>净买: 1894.16万</v>
       </c>
       <c r="E16">
@@ -10893,41 +10909,41 @@
       <c r="H16">
         <v>-2.81</v>
       </c>
-      <c r="I16" s="193">
+      <c r="I16" s="184">
         <v>9.03</v>
       </c>
-      <c r="J16" s="194">
+      <c r="J16" s="188">
         <v>-1.93</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="190">
         <v>-0.24</v>
       </c>
-      <c r="L16" s="186">
+      <c r="L16" s="194">
         <v>-0.72</v>
       </c>
-      <c r="M16" s="188">
+      <c r="M16" s="185">
         <v>9.27</v>
       </c>
-      <c r="N16" s="183">
+      <c r="N16" s="186">
         <v>6.74</v>
       </c>
-      <c r="O16" s="189">
+      <c r="O16" s="191">
         <v>10.95</v>
       </c>
-      <c r="P16" s="184">
+      <c r="P16" s="195">
         <v>22.02</v>
       </c>
       <c r="Q16" s="187">
         <v>34.18</v>
       </c>
-      <c r="R16" s="185">
+      <c r="R16" s="192">
         <v>23.47</v>
       </c>
-      <c r="S16" s="190">
+      <c r="S16" s="193">
         <v>11.07</v>
       </c>
-      <c r="T16" s="191">
-        <v>-30.69</v>
+      <c r="T16" s="189">
+        <v>-30.08</v>
       </c>
     </row>
     <row r="17">
@@ -10940,7 +10956,7 @@
       <c r="C17" t="str">
         <v>600403</v>
       </c>
-      <c r="D17" s="204" t="str">
+      <c r="D17" s="199" t="str">
         <v>净卖: -1651.88万</v>
       </c>
       <c r="E17">
@@ -10955,41 +10971,41 @@
       <c r="H17">
         <v>-7.84</v>
       </c>
-      <c r="I17" s="205">
+      <c r="I17" s="200">
         <v>-2.4</v>
       </c>
-      <c r="J17" s="197">
+      <c r="J17" s="205">
         <v>-0.72</v>
       </c>
-      <c r="K17" s="208">
+      <c r="K17" s="206">
         <v>-1.2</v>
       </c>
-      <c r="L17" s="200">
+      <c r="L17" s="201">
         <v>8.74</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="202">
         <v>6.23</v>
       </c>
-      <c r="N17" s="202">
+      <c r="N17" s="196">
         <v>10.42</v>
       </c>
-      <c r="O17" s="198">
+      <c r="O17" s="203">
         <v>21.44</v>
       </c>
-      <c r="P17" s="199">
+      <c r="P17" s="207">
         <v>33.53</v>
       </c>
-      <c r="Q17" s="206">
+      <c r="Q17" s="208">
         <v>22.87</v>
       </c>
-      <c r="R17" s="207">
+      <c r="R17" s="198">
         <v>10.54</v>
       </c>
-      <c r="S17" s="203">
+      <c r="S17" s="197">
         <v>-0.48</v>
       </c>
-      <c r="T17" s="196">
-        <v>-31.02</v>
+      <c r="T17" s="204">
+        <v>-30.42</v>
       </c>
     </row>
     <row r="18">
@@ -11002,7 +11018,7 @@
       <c r="C18" t="str">
         <v>000799</v>
       </c>
-      <c r="D18" s="219" t="str">
+      <c r="D18" s="218" t="str">
         <v>净卖: -4574.20万</v>
       </c>
       <c r="E18">
@@ -11020,38 +11036,38 @@
       <c r="I18" s="216">
         <v>10.23</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="214">
         <v>11.19</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="215">
         <v>9.73</v>
       </c>
-      <c r="L18" s="212">
+      <c r="L18" s="209">
         <v>12.16</v>
       </c>
-      <c r="M18" s="217">
+      <c r="M18" s="219">
         <v>9.55</v>
       </c>
-      <c r="N18" s="213">
+      <c r="N18" s="217">
         <v>8.7</v>
       </c>
-      <c r="O18" s="218">
+      <c r="O18" s="220">
         <v>6.71</v>
       </c>
-      <c r="P18" s="214">
+      <c r="P18" s="210">
         <v>4.16</v>
       </c>
-      <c r="Q18" s="221">
+      <c r="Q18" s="211">
         <v>2.68</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="212">
         <v>-2.26</v>
       </c>
-      <c r="S18" s="210">
+      <c r="S18" s="221">
         <v>-4.4</v>
       </c>
-      <c r="T18" s="209">
-        <v>-27.22</v>
+      <c r="T18" s="213">
+        <v>-28.04</v>
       </c>
     </row>
     <row r="19">
@@ -11064,7 +11080,7 @@
       <c r="C19" t="str">
         <v>000069</v>
       </c>
-      <c r="D19" s="225" t="str">
+      <c r="D19" s="231" t="str">
         <v>净卖: -7553.88万</v>
       </c>
       <c r="E19">
@@ -11079,41 +11095,41 @@
       <c r="H19">
         <v>1.88</v>
       </c>
-      <c r="I19" s="222">
+      <c r="I19" s="234">
         <v>8.12</v>
       </c>
-      <c r="J19" s="226">
+      <c r="J19" s="228">
         <v>3.69</v>
       </c>
-      <c r="K19" s="227">
+      <c r="K19" s="224">
         <v>4.06</v>
       </c>
-      <c r="L19" s="234">
+      <c r="L19" s="222">
         <v>2.95</v>
       </c>
-      <c r="M19" s="228">
+      <c r="M19" s="223">
         <v>4.8</v>
       </c>
       <c r="N19" s="229">
         <v>0.37</v>
       </c>
-      <c r="O19" s="231">
+      <c r="O19" s="225">
         <v>-2.95</v>
       </c>
-      <c r="P19" s="232">
+      <c r="P19" s="230">
         <v>0</v>
       </c>
-      <c r="Q19" s="223">
+      <c r="Q19" s="226">
         <v>-1.11</v>
       </c>
-      <c r="R19" s="224">
+      <c r="R19" s="232">
         <v>-1.85</v>
       </c>
-      <c r="S19" s="230">
+      <c r="S19" s="227">
         <v>0</v>
       </c>
       <c r="T19" s="233">
-        <v>-18.08</v>
+        <v>-18.82</v>
       </c>
     </row>
     <row r="20">
@@ -11126,7 +11142,7 @@
       <c r="C20" t="str">
         <v>002709</v>
       </c>
-      <c r="D20" s="239" t="str">
+      <c r="D20" s="247" t="str">
         <v>净买: 1.65亿</v>
       </c>
       <c r="E20">
@@ -11141,41 +11157,41 @@
       <c r="H20">
         <v>1.37</v>
       </c>
-      <c r="I20" s="244">
+      <c r="I20" s="235">
         <v>8.51</v>
       </c>
-      <c r="J20" s="235">
+      <c r="J20" s="243">
         <v>7.15</v>
       </c>
-      <c r="K20" s="240">
+      <c r="K20" s="244">
         <v>9.4</v>
       </c>
-      <c r="L20" s="236">
+      <c r="L20" s="240">
         <v>-1.54</v>
       </c>
-      <c r="M20" s="237">
+      <c r="M20" s="241">
         <v>3.1</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="242">
         <v>1.91</v>
       </c>
-      <c r="O20" s="238">
+      <c r="O20" s="245">
         <v>-8.25</v>
       </c>
-      <c r="P20" s="245">
+      <c r="P20" s="236">
         <v>-11.49</v>
       </c>
-      <c r="Q20" s="246">
+      <c r="Q20" s="237">
         <v>-7.63</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="246">
         <v>-9.03</v>
       </c>
-      <c r="S20" s="242">
+      <c r="S20" s="238">
         <v>-6.57</v>
       </c>
-      <c r="T20" s="243">
-        <v>14.14</v>
+      <c r="T20" s="239">
+        <v>21.36</v>
       </c>
     </row>
     <row r="21">
@@ -11188,7 +11204,7 @@
       <c r="C21" t="str">
         <v>300497</v>
       </c>
-      <c r="D21" s="256" t="str">
+      <c r="D21" s="253" t="str">
         <v>净买: 4667.27万</v>
       </c>
       <c r="E21">
@@ -11203,41 +11219,41 @@
       <c r="H21">
         <v>3.39</v>
       </c>
-      <c r="I21" s="257">
+      <c r="I21" s="258">
         <v>8.46</v>
       </c>
-      <c r="J21" s="252">
+      <c r="J21" s="248">
         <v>-7.74</v>
       </c>
-      <c r="K21" s="253">
+      <c r="K21" s="256">
         <v>-6.92</v>
       </c>
-      <c r="L21" s="260">
+      <c r="L21" s="254">
         <v>-6.67</v>
       </c>
-      <c r="M21" s="258">
+      <c r="M21" s="249">
         <v>-20</v>
       </c>
-      <c r="N21" s="259">
+      <c r="N21" s="255">
         <v>-17.49</v>
       </c>
-      <c r="O21" s="248">
+      <c r="O21" s="250">
         <v>-15.9</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="257">
         <v>-19.69</v>
       </c>
-      <c r="Q21" s="249">
+      <c r="Q21" s="259">
         <v>-16.56</v>
       </c>
       <c r="R21" s="251">
         <v>-17.03</v>
       </c>
-      <c r="S21" s="254">
+      <c r="S21" s="252">
         <v>-17.59</v>
       </c>
-      <c r="T21" s="255">
-        <v>-3.38</v>
+      <c r="T21" s="260">
+        <v>-6.41</v>
       </c>
     </row>
     <row r="22">
@@ -11250,7 +11266,7 @@
       <c r="C22" t="str">
         <v>600343</v>
       </c>
-      <c r="D22" s="270" t="str">
+      <c r="D22" s="265" t="str">
         <v>净卖: -1.50亿</v>
       </c>
       <c r="E22">
@@ -11265,41 +11281,41 @@
       <c r="H22">
         <v>-2.42</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="268">
         <v>5.68</v>
       </c>
-      <c r="J22" s="263">
+      <c r="J22" s="271">
         <v>9.44</v>
       </c>
-      <c r="K22" s="271">
+      <c r="K22" s="266">
         <v>20.4</v>
       </c>
-      <c r="L22" s="264">
+      <c r="L22" s="269">
         <v>32.45</v>
       </c>
-      <c r="M22" s="268">
+      <c r="M22" s="261">
         <v>25.78</v>
       </c>
-      <c r="N22" s="265">
+      <c r="N22" s="262">
         <v>29.91</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="270">
         <v>19.51</v>
       </c>
-      <c r="P22" s="272">
+      <c r="P22" s="263">
         <v>20.5</v>
       </c>
-      <c r="Q22" s="273">
+      <c r="Q22" s="267">
         <v>27.5</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="264">
         <v>22.58</v>
       </c>
-      <c r="S22" s="266">
+      <c r="S22" s="272">
         <v>25.45</v>
       </c>
-      <c r="T22" s="261">
-        <v>23.44</v>
+      <c r="T22" s="273">
+        <v>20.9</v>
       </c>
     </row>
     <row r="23">
@@ -11312,7 +11328,7 @@
       <c r="C23" t="str">
         <v>600151</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="279" t="str">
         <v>净买: 9889.49万</v>
       </c>
       <c r="E23">
@@ -11327,41 +11343,41 @@
       <c r="H23">
         <v>3.9</v>
       </c>
-      <c r="I23" s="278">
+      <c r="I23" s="274">
         <v>5.88</v>
       </c>
-      <c r="J23" s="284">
+      <c r="J23" s="277">
         <v>7.37</v>
       </c>
-      <c r="K23" s="285">
+      <c r="K23" s="280">
         <v>13.25</v>
       </c>
       <c r="L23" s="281">
         <v>18.63</v>
       </c>
-      <c r="M23" s="276">
+      <c r="M23" s="284">
         <v>18</v>
       </c>
-      <c r="N23" s="277">
+      <c r="N23" s="285">
         <v>11.5</v>
       </c>
-      <c r="O23" s="279">
+      <c r="O23" s="275">
         <v>0.37</v>
       </c>
       <c r="P23" s="282">
         <v>-0.62</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="283">
         <v>2.81</v>
       </c>
-      <c r="R23" s="283">
+      <c r="R23" s="276">
         <v>3.94</v>
       </c>
-      <c r="S23" s="280">
+      <c r="S23" s="278">
         <v>14.31</v>
       </c>
-      <c r="T23" s="274">
-        <v>-6.31</v>
+      <c r="T23" s="286">
+        <v>-5.5</v>
       </c>
     </row>
     <row r="24">
@@ -11374,7 +11390,7 @@
       <c r="C24" t="str">
         <v>603698</v>
       </c>
-      <c r="D24" s="295" t="str">
+      <c r="D24" s="294" t="str">
         <v>净卖: -4244.39万</v>
       </c>
       <c r="E24">
@@ -11389,41 +11405,41 @@
       <c r="H24">
         <v>-5.05</v>
       </c>
-      <c r="I24" s="288">
+      <c r="I24" s="290">
         <v>6.05</v>
       </c>
-      <c r="J24" s="293">
+      <c r="J24" s="287">
         <v>-4.33</v>
       </c>
-      <c r="K24" s="294">
+      <c r="K24" s="288">
         <v>-4.4</v>
       </c>
-      <c r="L24" s="296">
+      <c r="L24" s="295">
         <v>5.17</v>
       </c>
-      <c r="M24" s="298">
+      <c r="M24" s="291">
         <v>7.66</v>
       </c>
-      <c r="N24" s="299">
+      <c r="N24" s="296">
         <v>18.42</v>
       </c>
-      <c r="O24" s="289">
+      <c r="O24" s="292">
         <v>30.25</v>
       </c>
-      <c r="P24" s="297">
+      <c r="P24" s="293">
         <v>43.26</v>
       </c>
-      <c r="Q24" s="290">
+      <c r="Q24" s="289">
         <v>50.8</v>
       </c>
-      <c r="R24" s="287">
+      <c r="R24" s="298">
         <v>42.08</v>
       </c>
-      <c r="S24" s="291">
+      <c r="S24" s="297">
         <v>40.89</v>
       </c>
-      <c r="T24" s="292">
-        <v>74.96</v>
+      <c r="T24" s="299">
+        <v>76.91</v>
       </c>
     </row>
     <row r="25">
@@ -11436,7 +11452,7 @@
       <c r="C25" t="str">
         <v>002149</v>
       </c>
-      <c r="D25" s="303" t="str">
+      <c r="D25" s="302" t="str">
         <v>净买: 8459.47万</v>
       </c>
       <c r="E25">
@@ -11451,41 +11467,41 @@
       <c r="H25">
         <v>1.6</v>
       </c>
-      <c r="I25" s="300">
+      <c r="I25" s="303">
         <v>8.27</v>
       </c>
-      <c r="J25" s="306">
+      <c r="J25" s="304">
         <v>19.1</v>
       </c>
-      <c r="K25" s="307">
+      <c r="K25" s="310">
         <v>17.78</v>
       </c>
-      <c r="L25" s="301">
+      <c r="L25" s="311">
         <v>22.26</v>
       </c>
-      <c r="M25" s="308">
+      <c r="M25" s="307">
         <v>32.62</v>
       </c>
-      <c r="N25" s="304">
+      <c r="N25" s="312">
         <v>45.88</v>
       </c>
       <c r="O25" s="305">
         <v>47.71</v>
       </c>
-      <c r="P25" s="310">
+      <c r="P25" s="306">
         <v>41.17</v>
       </c>
-      <c r="Q25" s="311">
+      <c r="Q25" s="300">
         <v>35.78</v>
       </c>
-      <c r="R25" s="302">
+      <c r="R25" s="308">
         <v>43.7</v>
       </c>
-      <c r="S25" s="312">
+      <c r="S25" s="309">
         <v>45.34</v>
       </c>
-      <c r="T25" s="309">
-        <v>90.34</v>
+      <c r="T25" s="301">
+        <v>93.65</v>
       </c>
     </row>
     <row r="26">
@@ -11498,7 +11514,7 @@
       <c r="C26" t="str">
         <v>002149</v>
       </c>
-      <c r="D26" s="321" t="str">
+      <c r="D26" s="315" t="str">
         <v>净卖: -9064.32万</v>
       </c>
       <c r="E26">
@@ -11513,7 +11529,7 @@
       <c r="H26">
         <v>2.07</v>
       </c>
-      <c r="I26" s="322">
+      <c r="I26" s="323">
         <v>7.77</v>
       </c>
       <c r="J26" s="316">
@@ -11522,32 +11538,32 @@
       <c r="K26" s="317">
         <v>10.63</v>
       </c>
-      <c r="L26" s="323">
+      <c r="L26" s="325">
         <v>20</v>
       </c>
-      <c r="M26" s="324">
+      <c r="M26" s="318">
         <v>32</v>
       </c>
-      <c r="N26" s="325">
+      <c r="N26" s="319">
         <v>33.66</v>
       </c>
-      <c r="O26" s="313">
+      <c r="O26" s="320">
         <v>27.74</v>
       </c>
-      <c r="P26" s="314">
+      <c r="P26" s="313">
         <v>22.86</v>
       </c>
-      <c r="Q26" s="320">
+      <c r="Q26" s="321">
         <v>30.03</v>
       </c>
-      <c r="R26" s="315">
+      <c r="R26" s="324">
         <v>31.51</v>
       </c>
-      <c r="S26" s="318">
+      <c r="S26" s="314">
         <v>42.26</v>
       </c>
-      <c r="T26" s="319">
-        <v>72.23</v>
+      <c r="T26" s="322">
+        <v>75.23</v>
       </c>
     </row>
     <row r="27">
@@ -11560,7 +11576,7 @@
       <c r="C27" t="str">
         <v>002149</v>
       </c>
-      <c r="D27" s="330" t="str">
+      <c r="D27" s="328" t="str">
         <v>净买: 7447.80万</v>
       </c>
       <c r="E27">
@@ -11575,41 +11591,41 @@
       <c r="H27">
         <v>0.1</v>
       </c>
-      <c r="I27" s="327">
+      <c r="I27" s="338">
         <v>9.9</v>
       </c>
-      <c r="J27" s="334">
+      <c r="J27" s="326">
         <v>11.27</v>
       </c>
-      <c r="K27" s="335">
+      <c r="K27" s="329">
         <v>6.35</v>
       </c>
-      <c r="L27" s="333">
+      <c r="L27" s="330">
         <v>2.28</v>
       </c>
-      <c r="M27" s="328">
+      <c r="M27" s="331">
         <v>8.25</v>
       </c>
-      <c r="N27" s="336">
+      <c r="N27" s="332">
         <v>9.49</v>
       </c>
-      <c r="O27" s="337">
+      <c r="O27" s="333">
         <v>18.43</v>
       </c>
-      <c r="P27" s="338">
+      <c r="P27" s="335">
         <v>13.87</v>
       </c>
-      <c r="Q27" s="331">
+      <c r="Q27" s="336">
         <v>17.51</v>
       </c>
-      <c r="R27" s="332">
+      <c r="R27" s="337">
         <v>20.31</v>
       </c>
-      <c r="S27" s="326">
+      <c r="S27" s="327">
         <v>22.76</v>
       </c>
-      <c r="T27" s="329">
-        <v>43.39</v>
+      <c r="T27" s="334">
+        <v>45.88</v>
       </c>
     </row>
     <row r="28">
@@ -11622,7 +11638,7 @@
       <c r="C28" t="str">
         <v>301005</v>
       </c>
-      <c r="D28" s="345" t="str">
+      <c r="D28" s="351" t="str">
         <v>净买: 8304.02万</v>
       </c>
       <c r="E28">
@@ -11637,41 +11653,41 @@
       <c r="H28">
         <v>5.58</v>
       </c>
-      <c r="I28" s="348">
+      <c r="I28" s="347">
         <v>13.66</v>
       </c>
-      <c r="J28" s="339">
+      <c r="J28" s="348">
         <v>15.41</v>
       </c>
-      <c r="K28" s="340">
+      <c r="K28" s="339">
         <v>34.28</v>
       </c>
       <c r="L28" s="349">
         <v>23.58</v>
       </c>
-      <c r="M28" s="346">
+      <c r="M28" s="350">
         <v>30.8</v>
       </c>
-      <c r="N28" s="341">
+      <c r="N28" s="343">
         <v>27.1</v>
       </c>
-      <c r="O28" s="342">
+      <c r="O28" s="340">
         <v>39.67</v>
       </c>
-      <c r="P28" s="350">
+      <c r="P28" s="344">
         <v>34.97</v>
       </c>
-      <c r="Q28" s="347">
+      <c r="Q28" s="341">
         <v>45.55</v>
       </c>
-      <c r="R28" s="351">
+      <c r="R28" s="342">
         <v>49.76</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="345">
         <v>66.78</v>
       </c>
-      <c r="T28" s="344">
-        <v>50.16</v>
+      <c r="T28" s="346">
+        <v>51.74</v>
       </c>
     </row>
     <row r="29">
@@ -11684,7 +11700,7 @@
       <c r="C29" t="str">
         <v>300503</v>
       </c>
-      <c r="D29" s="352" t="str">
+      <c r="D29" s="354" t="str">
         <v>净买: 6889.84万</v>
       </c>
       <c r="E29">
@@ -11699,41 +11715,41 @@
       <c r="H29">
         <v>-5.69</v>
       </c>
-      <c r="I29" s="357">
+      <c r="I29" s="355">
         <v>25.74</v>
       </c>
-      <c r="J29" s="358">
+      <c r="J29" s="362">
         <v>25.58</v>
       </c>
-      <c r="K29" s="361">
+      <c r="K29" s="356">
         <v>19.55</v>
       </c>
-      <c r="L29" s="353">
+      <c r="L29" s="357">
         <v>22.01</v>
       </c>
-      <c r="M29" s="362">
+      <c r="M29" s="363">
         <v>17.5</v>
       </c>
-      <c r="N29" s="359">
+      <c r="N29" s="364">
         <v>19.83</v>
       </c>
-      <c r="O29" s="354">
+      <c r="O29" s="352">
         <v>27.93</v>
       </c>
-      <c r="P29" s="356">
+      <c r="P29" s="353">
         <v>36.52</v>
       </c>
-      <c r="Q29" s="355">
+      <c r="Q29" s="358">
         <v>23.97</v>
       </c>
-      <c r="R29" s="363">
+      <c r="R29" s="360">
         <v>21.09</v>
       </c>
-      <c r="S29" s="364">
+      <c r="S29" s="359">
         <v>18.68</v>
       </c>
-      <c r="T29" s="360">
-        <v>23.06</v>
+      <c r="T29" s="361">
+        <v>20.5</v>
       </c>
     </row>
     <row r="30">
@@ -11746,7 +11762,7 @@
       <c r="C30" t="str">
         <v>002565</v>
       </c>
-      <c r="D30" s="369" t="str">
+      <c r="D30" s="370" t="str">
         <v>净卖: -6558.32万</v>
       </c>
       <c r="E30">
@@ -11761,41 +11777,41 @@
       <c r="H30">
         <v>5.73</v>
       </c>
-      <c r="I30" s="373">
+      <c r="I30" s="366">
         <v>-8.62</v>
       </c>
-      <c r="J30" s="365">
+      <c r="J30" s="367">
         <v>-4.85</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="371">
         <v>0.41</v>
       </c>
-      <c r="L30" s="375">
+      <c r="L30" s="372">
         <v>10.47</v>
       </c>
-      <c r="M30" s="366">
+      <c r="M30" s="375">
         <v>15.07</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="368">
         <v>18.11</v>
       </c>
       <c r="O30" s="377">
         <v>6.3</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="376">
         <v>-4.33</v>
       </c>
-      <c r="Q30" s="367">
+      <c r="Q30" s="373">
         <v>-13.88</v>
       </c>
-      <c r="R30" s="371">
+      <c r="R30" s="365">
         <v>-18.73</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="369">
         <v>-18.16</v>
       </c>
-      <c r="T30" s="368">
-        <v>4.7</v>
+      <c r="T30" s="374">
+        <v>15.17</v>
       </c>
     </row>
     <row r="31">
@@ -11808,7 +11824,7 @@
       <c r="C31" t="str">
         <v>002151</v>
       </c>
-      <c r="D31" s="389" t="str">
+      <c r="D31" s="382" t="str">
         <v>净买: 7582.89万</v>
       </c>
       <c r="E31">
@@ -11826,38 +11842,38 @@
       <c r="I31" s="380">
         <v>0.34</v>
       </c>
-      <c r="J31" s="384">
+      <c r="J31" s="386">
         <v>10.38</v>
       </c>
-      <c r="K31" s="381">
+      <c r="K31" s="388">
         <v>15.86</v>
       </c>
-      <c r="L31" s="385">
+      <c r="L31" s="381">
         <v>19.86</v>
       </c>
-      <c r="M31" s="390">
+      <c r="M31" s="389">
         <v>22.13</v>
       </c>
-      <c r="N31" s="382">
+      <c r="N31" s="383">
         <v>34.34</v>
       </c>
-      <c r="O31" s="386">
+      <c r="O31" s="384">
         <v>20.9</v>
       </c>
       <c r="P31" s="387">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="378">
+      <c r="Q31" s="390">
         <v>5.08</v>
       </c>
-      <c r="R31" s="379">
+      <c r="R31" s="378">
         <v>0.26</v>
       </c>
-      <c r="S31" s="388">
+      <c r="S31" s="379">
         <v>-0.74</v>
       </c>
-      <c r="T31" s="383">
-        <v>-19.44</v>
+      <c r="T31" s="385">
+        <v>-20.14</v>
       </c>
     </row>
     <row r="32">
@@ -11870,7 +11886,7 @@
       <c r="C32" t="str">
         <v>601698</v>
       </c>
-      <c r="D32" s="402" t="str">
+      <c r="D32" s="396" t="str">
         <v>净买: 194.55万</v>
       </c>
       <c r="E32">
@@ -11885,41 +11901,41 @@
       <c r="H32">
         <v>2.6</v>
       </c>
-      <c r="I32" s="396">
+      <c r="I32" s="391">
         <v>7.2</v>
       </c>
-      <c r="J32" s="403">
+      <c r="J32" s="397">
         <v>17.92</v>
       </c>
-      <c r="K32" s="397">
+      <c r="K32" s="398">
         <v>19.67</v>
       </c>
-      <c r="L32" s="392">
+      <c r="L32" s="399">
         <v>21.47</v>
       </c>
-      <c r="M32" s="391">
+      <c r="M32" s="401">
         <v>33.61</v>
       </c>
-      <c r="N32" s="398">
+      <c r="N32" s="392">
         <v>46.97</v>
       </c>
-      <c r="O32" s="399">
+      <c r="O32" s="402">
         <v>32.27</v>
       </c>
-      <c r="P32" s="393">
+      <c r="P32" s="400">
         <v>19.04</v>
       </c>
-      <c r="Q32" s="394">
+      <c r="Q32" s="403">
         <v>7.15</v>
       </c>
-      <c r="R32" s="400">
+      <c r="R32" s="393">
         <v>9.55</v>
       </c>
-      <c r="S32" s="401">
+      <c r="S32" s="394">
         <v>8.54</v>
       </c>
       <c r="T32" s="395">
-        <v>1.96</v>
+        <v>4.12</v>
       </c>
     </row>
     <row r="33">
@@ -11932,7 +11948,7 @@
       <c r="C33" t="str">
         <v>603698</v>
       </c>
-      <c r="D33" s="407" t="str">
+      <c r="D33" s="414" t="str">
         <v>净买: 6020.50万</v>
       </c>
       <c r="E33">
@@ -11947,41 +11963,41 @@
       <c r="H33">
         <v>-3.65</v>
       </c>
-      <c r="I33" s="408">
+      <c r="I33" s="415">
         <v>14.16</v>
       </c>
-      <c r="J33" s="409">
+      <c r="J33" s="407">
         <v>8.62</v>
       </c>
-      <c r="K33" s="415">
+      <c r="K33" s="416">
         <v>15.14</v>
       </c>
-      <c r="L33" s="410">
+      <c r="L33" s="409">
         <v>18.92</v>
       </c>
-      <c r="M33" s="416">
+      <c r="M33" s="412">
         <v>30.81</v>
       </c>
-      <c r="N33" s="411">
+      <c r="N33" s="410">
         <v>17.73</v>
       </c>
-      <c r="O33" s="404">
+      <c r="O33" s="408">
         <v>5.95</v>
       </c>
-      <c r="P33" s="412">
+      <c r="P33" s="413">
         <v>3.38</v>
       </c>
-      <c r="Q33" s="413">
+      <c r="Q33" s="404">
         <v>8.46</v>
       </c>
       <c r="R33" s="405">
         <v>3.19</v>
       </c>
-      <c r="S33" s="406">
+      <c r="S33" s="411">
         <v>-2.16</v>
       </c>
-      <c r="T33" s="414">
-        <v>23.51</v>
+      <c r="T33" s="406">
+        <v>24.89</v>
       </c>
     </row>
     <row r="34">
@@ -11994,7 +12010,7 @@
       <c r="C34" t="str">
         <v>002202</v>
       </c>
-      <c r="D34" s="419" t="str">
+      <c r="D34" s="424" t="str">
         <v>净买: 4.15亿</v>
       </c>
       <c r="E34">
@@ -12009,41 +12025,41 @@
       <c r="H34">
         <v>9.99</v>
       </c>
-      <c r="I34" s="427">
+      <c r="I34" s="418">
         <v>0</v>
       </c>
-      <c r="J34" s="420">
+      <c r="J34" s="419">
         <v>9.99</v>
       </c>
-      <c r="K34" s="428">
+      <c r="K34" s="421">
         <v>6.29</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="428">
         <v>4.51</v>
       </c>
-      <c r="M34" s="422">
+      <c r="M34" s="425">
         <v>-5.95</v>
       </c>
-      <c r="N34" s="421">
+      <c r="N34" s="429">
         <v>-15.34</v>
       </c>
-      <c r="O34" s="417">
+      <c r="O34" s="422">
         <v>-13.27</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="426">
         <v>-18.41</v>
       </c>
-      <c r="Q34" s="423">
+      <c r="Q34" s="420">
         <v>-20.32</v>
       </c>
-      <c r="R34" s="424">
+      <c r="R34" s="417">
         <v>-15.81</v>
       </c>
-      <c r="S34" s="425">
+      <c r="S34" s="423">
         <v>-7.39</v>
       </c>
-      <c r="T34" s="426">
-        <v>-16.75</v>
+      <c r="T34" s="427">
+        <v>-18.19</v>
       </c>
     </row>
     <row r="35">
@@ -12071,41 +12087,41 @@
       <c r="H35">
         <v>6.42</v>
       </c>
-      <c r="I35" s="439">
+      <c r="I35" s="432">
         <v>3.35</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="435">
         <v>-0.12</v>
       </c>
-      <c r="K35" s="440">
+      <c r="K35" s="436">
         <v>-1.79</v>
       </c>
-      <c r="L35" s="441">
+      <c r="L35" s="433">
         <v>-11.62</v>
       </c>
-      <c r="M35" s="432">
+      <c r="M35" s="439">
         <v>-20.45</v>
       </c>
-      <c r="N35" s="433">
+      <c r="N35" s="440">
         <v>-18.51</v>
       </c>
-      <c r="O35" s="434">
+      <c r="O35" s="437">
         <v>-23.33</v>
       </c>
-      <c r="P35" s="435">
+      <c r="P35" s="441">
         <v>-25.13</v>
       </c>
-      <c r="Q35" s="436">
+      <c r="Q35" s="438">
         <v>-20.89</v>
       </c>
       <c r="R35" s="442">
         <v>-12.97</v>
       </c>
-      <c r="S35" s="437">
+      <c r="S35" s="430">
         <v>-16.45</v>
       </c>
-      <c r="T35" s="430">
-        <v>-21.77</v>
+      <c r="T35" s="434">
+        <v>-23.12</v>
       </c>
     </row>
     <row r="36">
@@ -12118,7 +12134,7 @@
       <c r="C36" t="str">
         <v>000901</v>
       </c>
-      <c r="D36" s="448" t="str">
+      <c r="D36" s="455" t="str">
         <v>净买: 926.43万</v>
       </c>
       <c r="E36">
@@ -12133,41 +12149,41 @@
       <c r="H36">
         <v>1.96</v>
       </c>
-      <c r="I36" s="443">
+      <c r="I36" s="445">
         <v>6.61</v>
       </c>
-      <c r="J36" s="450">
+      <c r="J36" s="446">
         <v>-4.05</v>
       </c>
-      <c r="K36" s="447">
+      <c r="K36" s="450">
         <v>-11.42</v>
       </c>
-      <c r="L36" s="444">
+      <c r="L36" s="443">
         <v>-16.39</v>
       </c>
-      <c r="M36" s="451">
+      <c r="M36" s="447">
         <v>-14.59</v>
       </c>
-      <c r="N36" s="452">
+      <c r="N36" s="448">
         <v>-14.59</v>
       </c>
-      <c r="O36" s="453">
+      <c r="O36" s="449">
         <v>-20.53</v>
       </c>
-      <c r="P36" s="445">
+      <c r="P36" s="451">
         <v>-21.57</v>
       </c>
-      <c r="Q36" s="454">
+      <c r="Q36" s="444">
         <v>-18.98</v>
       </c>
-      <c r="R36" s="449">
+      <c r="R36" s="453">
         <v>-15.35</v>
       </c>
-      <c r="S36" s="446">
+      <c r="S36" s="452">
         <v>-23.06</v>
       </c>
-      <c r="T36" s="455">
-        <v>-27.11</v>
+      <c r="T36" s="454">
+        <v>-28.21</v>
       </c>
     </row>
     <row r="37">
@@ -12180,7 +12196,7 @@
       <c r="C37" t="str">
         <v>600498</v>
       </c>
-      <c r="D37" s="463" t="str">
+      <c r="D37" s="467" t="str">
         <v>净卖: -3.15亿</v>
       </c>
       <c r="E37">
@@ -12195,41 +12211,41 @@
       <c r="H37">
         <v>3.52</v>
       </c>
-      <c r="I37" s="464">
+      <c r="I37" s="465">
         <v>4.32</v>
       </c>
-      <c r="J37" s="459">
+      <c r="J37" s="468">
         <v>-6.12</v>
       </c>
-      <c r="K37" s="460">
+      <c r="K37" s="464">
         <v>-14.95</v>
       </c>
-      <c r="L37" s="465">
+      <c r="L37" s="462">
         <v>-14.32</v>
       </c>
-      <c r="M37" s="461">
+      <c r="M37" s="463">
         <v>-19.2</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="456">
         <v>-20.25</v>
       </c>
-      <c r="O37" s="467">
+      <c r="O37" s="457">
         <v>-17.13</v>
       </c>
-      <c r="P37" s="468">
+      <c r="P37" s="458">
         <v>-8.85</v>
       </c>
-      <c r="Q37" s="457">
+      <c r="Q37" s="459">
         <v>-12.45</v>
       </c>
-      <c r="R37" s="462">
+      <c r="R37" s="460">
         <v>-13.08</v>
       </c>
-      <c r="S37" s="456">
+      <c r="S37" s="461">
         <v>-11.97</v>
       </c>
-      <c r="T37" s="458">
-        <v>15.45</v>
+      <c r="T37" s="466">
+        <v>15.63</v>
       </c>
     </row>
     <row r="38">
@@ -12242,7 +12258,7 @@
       <c r="C38" t="str">
         <v>002202</v>
       </c>
-      <c r="D38" s="475" t="str">
+      <c r="D38" s="470" t="str">
         <v>净卖: -1.92亿</v>
       </c>
       <c r="E38">
@@ -12257,41 +12273,41 @@
       <c r="H38">
         <v>-8.96</v>
       </c>
-      <c r="I38" s="481">
+      <c r="I38" s="479">
         <v>-1.15</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="471">
         <v>-11.02</v>
       </c>
-      <c r="K38" s="469">
+      <c r="K38" s="480">
         <v>-8.85</v>
       </c>
-      <c r="L38" s="470">
+      <c r="L38" s="472">
         <v>-14.25</v>
       </c>
-      <c r="M38" s="476">
+      <c r="M38" s="481">
         <v>-16.26</v>
       </c>
-      <c r="N38" s="477">
+      <c r="N38" s="473">
         <v>-11.52</v>
       </c>
-      <c r="O38" s="471">
+      <c r="O38" s="469">
         <v>-2.67</v>
       </c>
-      <c r="P38" s="472">
+      <c r="P38" s="477">
         <v>-6.55</v>
       </c>
-      <c r="Q38" s="474">
+      <c r="Q38" s="476">
         <v>-5.92</v>
       </c>
       <c r="R38" s="478">
         <v>-8.82</v>
       </c>
-      <c r="S38" s="479">
+      <c r="S38" s="474">
         <v>-11.48</v>
       </c>
-      <c r="T38" s="480">
-        <v>-12.5</v>
+      <c r="T38" s="475">
+        <v>-14.02</v>
       </c>
     </row>
     <row r="39">
@@ -12304,7 +12320,7 @@
       <c r="C39" t="str">
         <v>002202</v>
       </c>
-      <c r="D39" s="482" t="str">
+      <c r="D39" s="494" t="str">
         <v>净卖: -1.10亿</v>
       </c>
       <c r="E39">
@@ -12319,41 +12335,41 @@
       <c r="H39">
         <v>-9.99</v>
       </c>
-      <c r="I39" s="483">
+      <c r="I39" s="491">
         <v>0</v>
       </c>
-      <c r="J39" s="484">
+      <c r="J39" s="485">
         <v>2.44</v>
       </c>
-      <c r="K39" s="494">
+      <c r="K39" s="492">
         <v>-3.62</v>
       </c>
-      <c r="L39" s="485">
+      <c r="L39" s="484">
         <v>-5.88</v>
       </c>
-      <c r="M39" s="488">
+      <c r="M39" s="486">
         <v>-0.55</v>
       </c>
-      <c r="N39" s="486">
+      <c r="N39" s="493">
         <v>9.39</v>
       </c>
-      <c r="O39" s="489">
+      <c r="O39" s="487">
         <v>5.03</v>
       </c>
-      <c r="P39" s="490">
+      <c r="P39" s="482">
         <v>5.73</v>
       </c>
-      <c r="Q39" s="491">
+      <c r="Q39" s="488">
         <v>2.48</v>
       </c>
-      <c r="R39" s="492">
+      <c r="R39" s="489">
         <v>-0.52</v>
       </c>
-      <c r="S39" s="493">
+      <c r="S39" s="483">
         <v>-3.44</v>
       </c>
-      <c r="T39" s="487">
-        <v>-1.66</v>
+      <c r="T39" s="490">
+        <v>-3.37</v>
       </c>
     </row>
     <row r="40">
@@ -12366,7 +12382,7 @@
       <c r="C40" t="str">
         <v>300118</v>
       </c>
-      <c r="D40" s="503" t="str">
+      <c r="D40" s="495" t="str">
         <v>净买: 1.31亿</v>
       </c>
       <c r="E40">
@@ -12381,7 +12397,7 @@
       <c r="H40">
         <v>15.61</v>
       </c>
-      <c r="I40" s="501">
+      <c r="I40" s="506">
         <v>-6.17</v>
       </c>
       <c r="J40" s="496">
@@ -12390,32 +12406,32 @@
       <c r="K40" s="497">
         <v>-11.42</v>
       </c>
-      <c r="L40" s="504">
+      <c r="L40" s="503">
         <v>-12.25</v>
       </c>
-      <c r="M40" s="505">
+      <c r="M40" s="504">
         <v>-16.96</v>
       </c>
-      <c r="N40" s="498">
+      <c r="N40" s="500">
         <v>-12.92</v>
       </c>
       <c r="O40" s="507">
         <v>-6.46</v>
       </c>
-      <c r="P40" s="499">
+      <c r="P40" s="498">
         <v>0</v>
       </c>
-      <c r="Q40" s="500">
+      <c r="Q40" s="501">
         <v>-3.17</v>
       </c>
-      <c r="R40" s="506">
+      <c r="R40" s="499">
         <v>-6.54</v>
       </c>
-      <c r="S40" s="495">
+      <c r="S40" s="502">
         <v>-4.71</v>
       </c>
-      <c r="T40" s="502">
-        <v>-27.75</v>
+      <c r="T40" s="505">
+        <v>-28.79</v>
       </c>
     </row>
     <row r="41">
@@ -12428,7 +12444,7 @@
       <c r="C41" t="str">
         <v>001337</v>
       </c>
-      <c r="D41" s="516" t="str">
+      <c r="D41" s="511" t="str">
         <v>净买: 4696.53万</v>
       </c>
       <c r="E41">
@@ -12446,38 +12462,38 @@
       <c r="I41" s="509">
         <v>4.47</v>
       </c>
-      <c r="J41" s="513">
+      <c r="J41" s="512">
         <v>14.89</v>
       </c>
-      <c r="K41" s="514">
+      <c r="K41" s="510">
         <v>3.41</v>
       </c>
-      <c r="L41" s="517">
+      <c r="L41" s="516">
         <v>-6.94</v>
       </c>
-      <c r="M41" s="510">
+      <c r="M41" s="513">
         <v>-12.41</v>
       </c>
-      <c r="N41" s="518">
+      <c r="N41" s="519">
         <v>-20.23</v>
       </c>
-      <c r="O41" s="515">
+      <c r="O41" s="517">
         <v>-28.05</v>
       </c>
-      <c r="P41" s="511">
+      <c r="P41" s="514">
         <v>-27.52</v>
       </c>
-      <c r="Q41" s="519">
+      <c r="Q41" s="520">
         <v>-24</v>
       </c>
-      <c r="R41" s="512">
+      <c r="R41" s="518">
         <v>-27.11</v>
       </c>
-      <c r="S41" s="520">
+      <c r="S41" s="515">
         <v>-26.55</v>
       </c>
       <c r="T41" s="508">
-        <v>-24.28</v>
+        <v>-24.14</v>
       </c>
     </row>
     <row r="42">
@@ -12505,41 +12521,41 @@
       <c r="H42">
         <v>10.01</v>
       </c>
-      <c r="I42" s="527">
+      <c r="I42" s="533">
         <v>-0.03</v>
       </c>
-      <c r="J42" s="531">
+      <c r="J42" s="527">
         <v>-10.02</v>
       </c>
-      <c r="K42" s="528">
+      <c r="K42" s="524">
         <v>-19.02</v>
       </c>
-      <c r="L42" s="523">
+      <c r="L42" s="528">
         <v>-23.78</v>
       </c>
-      <c r="M42" s="532">
+      <c r="M42" s="525">
         <v>-30.59</v>
       </c>
-      <c r="N42" s="533">
+      <c r="N42" s="521">
         <v>-37.39</v>
       </c>
-      <c r="O42" s="524">
+      <c r="O42" s="529">
         <v>-36.93</v>
       </c>
-      <c r="P42" s="529">
+      <c r="P42" s="522">
         <v>-33.87</v>
       </c>
-      <c r="Q42" s="525">
+      <c r="Q42" s="523">
         <v>-36.57</v>
       </c>
-      <c r="R42" s="522">
+      <c r="R42" s="531">
         <v>-36.08</v>
       </c>
-      <c r="S42" s="530">
+      <c r="S42" s="532">
         <v>-36.64</v>
       </c>
-      <c r="T42" s="521">
-        <v>-34.11</v>
+      <c r="T42" s="530">
+        <v>-33.99</v>
       </c>
     </row>
     <row r="43">
@@ -12552,7 +12568,7 @@
       <c r="C43" t="str">
         <v>000995</v>
       </c>
-      <c r="D43" s="542" t="str">
+      <c r="D43" s="546" t="str">
         <v>净买: 1752.24万</v>
       </c>
       <c r="E43">
@@ -12567,41 +12583,41 @@
       <c r="H43">
         <v>10.01</v>
       </c>
-      <c r="I43" s="540">
+      <c r="I43" s="542">
         <v>0</v>
       </c>
       <c r="J43" s="543">
         <v>9.98</v>
       </c>
-      <c r="K43" s="544">
+      <c r="K43" s="539">
         <v>20.97</v>
       </c>
-      <c r="L43" s="537">
+      <c r="L43" s="534">
         <v>19.02</v>
       </c>
-      <c r="M43" s="538">
+      <c r="M43" s="535">
         <v>26.11</v>
       </c>
       <c r="N43" s="545">
         <v>13.5</v>
       </c>
-      <c r="O43" s="535">
+      <c r="O43" s="540">
         <v>18.02</v>
       </c>
-      <c r="P43" s="541">
+      <c r="P43" s="536">
         <v>6.91</v>
       </c>
-      <c r="Q43" s="546">
+      <c r="Q43" s="541">
         <v>4.02</v>
       </c>
-      <c r="R43" s="534">
+      <c r="R43" s="537">
         <v>0.38</v>
       </c>
-      <c r="S43" s="536">
+      <c r="S43" s="538">
         <v>-1.63</v>
       </c>
-      <c r="T43" s="539">
-        <v>-12.74</v>
+      <c r="T43" s="544">
+        <v>-13.18</v>
       </c>
     </row>
     <row r="44">
@@ -12614,7 +12630,7 @@
       <c r="C44" t="str">
         <v>000995</v>
       </c>
-      <c r="D44" s="557" t="str">
+      <c r="D44" s="547" t="str">
         <v>净卖: -1741.06万</v>
       </c>
       <c r="E44">
@@ -12629,41 +12645,41 @@
       <c r="H44">
         <v>-4.33</v>
       </c>
-      <c r="I44" s="559">
+      <c r="I44" s="550">
         <v>14.96</v>
       </c>
-      <c r="J44" s="548">
+      <c r="J44" s="556">
         <v>26.44</v>
       </c>
-      <c r="K44" s="549">
+      <c r="K44" s="548">
         <v>24.41</v>
       </c>
-      <c r="L44" s="547">
+      <c r="L44" s="549">
         <v>31.82</v>
       </c>
-      <c r="M44" s="550">
+      <c r="M44" s="551">
         <v>18.64</v>
       </c>
-      <c r="N44" s="555">
+      <c r="N44" s="552">
         <v>23.36</v>
       </c>
-      <c r="O44" s="556">
+      <c r="O44" s="557">
         <v>11.75</v>
       </c>
-      <c r="P44" s="551">
+      <c r="P44" s="558">
         <v>8.73</v>
       </c>
-      <c r="Q44" s="558">
+      <c r="Q44" s="559">
         <v>4.92</v>
       </c>
-      <c r="R44" s="552">
+      <c r="R44" s="553">
         <v>2.82</v>
       </c>
-      <c r="S44" s="553">
+      <c r="S44" s="554">
         <v>3.87</v>
       </c>
-      <c r="T44" s="554">
-        <v>-8.79</v>
+      <c r="T44" s="555">
+        <v>-9.25</v>
       </c>
     </row>
     <row r="45">
@@ -12676,7 +12692,7 @@
       <c r="C45" t="str">
         <v>301292</v>
       </c>
-      <c r="D45" s="570" t="str">
+      <c r="D45" s="569" t="str">
         <v>净买: 2923.62万</v>
       </c>
       <c r="E45">
@@ -12691,41 +12707,41 @@
       <c r="H45">
         <v>-0.29</v>
       </c>
-      <c r="I45" s="571">
+      <c r="I45" s="570">
         <v>20.35</v>
       </c>
-      <c r="J45" s="563">
+      <c r="J45" s="561">
         <v>23.96</v>
       </c>
-      <c r="K45" s="567">
+      <c r="K45" s="571">
         <v>16.61</v>
       </c>
-      <c r="L45" s="564">
+      <c r="L45" s="562">
         <v>13.75</v>
       </c>
-      <c r="M45" s="572">
+      <c r="M45" s="564">
         <v>10.84</v>
       </c>
-      <c r="N45" s="561">
+      <c r="N45" s="572">
         <v>7.09</v>
       </c>
-      <c r="O45" s="568">
+      <c r="O45" s="563">
         <v>7.44</v>
       </c>
-      <c r="P45" s="565">
+      <c r="P45" s="567">
         <v>2.1</v>
       </c>
-      <c r="Q45" s="562">
+      <c r="Q45" s="568">
         <v>1.76</v>
       </c>
-      <c r="R45" s="560">
+      <c r="R45" s="565">
         <v>6.85</v>
       </c>
       <c r="S45" s="566">
         <v>11.3</v>
       </c>
-      <c r="T45" s="569">
-        <v>14.36</v>
+      <c r="T45" s="560">
+        <v>22.42</v>
       </c>
     </row>
     <row r="46">
@@ -12738,7 +12754,7 @@
       <c r="C46" t="str">
         <v>301396</v>
       </c>
-      <c r="D46" s="573" t="str">
+      <c r="D46" s="578" t="str">
         <v>净买: 9469.00万</v>
       </c>
       <c r="E46">
@@ -12753,16 +12769,18 @@
       <c r="H46">
         <v>2.83</v>
       </c>
-      <c r="I46" s="574">
+      <c r="I46" s="573">
         <v>16.7</v>
       </c>
-      <c r="J46" s="575">
+      <c r="J46" s="574">
         <v>13.98</v>
       </c>
-      <c r="K46" s="576">
+      <c r="K46" s="575">
         <v>16.53</v>
       </c>
-      <c r="L46" t="str"/>
+      <c r="L46" s="576">
+        <v>12.63</v>
+      </c>
       <c r="M46" t="str"/>
       <c r="N46" t="str"/>
       <c r="O46" t="str"/>
@@ -12771,7 +12789,7 @@
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
       <c r="T46" s="577">
-        <v>16.53</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="47">
@@ -12795,7 +12813,7 @@
         <v>45</v>
       </c>
       <c r="L47">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="M47">
         <v>44</v>
@@ -12833,40 +12851,40 @@
       <c r="F48" t="str"/>
       <c r="G48" t="str"/>
       <c r="H48" t="str"/>
-      <c r="I48" s="582">
+      <c r="I48" s="589">
         <v>71.11</v>
       </c>
-      <c r="J48" s="585">
+      <c r="J48" s="584">
         <v>64.44</v>
       </c>
-      <c r="K48" s="589">
+      <c r="K48" s="590">
         <v>60</v>
       </c>
-      <c r="L48" s="578">
-        <v>56.82</v>
-      </c>
-      <c r="M48" s="579">
+      <c r="L48" s="582">
+        <v>57.78</v>
+      </c>
+      <c r="M48" s="583">
         <v>61.36</v>
       </c>
-      <c r="N48" s="586">
+      <c r="N48" s="579">
         <v>61.36</v>
       </c>
       <c r="O48" s="587">
         <v>56.82</v>
       </c>
-      <c r="P48" s="583">
+      <c r="P48" s="580">
         <v>52.27</v>
       </c>
-      <c r="Q48" s="584">
+      <c r="Q48" s="585">
         <v>59.09</v>
       </c>
-      <c r="R48" s="580">
+      <c r="R48" s="581">
         <v>52.27</v>
       </c>
-      <c r="S48" s="588">
+      <c r="S48" s="586">
         <v>43.18</v>
       </c>
-      <c r="T48" s="581">
+      <c r="T48" s="588">
         <v>35.56</v>
       </c>
     </row>
@@ -12881,41 +12899,41 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="597">
+      <c r="I49" s="596">
         <v>5.74</v>
       </c>
-      <c r="J49" s="598">
+      <c r="J49" s="592">
         <v>5.25</v>
       </c>
-      <c r="K49" s="601">
+      <c r="K49" s="600">
         <v>4.3</v>
       </c>
-      <c r="L49" s="590">
-        <v>3.64</v>
-      </c>
-      <c r="M49" s="591">
+      <c r="L49" s="593">
+        <v>3.84</v>
+      </c>
+      <c r="M49" s="597">
         <v>4.36</v>
       </c>
-      <c r="N49" s="599">
+      <c r="N49" s="601">
         <v>5.31</v>
       </c>
-      <c r="O49" s="592">
+      <c r="O49" s="598">
         <v>3.86</v>
       </c>
-      <c r="P49" s="593">
+      <c r="P49" s="594">
         <v>2.82</v>
       </c>
-      <c r="Q49" s="594">
+      <c r="Q49" s="602">
         <v>3.34</v>
       </c>
-      <c r="R49" s="595">
+      <c r="R49" s="599">
         <v>3.21</v>
       </c>
-      <c r="S49" s="596">
+      <c r="S49" s="591">
         <v>3.56</v>
       </c>
-      <c r="T49" s="600">
-        <v>0.24</v>
+      <c r="T49" s="595">
+        <v>0.03</v>
       </c>
     </row>
   </sheetData>

--- a/youzi/徐晓/index.xlsx
+++ b/youzi/徐晓/index.xlsx
@@ -24,7 +24,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="610">
+  <fills count="613">
     <fill>
       <patternFill patternType="none">
         <fgColor/>
@@ -81,43 +81,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3AAE54"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208939"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15260"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -129,6 +153,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF28A745"/>
         <bgColor/>
       </patternFill>
@@ -141,61 +171,91 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFEFEFE"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDA3444"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF3AAE54"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208939"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15260"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD33140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -207,85 +267,445 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A59"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF58BA6E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD33140"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7D34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A644"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0515F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F9F4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF27A544"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFDC3545"/>
         <bgColor/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A59"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7D34"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208839"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF4EB666"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD5EEDB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D9AF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAA1E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02837"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC72B3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43140"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD53241"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B2B8"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB0212E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB82432"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -297,19 +717,1531 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD33140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A644"/>
+        <fgColor rgb="FFDC3646"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A38"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259E41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8337"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24983F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC919A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFABDCB6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD73242"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87A85"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF61BE76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDF1E1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD6EEDC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25865"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4BFC4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBBE3C4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE1F3E5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3606D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56B76"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF67C17C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF88CE98"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0A9B0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8035"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A7230"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF218E3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA7AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAE202D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF4FAF6"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFACDDB7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB1212F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0F2E4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCBE9D2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2F3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF97D4A5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEAF6ED"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42330"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB42331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEC929B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA91E2B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE15664"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF9DD7AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDD3D4C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCFEBD5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAFDEBA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBA2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE56975"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25A67"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF80CB91"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEA8791"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208738"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1B7732"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE9818B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF1B1B7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1E8036"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F8638"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBCE3C5"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22933D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCF0F1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4F4E7"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD23040"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22938"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE35F6C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBF2836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDA3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF41B15B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBE2736"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCB2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAC1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCD2E3D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEFA2AA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB92533"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA81D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF44B25D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2EA94A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEEEF"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -339,67 +2271,85 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF58BA6E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF27A544"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0515F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F9F4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
+        <fgColor rgb="FF89CE99"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1D7C34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDFF1E3"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2222F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDF4F5"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -411,73 +2361,421 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4EB666"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF69C17D"/>
+        <fgColor rgb="FFFCF1F2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAB1F2C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC42A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB62431"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF49B461"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE87E88"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77681"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC92C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB72432"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA2D8AE"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB52331"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD1303F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF208A3A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCE2E3E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4857"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259B40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB2DFBC"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77782"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF9FCFA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCA2D3C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF50B768"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -501,13 +2799,493 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC02837"/>
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0505E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF8CD09B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7933"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCDEAD4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF63BF78"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF259C40"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFAD1F2D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F5EB"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF269F41"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDB3444"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD43141"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9CA4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6BC27F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE7F5EA"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFED9AA2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3FB059"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23953E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF23943D"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF24993F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF76C789"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF34AC4F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF22903C"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDF4A58"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE77580"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF28A745"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFEFD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE25C69"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFCEFF0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -519,25 +3297,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA2D9AF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAA1E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFB8E2C2"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3626F"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -549,7 +3327,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFD5EEDB"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -561,145 +3345,289 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA6DAB2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A38"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43140"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B2B8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3847"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFEB8D96"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC52A39"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC22937"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0AAB0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC82C3B"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2B7BD"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF6CCD0"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC02836"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF7D1D4"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3BBC1"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF6CC280"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFD02F3F"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDC3545"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE3616E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1C7B34"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -711,253 +3639,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3646"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD53241"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB0212E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8337"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC919A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259E41"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24983F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25865"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFABDCB6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4BFC4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF61BE76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBBE3C4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD6EEDC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDF1E1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD73242"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87A85"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF88CE98"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56B76"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0A9B0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE1F3E5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF67C17C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3606D"/>
+        <fgColor rgb="FF196C2E"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -975,2689 +3681,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8035"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218E3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1A7230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA7AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAE202D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB1212F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFACDDB7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF4FAF6"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF97D4A5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0F2E4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2F3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEAF6ED"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCBE9D2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE15664"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA91E2B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEC929B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC92C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF9DD7AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAFDEBA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDD3D4C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25A67"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEA8791"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF80CB91"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCFEBD5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBA2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE56975"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBCE3C5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE9818B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF1B1B7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208738"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8036"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1B7732"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF6CDD1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22933D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1F8638"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD23040"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE35F6C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF0F1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE4F4E7"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF41B15B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDA3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBF2836"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBE2736"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCB2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA81D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEFA2AA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB92533"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCD2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAC1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF4BB563"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1D7C34"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2EA94A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF44B25D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEEEF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDFF1E3"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCF1F2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDF4F5"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBEBEC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAB1F2C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB62431"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB32230"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77681"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA2D8AE"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE87E88"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD1303F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB52331"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB72432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF208A3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259B40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCE2E3E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4857"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77782"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF9FCFA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2DFBC"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCA2D3C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF50B768"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0505E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF8CD09B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCDEAD4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1C7933"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFAD1F2D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDB3444"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD43141"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9AA2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6BC27F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF63BF78"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8F5EB"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFADDDB8"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFED9CA4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF259C40"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE7F5EA"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23943D"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF24993F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF23953E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF34AC4F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF3FB059"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF76C789"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4A58"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE77580"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF22903C"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFDFEFD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC72B3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE25C69"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFFF"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFCEFF0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB8E2C2"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3847"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB42330"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFEB8D96"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF196C2E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3626F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF28A745"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2B7BD"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC32938"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC82C3B"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC52A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC22937"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF0AAB0"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC42A39"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDC3545"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDF4755"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF7D1D4"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFD02F3F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF3BBC1"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF218C3A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE3616E"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF6CC280"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB82432"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFB2222F"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF1E8236"/>
+        <fgColor rgb="FFA71D2A"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFBB2634"/>
+        <bgColor/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA71D2A"/>
         <bgColor/>
       </patternFill>
     </fill>
@@ -3667,26 +3703,29 @@
         <bgColor/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA71D2A"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFBB2634"/>
-        <bgColor/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="609">
+  <borders count="612">
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
     <border>
       <left/>
       <right/>
@@ -7954,7 +7993,7 @@
   <cellStyleXfs count="1">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0"/>
   </cellStyleXfs>
-  <cellXfs count="609">
+  <cellXfs count="612">
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0"/>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="1" fillId="2" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
@@ -9778,6 +9817,15 @@
       <alignment/>
     </xf>
     <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="608" fillId="609" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="609" fillId="610" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="610" fillId="611" fontId="0" numFmtId="0" xfId="0">
+      <alignment/>
+    </xf>
+    <xf applyAlignment="false" applyBorder="false" applyFill="false" applyFont="false" applyNumberFormat="false" applyProtection="false" borderId="611" fillId="612" fontId="0" numFmtId="0" xfId="0">
       <alignment/>
     </xf>
   </cellXfs>
@@ -10122,7 +10170,7 @@
       <c r="C2" t="str">
         <v>600120</v>
       </c>
-      <c r="D2" s="13" t="str">
+      <c r="D2" s="8" t="str">
         <v>净卖: -1.33亿</v>
       </c>
       <c r="E2">
@@ -10137,41 +10185,41 @@
       <c r="H2">
         <v>9.97</v>
       </c>
-      <c r="I2" s="6">
+      <c r="I2" s="1">
         <v>-12.49</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="2">
         <v>-21.25</v>
       </c>
-      <c r="K2" s="11">
+      <c r="K2" s="3">
         <v>-22.96</v>
       </c>
-      <c r="L2" s="8">
+      <c r="L2" s="9">
         <v>-26.08</v>
       </c>
-      <c r="M2" s="1">
+      <c r="M2" s="10">
         <v>-20.85</v>
       </c>
-      <c r="N2" s="2">
+      <c r="N2" s="4">
         <v>-20.85</v>
       </c>
       <c r="O2" s="12">
         <v>-22.16</v>
       </c>
-      <c r="P2" s="4">
+      <c r="P2" s="11">
         <v>-26.28</v>
       </c>
-      <c r="Q2" s="5">
+      <c r="Q2" s="6">
         <v>-25.48</v>
       </c>
-      <c r="R2" s="9">
+      <c r="R2" s="5">
         <v>-24.07</v>
       </c>
-      <c r="S2" s="3">
+      <c r="S2" s="13">
         <v>-25.78</v>
       </c>
-      <c r="T2" s="10">
-        <v>-41.99</v>
+      <c r="T2" s="7">
+        <v>-42.7</v>
       </c>
     </row>
     <row r="3">
@@ -10184,7 +10232,7 @@
       <c r="C3" t="str">
         <v>003021</v>
       </c>
-      <c r="D3" s="16" t="str">
+      <c r="D3" s="21" t="str">
         <v>净卖: -3895.40万</v>
       </c>
       <c r="E3">
@@ -10199,41 +10247,41 @@
       <c r="H3">
         <v>-3</v>
       </c>
-      <c r="I3" s="17">
+      <c r="I3" s="22">
         <v>-7.22</v>
       </c>
-      <c r="J3" s="25">
+      <c r="J3" s="23">
         <v>-10.22</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="16">
         <v>-4.57</v>
       </c>
-      <c r="L3" s="21">
+      <c r="L3" s="17">
         <v>-7.52</v>
       </c>
-      <c r="M3" s="18">
+      <c r="M3" s="24">
         <v>-0.02</v>
       </c>
-      <c r="N3" s="22">
+      <c r="N3" s="18">
         <v>4.27</v>
       </c>
-      <c r="O3" s="19">
+      <c r="O3" s="26">
         <v>5.17</v>
       </c>
-      <c r="P3" s="15">
+      <c r="P3" s="19">
         <v>3.7</v>
       </c>
-      <c r="Q3" s="23">
+      <c r="Q3" s="25">
         <v>13.88</v>
       </c>
-      <c r="R3" s="26">
+      <c r="R3" s="14">
         <v>25.27</v>
       </c>
-      <c r="S3" s="14">
+      <c r="S3" s="15">
         <v>24.52</v>
       </c>
-      <c r="T3" s="24">
-        <v>-20.54</v>
+      <c r="T3" s="20">
+        <v>-26.44</v>
       </c>
     </row>
     <row r="4">
@@ -10246,7 +10294,7 @@
       <c r="C4" t="str">
         <v>002896</v>
       </c>
-      <c r="D4" s="30" t="str">
+      <c r="D4" s="28" t="str">
         <v>净买: 5162.35万</v>
       </c>
       <c r="E4">
@@ -10261,41 +10309,41 @@
       <c r="H4">
         <v>3</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="38">
         <v>6.79</v>
       </c>
-      <c r="J4" s="31">
+      <c r="J4" s="35">
         <v>17.47</v>
       </c>
-      <c r="K4" s="29">
+      <c r="K4" s="36">
         <v>5.82</v>
       </c>
       <c r="L4" s="32">
         <v>15.69</v>
       </c>
-      <c r="M4" s="37">
+      <c r="M4" s="33">
         <v>27.26</v>
       </c>
-      <c r="N4" s="35">
+      <c r="N4" s="39">
         <v>39.98</v>
       </c>
-      <c r="O4" s="38">
+      <c r="O4" s="29">
         <v>25.98</v>
       </c>
-      <c r="P4" s="33">
+      <c r="P4" s="34">
         <v>13.39</v>
       </c>
-      <c r="Q4" s="36">
+      <c r="Q4" s="27">
         <v>16.45</v>
       </c>
-      <c r="R4" s="39">
+      <c r="R4" s="30">
         <v>19.91</v>
       </c>
-      <c r="S4" s="34">
+      <c r="S4" s="37">
         <v>19.53</v>
       </c>
-      <c r="T4" s="27">
-        <v>-14.09</v>
+      <c r="T4" s="31">
+        <v>-17.99</v>
       </c>
     </row>
     <row r="5">
@@ -10308,7 +10356,7 @@
       <c r="C5" t="str">
         <v>600602</v>
       </c>
-      <c r="D5" s="43" t="str">
+      <c r="D5" s="41" t="str">
         <v>净买: 1.03亿</v>
       </c>
       <c r="E5">
@@ -10323,41 +10371,41 @@
       <c r="H5">
         <v>-2.66</v>
       </c>
-      <c r="I5" s="50">
+      <c r="I5" s="42">
         <v>10.77</v>
       </c>
-      <c r="J5" s="44">
+      <c r="J5" s="48">
         <v>5.81</v>
       </c>
-      <c r="K5" s="51">
+      <c r="K5" s="46">
         <v>-3.88</v>
       </c>
-      <c r="L5" s="52">
+      <c r="L5" s="43">
         <v>-13.5</v>
       </c>
-      <c r="M5" s="45">
+      <c r="M5" s="49">
         <v>-15.88</v>
       </c>
-      <c r="N5" s="47">
+      <c r="N5" s="50">
         <v>-14.23</v>
       </c>
-      <c r="O5" s="42">
+      <c r="O5" s="51">
         <v>-8.5</v>
       </c>
-      <c r="P5" s="46">
+      <c r="P5" s="52">
         <v>-5.04</v>
       </c>
-      <c r="Q5" s="40">
+      <c r="Q5" s="44">
         <v>4.46</v>
       </c>
-      <c r="R5" s="48">
+      <c r="R5" s="45">
         <v>6.31</v>
       </c>
-      <c r="S5" s="41">
+      <c r="S5" s="40">
         <v>10.62</v>
       </c>
-      <c r="T5" s="49">
-        <v>-13.12</v>
+      <c r="T5" s="47">
+        <v>-16.96</v>
       </c>
     </row>
     <row r="6">
@@ -10370,7 +10418,7 @@
       <c r="C6" t="str">
         <v>003021</v>
       </c>
-      <c r="D6" s="62" t="str">
+      <c r="D6" s="65" t="str">
         <v>净买: 5581.43万</v>
       </c>
       <c r="E6">
@@ -10385,41 +10433,41 @@
       <c r="H6">
         <v>-1.3</v>
       </c>
-      <c r="I6" s="54">
+      <c r="I6" s="63">
         <v>11.45</v>
       </c>
-      <c r="J6" s="55">
+      <c r="J6" s="53">
         <v>10.79</v>
       </c>
-      <c r="K6" s="59">
+      <c r="K6" s="57">
         <v>-0.29</v>
       </c>
-      <c r="L6" s="56">
+      <c r="L6" s="59">
         <v>-5.12</v>
       </c>
-      <c r="M6" s="57">
+      <c r="M6" s="54">
         <v>4.3</v>
       </c>
-      <c r="N6" s="58">
+      <c r="N6" s="64">
         <v>14.73</v>
       </c>
-      <c r="O6" s="60">
+      <c r="O6" s="55">
         <v>13.05</v>
       </c>
-      <c r="P6" s="65">
+      <c r="P6" s="58">
         <v>12.06</v>
       </c>
-      <c r="Q6" s="53">
+      <c r="Q6" s="60">
         <v>13.73</v>
       </c>
-      <c r="R6" s="63">
+      <c r="R6" s="56">
         <v>10.86</v>
       </c>
       <c r="S6" s="61">
         <v>10.2</v>
       </c>
-      <c r="T6" s="64">
-        <v>-29.31</v>
+      <c r="T6" s="62">
+        <v>-34.55</v>
       </c>
     </row>
     <row r="7">
@@ -10432,7 +10480,7 @@
       <c r="C7" t="str">
         <v>002522</v>
       </c>
-      <c r="D7" s="75" t="str">
+      <c r="D7" s="74" t="str">
         <v>净卖: -2406.69万</v>
       </c>
       <c r="E7">
@@ -10447,41 +10495,41 @@
       <c r="H7">
         <v>-5.38</v>
       </c>
-      <c r="I7" s="67">
+      <c r="I7" s="76">
         <v>-4.11</v>
       </c>
-      <c r="J7" s="76">
+      <c r="J7" s="77">
         <v>-13.74</v>
       </c>
-      <c r="K7" s="77">
+      <c r="K7" s="69">
         <v>-21.64</v>
       </c>
-      <c r="L7" s="72">
+      <c r="L7" s="78">
         <v>-19.75</v>
       </c>
-      <c r="M7" s="68">
+      <c r="M7" s="70">
         <v>-18.96</v>
       </c>
-      <c r="N7" s="69">
+      <c r="N7" s="73">
         <v>-16.9</v>
       </c>
-      <c r="O7" s="73">
+      <c r="O7" s="71">
         <v>-18.64</v>
       </c>
-      <c r="P7" s="70">
+      <c r="P7" s="66">
         <v>-16.27</v>
       </c>
-      <c r="Q7" s="66">
+      <c r="Q7" s="72">
         <v>-17.06</v>
       </c>
-      <c r="R7" s="78">
+      <c r="R7" s="67">
         <v>-16.75</v>
       </c>
-      <c r="S7" s="71">
+      <c r="S7" s="68">
         <v>-19.59</v>
       </c>
-      <c r="T7" s="74">
-        <v>-3.48</v>
+      <c r="T7" s="75">
+        <v>-7.58</v>
       </c>
     </row>
     <row r="8">
@@ -10494,7 +10542,7 @@
       <c r="C8" t="str">
         <v>003021</v>
       </c>
-      <c r="D8" s="85" t="str">
+      <c r="D8" s="87" t="str">
         <v>净卖: -7322.64万</v>
       </c>
       <c r="E8">
@@ -10509,41 +10557,41 @@
       <c r="H8">
         <v>-1.2</v>
       </c>
-      <c r="I8" s="91">
+      <c r="I8" s="84">
         <v>11.33</v>
       </c>
-      <c r="J8" s="82">
+      <c r="J8" s="88">
         <v>9.7</v>
       </c>
-      <c r="K8" s="87">
+      <c r="K8" s="85">
         <v>8.74</v>
       </c>
-      <c r="L8" s="88">
+      <c r="L8" s="86">
         <v>10.37</v>
       </c>
-      <c r="M8" s="79">
+      <c r="M8" s="89">
         <v>7.58</v>
       </c>
-      <c r="N8" s="80">
+      <c r="N8" s="91">
         <v>6.94</v>
       </c>
-      <c r="O8" s="86">
+      <c r="O8" s="79">
         <v>-0.96</v>
       </c>
-      <c r="P8" s="83">
+      <c r="P8" s="80">
         <v>1.12</v>
       </c>
-      <c r="Q8" s="84">
+      <c r="Q8" s="90">
         <v>2.48</v>
       </c>
-      <c r="R8" s="89">
+      <c r="R8" s="81">
         <v>-0.05</v>
       </c>
-      <c r="S8" s="81">
+      <c r="S8" s="82">
         <v>-2.14</v>
       </c>
-      <c r="T8" s="90">
-        <v>-31.4</v>
+      <c r="T8" s="83">
+        <v>-36.49</v>
       </c>
     </row>
     <row r="9">
@@ -10556,7 +10604,7 @@
       <c r="C9" t="str">
         <v>002261</v>
       </c>
-      <c r="D9" s="97" t="str">
+      <c r="D9" s="99" t="str">
         <v>净卖: -1.12亿</v>
       </c>
       <c r="E9">
@@ -10571,41 +10619,41 @@
       <c r="H9">
         <v>-3.17</v>
       </c>
-      <c r="I9" s="103">
+      <c r="I9" s="102">
         <v>-7.06</v>
       </c>
       <c r="J9" s="100">
         <v>-13.04</v>
       </c>
-      <c r="K9" s="104">
+      <c r="K9" s="101">
         <v>-11.69</v>
       </c>
-      <c r="L9" s="93">
+      <c r="L9" s="94">
         <v>-10.05</v>
       </c>
-      <c r="M9" s="94">
+      <c r="M9" s="95">
         <v>-11.15</v>
       </c>
-      <c r="N9" s="95">
+      <c r="N9" s="96">
         <v>-12.48</v>
       </c>
-      <c r="O9" s="98">
+      <c r="O9" s="97">
         <v>-11.61</v>
       </c>
-      <c r="P9" s="99">
+      <c r="P9" s="104">
         <v>-10.56</v>
       </c>
-      <c r="Q9" s="96">
+      <c r="Q9" s="103">
         <v>-12.51</v>
       </c>
-      <c r="R9" s="101">
+      <c r="R9" s="98">
         <v>-9.97</v>
       </c>
-      <c r="S9" s="102">
+      <c r="S9" s="92">
         <v>-18.06</v>
       </c>
-      <c r="T9" s="92">
-        <v>-2.05</v>
+      <c r="T9" s="93">
+        <v>-10.41</v>
       </c>
     </row>
     <row r="10">
@@ -10618,7 +10666,7 @@
       <c r="C10" t="str">
         <v>000799</v>
       </c>
-      <c r="D10" s="111" t="str">
+      <c r="D10" s="116" t="str">
         <v>净卖: -41.89万</v>
       </c>
       <c r="E10">
@@ -10633,19 +10681,19 @@
       <c r="H10">
         <v>0</v>
       </c>
-      <c r="I10" s="116">
+      <c r="I10" s="107">
         <v>10.01</v>
       </c>
-      <c r="J10" s="117">
+      <c r="J10" s="110">
         <v>9.1</v>
       </c>
       <c r="K10" s="112">
         <v>8.38</v>
       </c>
-      <c r="L10" s="105">
+      <c r="L10" s="117">
         <v>7.23</v>
       </c>
-      <c r="M10" s="107">
+      <c r="M10" s="105">
         <v>5.75</v>
       </c>
       <c r="N10" s="113">
@@ -10657,17 +10705,17 @@
       <c r="P10" s="106">
         <v>6.34</v>
       </c>
-      <c r="Q10" s="115">
+      <c r="Q10" s="108">
         <v>5.62</v>
       </c>
-      <c r="R10" s="108">
+      <c r="R10" s="115">
         <v>4.79</v>
       </c>
       <c r="S10" s="109">
         <v>1.89</v>
       </c>
-      <c r="T10" s="110">
-        <v>-10.81</v>
+      <c r="T10" s="111">
+        <v>-12.68</v>
       </c>
     </row>
     <row r="11">
@@ -10680,7 +10728,7 @@
       <c r="C11" t="str">
         <v>688108</v>
       </c>
-      <c r="D11" s="121" t="str">
+      <c r="D11" s="129" t="str">
         <v>净买: 3339.73万</v>
       </c>
       <c r="E11">
@@ -10695,41 +10743,41 @@
       <c r="H11">
         <v>5</v>
       </c>
-      <c r="I11" s="130">
+      <c r="I11" s="124">
         <v>14.27</v>
       </c>
-      <c r="J11" s="118">
+      <c r="J11" s="120">
         <v>11.35</v>
       </c>
-      <c r="K11" s="126">
+      <c r="K11" s="125">
         <v>2.7</v>
       </c>
-      <c r="L11" s="127">
+      <c r="L11" s="121">
         <v>-5.73</v>
       </c>
-      <c r="M11" s="122">
+      <c r="M11" s="126">
         <v>-9.92</v>
       </c>
-      <c r="N11" s="124">
+      <c r="N11" s="122">
         <v>-8.04</v>
       </c>
-      <c r="O11" s="119">
+      <c r="O11" s="130">
         <v>-12.4</v>
       </c>
-      <c r="P11" s="123">
+      <c r="P11" s="127">
         <v>-16.72</v>
       </c>
-      <c r="Q11" s="120">
+      <c r="Q11" s="128">
         <v>-12.2</v>
       </c>
-      <c r="R11" s="128">
+      <c r="R11" s="118">
         <v>-8.57</v>
       </c>
-      <c r="S11" s="129">
+      <c r="S11" s="123">
         <v>-6.23</v>
       </c>
-      <c r="T11" s="125">
-        <v>-42.37</v>
+      <c r="T11" s="119">
+        <v>-43.25</v>
       </c>
     </row>
     <row r="12">
@@ -10742,7 +10790,7 @@
       <c r="C12" t="str">
         <v>300222</v>
       </c>
-      <c r="D12" s="141" t="str">
+      <c r="D12" s="134" t="str">
         <v>净卖: -6818.64万</v>
       </c>
       <c r="E12">
@@ -10757,41 +10805,41 @@
       <c r="H12">
         <v>2.15</v>
       </c>
-      <c r="I12" s="136">
+      <c r="I12" s="139">
         <v>16.68</v>
       </c>
-      <c r="J12" s="134">
+      <c r="J12" s="132">
         <v>11.46</v>
       </c>
-      <c r="K12" s="142">
+      <c r="K12" s="135">
         <v>5.46</v>
       </c>
-      <c r="L12" s="143">
+      <c r="L12" s="136">
         <v>3.27</v>
       </c>
-      <c r="M12" s="131">
+      <c r="M12" s="141">
         <v>4.13</v>
       </c>
-      <c r="N12" s="132">
+      <c r="N12" s="133">
         <v>-1.95</v>
       </c>
       <c r="O12" s="137">
         <v>-3.66</v>
       </c>
-      <c r="P12" s="139">
+      <c r="P12" s="140">
         <v>-0.94</v>
       </c>
-      <c r="Q12" s="133">
+      <c r="Q12" s="142">
         <v>1.56</v>
       </c>
-      <c r="R12" s="138">
+      <c r="R12" s="143">
         <v>-1.56</v>
       </c>
-      <c r="S12" s="140">
+      <c r="S12" s="138">
         <v>-0.78</v>
       </c>
-      <c r="T12" s="135">
-        <v>-12.47</v>
+      <c r="T12" s="131">
+        <v>-14.26</v>
       </c>
     </row>
     <row r="13">
@@ -10804,7 +10852,7 @@
       <c r="C13" t="str">
         <v>002837</v>
       </c>
-      <c r="D13" s="151" t="str">
+      <c r="D13" s="147" t="str">
         <v>净买: 1.07亿</v>
       </c>
       <c r="E13">
@@ -10819,41 +10867,41 @@
       <c r="H13">
         <v>-3.13</v>
       </c>
-      <c r="I13" s="156">
+      <c r="I13" s="153">
         <v>13.56</v>
       </c>
-      <c r="J13" s="145">
+      <c r="J13" s="154">
         <v>14.94</v>
       </c>
-      <c r="K13" s="146">
+      <c r="K13" s="148">
         <v>15.17</v>
       </c>
-      <c r="L13" s="147">
+      <c r="L13" s="151">
         <v>3.66</v>
       </c>
-      <c r="M13" s="148">
+      <c r="M13" s="149">
         <v>5.96</v>
       </c>
-      <c r="N13" s="144">
+      <c r="N13" s="155">
         <v>-2.76</v>
       </c>
-      <c r="O13" s="149">
+      <c r="O13" s="156">
         <v>2.11</v>
       </c>
-      <c r="P13" s="152">
+      <c r="P13" s="144">
         <v>-0.68</v>
       </c>
-      <c r="Q13" s="153">
+      <c r="Q13" s="152">
         <v>-3.52</v>
       </c>
-      <c r="R13" s="154">
+      <c r="R13" s="145">
         <v>3.92</v>
       </c>
-      <c r="S13" s="155">
+      <c r="S13" s="150">
         <v>8.92</v>
       </c>
-      <c r="T13" s="150">
-        <v>37.93</v>
+      <c r="T13" s="146">
+        <v>33.39</v>
       </c>
     </row>
     <row r="14">
@@ -10866,7 +10914,7 @@
       <c r="C14" t="str">
         <v>600521</v>
       </c>
-      <c r="D14" s="163" t="str">
+      <c r="D14" s="158" t="str">
         <v>净买: 2288.75万</v>
       </c>
       <c r="E14">
@@ -10884,38 +10932,38 @@
       <c r="I14" s="167">
         <v>-9.43</v>
       </c>
-      <c r="J14" s="158">
+      <c r="J14" s="164">
         <v>-8.27</v>
       </c>
-      <c r="K14" s="168">
+      <c r="K14" s="159">
         <v>-12.18</v>
       </c>
-      <c r="L14" s="159">
+      <c r="L14" s="168">
         <v>-7.04</v>
       </c>
-      <c r="M14" s="169">
+      <c r="M14" s="165">
         <v>-9.99</v>
       </c>
-      <c r="N14" s="157">
+      <c r="N14" s="160">
         <v>-12.07</v>
       </c>
-      <c r="O14" s="160">
+      <c r="O14" s="161">
         <v>-12</v>
       </c>
-      <c r="P14" s="165">
+      <c r="P14" s="169">
         <v>-13.97</v>
       </c>
-      <c r="Q14" s="166">
+      <c r="Q14" s="162">
         <v>-14.46</v>
       </c>
-      <c r="R14" s="164">
+      <c r="R14" s="163">
         <v>-16.47</v>
       </c>
-      <c r="S14" s="161">
+      <c r="S14" s="166">
         <v>-19.15</v>
       </c>
-      <c r="T14" s="162">
-        <v>-41.21</v>
+      <c r="T14" s="157">
+        <v>-41.13</v>
       </c>
     </row>
     <row r="15">
@@ -10943,41 +10991,41 @@
       <c r="H15">
         <v>7.68</v>
       </c>
-      <c r="I15" s="177">
+      <c r="I15" s="172">
         <v>2.16</v>
       </c>
-      <c r="J15" s="172">
+      <c r="J15" s="177">
         <v>12.36</v>
       </c>
-      <c r="K15" s="181">
+      <c r="K15" s="180">
         <v>23.61</v>
       </c>
-      <c r="L15" s="173">
+      <c r="L15" s="174">
         <v>18.97</v>
       </c>
-      <c r="M15" s="178">
+      <c r="M15" s="181">
         <v>17.66</v>
       </c>
-      <c r="N15" s="174">
+      <c r="N15" s="173">
         <v>25.9</v>
       </c>
-      <c r="O15" s="179">
+      <c r="O15" s="178">
         <v>25.51</v>
       </c>
-      <c r="P15" s="180">
+      <c r="P15" s="182">
         <v>28.19</v>
       </c>
-      <c r="Q15" s="182">
+      <c r="Q15" s="175">
         <v>28.12</v>
       </c>
-      <c r="R15" s="170">
+      <c r="R15" s="179">
         <v>40.94</v>
       </c>
-      <c r="S15" s="175">
+      <c r="S15" s="170">
         <v>55.07</v>
       </c>
       <c r="T15" s="176">
-        <v>33.16</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="16">
@@ -10990,7 +11038,7 @@
       <c r="C16" t="str">
         <v>600403</v>
       </c>
-      <c r="D16" s="194" t="str">
+      <c r="D16" s="185" t="str">
         <v>净买: 1894.16万</v>
       </c>
       <c r="E16">
@@ -11005,13 +11053,13 @@
       <c r="H16">
         <v>-2.81</v>
       </c>
-      <c r="I16" s="190">
+      <c r="I16" s="195">
         <v>9.03</v>
       </c>
-      <c r="J16" s="192">
+      <c r="J16" s="190">
         <v>-1.93</v>
       </c>
-      <c r="K16" s="195">
+      <c r="K16" s="186">
         <v>-0.24</v>
       </c>
       <c r="L16" s="187">
@@ -11020,26 +11068,26 @@
       <c r="M16" s="183">
         <v>9.27</v>
       </c>
-      <c r="N16" s="188">
+      <c r="N16" s="191">
         <v>6.74</v>
       </c>
-      <c r="O16" s="184">
+      <c r="O16" s="189">
         <v>10.95</v>
       </c>
-      <c r="P16" s="185">
+      <c r="P16" s="192">
         <v>22.02</v>
       </c>
-      <c r="Q16" s="186">
+      <c r="Q16" s="184">
         <v>34.18</v>
       </c>
-      <c r="R16" s="189">
+      <c r="R16" s="193">
         <v>23.47</v>
       </c>
-      <c r="S16" s="191">
+      <c r="S16" s="188">
         <v>11.07</v>
       </c>
-      <c r="T16" s="193">
-        <v>-31.29</v>
+      <c r="T16" s="194">
+        <v>-30.2</v>
       </c>
     </row>
     <row r="17">
@@ -11052,7 +11100,7 @@
       <c r="C17" t="str">
         <v>600403</v>
       </c>
-      <c r="D17" s="199" t="str">
+      <c r="D17" s="208" t="str">
         <v>净卖: -1651.88万</v>
       </c>
       <c r="E17">
@@ -11067,41 +11115,41 @@
       <c r="H17">
         <v>-7.84</v>
       </c>
-      <c r="I17" s="196">
+      <c r="I17" s="201">
         <v>-2.4</v>
       </c>
-      <c r="J17" s="200">
+      <c r="J17" s="196">
         <v>-0.72</v>
       </c>
-      <c r="K17" s="206">
+      <c r="K17" s="197">
         <v>-1.2</v>
       </c>
-      <c r="L17" s="197">
+      <c r="L17" s="206">
         <v>8.74</v>
       </c>
-      <c r="M17" s="201">
+      <c r="M17" s="198">
         <v>6.23</v>
       </c>
-      <c r="N17" s="202">
+      <c r="N17" s="199">
         <v>10.42</v>
       </c>
-      <c r="O17" s="207">
+      <c r="O17" s="203">
         <v>21.44</v>
       </c>
-      <c r="P17" s="203">
+      <c r="P17" s="200">
         <v>33.53</v>
       </c>
-      <c r="Q17" s="208">
+      <c r="Q17" s="204">
         <v>22.87</v>
       </c>
-      <c r="R17" s="204">
+      <c r="R17" s="205">
         <v>10.54</v>
       </c>
-      <c r="S17" s="205">
+      <c r="S17" s="202">
         <v>-0.48</v>
       </c>
-      <c r="T17" s="198">
-        <v>-31.62</v>
+      <c r="T17" s="207">
+        <v>-30.54</v>
       </c>
     </row>
     <row r="18">
@@ -11129,41 +11177,41 @@
       <c r="H18">
         <v>-0.22</v>
       </c>
-      <c r="I18" s="219">
+      <c r="I18" s="221">
         <v>10.23</v>
       </c>
-      <c r="J18" s="220">
+      <c r="J18" s="210">
         <v>11.19</v>
       </c>
-      <c r="K18" s="211">
+      <c r="K18" s="217">
         <v>9.73</v>
       </c>
-      <c r="L18" s="221">
+      <c r="L18" s="211">
         <v>12.16</v>
       </c>
       <c r="M18" s="212">
         <v>9.55</v>
       </c>
-      <c r="N18" s="209">
+      <c r="N18" s="213">
         <v>8.7</v>
       </c>
-      <c r="O18" s="214">
+      <c r="O18" s="218">
         <v>6.71</v>
       </c>
-      <c r="P18" s="210">
+      <c r="P18" s="219">
         <v>4.16</v>
       </c>
-      <c r="Q18" s="213">
+      <c r="Q18" s="214">
         <v>2.68</v>
       </c>
-      <c r="R18" s="215">
+      <c r="R18" s="220">
         <v>-2.26</v>
       </c>
-      <c r="S18" s="217">
+      <c r="S18" s="215">
         <v>-4.4</v>
       </c>
-      <c r="T18" s="218">
-        <v>-29.67</v>
+      <c r="T18" s="209">
+        <v>-31.14</v>
       </c>
     </row>
     <row r="19">
@@ -11176,7 +11224,7 @@
       <c r="C19" t="str">
         <v>000069</v>
       </c>
-      <c r="D19" s="232" t="str">
+      <c r="D19" s="222" t="str">
         <v>净卖: -7553.88万</v>
       </c>
       <c r="E19">
@@ -11191,16 +11239,16 @@
       <c r="H19">
         <v>1.88</v>
       </c>
-      <c r="I19" s="229">
+      <c r="I19" s="227">
         <v>8.12</v>
       </c>
-      <c r="J19" s="233">
+      <c r="J19" s="228">
         <v>3.69</v>
       </c>
-      <c r="K19" s="225">
+      <c r="K19" s="229">
         <v>4.06</v>
       </c>
-      <c r="L19" s="226">
+      <c r="L19" s="233">
         <v>2.95</v>
       </c>
       <c r="M19" s="223">
@@ -11209,23 +11257,23 @@
       <c r="N19" s="230">
         <v>0.37</v>
       </c>
-      <c r="O19" s="227">
+      <c r="O19" s="231">
         <v>-2.95</v>
       </c>
-      <c r="P19" s="234">
+      <c r="P19" s="225">
         <v>0</v>
       </c>
-      <c r="Q19" s="228">
+      <c r="Q19" s="224">
         <v>-1.11</v>
       </c>
-      <c r="R19" s="222">
+      <c r="R19" s="226">
         <v>-1.85</v>
       </c>
-      <c r="S19" s="224">
+      <c r="S19" s="234">
         <v>0</v>
       </c>
-      <c r="T19" s="231">
-        <v>-19.56</v>
+      <c r="T19" s="232">
+        <v>-19.93</v>
       </c>
     </row>
     <row r="20">
@@ -11238,7 +11286,7 @@
       <c r="C20" t="str">
         <v>002709</v>
       </c>
-      <c r="D20" s="244" t="str">
+      <c r="D20" s="246" t="str">
         <v>净买: 1.65亿</v>
       </c>
       <c r="E20">
@@ -11253,41 +11301,41 @@
       <c r="H20">
         <v>1.37</v>
       </c>
-      <c r="I20" s="235">
+      <c r="I20" s="237">
         <v>8.51</v>
       </c>
-      <c r="J20" s="236">
+      <c r="J20" s="238">
         <v>7.15</v>
       </c>
-      <c r="K20" s="246">
+      <c r="K20" s="239">
         <v>9.4</v>
       </c>
-      <c r="L20" s="237">
+      <c r="L20" s="242">
         <v>-1.54</v>
       </c>
-      <c r="M20" s="238">
+      <c r="M20" s="243">
         <v>3.1</v>
       </c>
-      <c r="N20" s="241">
+      <c r="N20" s="244">
         <v>1.91</v>
       </c>
-      <c r="O20" s="245">
+      <c r="O20" s="247">
         <v>-8.25</v>
       </c>
-      <c r="P20" s="239">
+      <c r="P20" s="245">
         <v>-11.49</v>
       </c>
-      <c r="Q20" s="242">
+      <c r="Q20" s="235">
         <v>-7.63</v>
       </c>
-      <c r="R20" s="247">
+      <c r="R20" s="240">
         <v>-9.03</v>
       </c>
-      <c r="S20" s="243">
+      <c r="S20" s="241">
         <v>-6.57</v>
       </c>
-      <c r="T20" s="240">
-        <v>27.03</v>
+      <c r="T20" s="236">
+        <v>24.67</v>
       </c>
     </row>
     <row r="21">
@@ -11315,41 +11363,41 @@
       <c r="H21">
         <v>3.39</v>
       </c>
-      <c r="I21" s="253">
+      <c r="I21" s="257">
         <v>8.46</v>
       </c>
-      <c r="J21" s="259">
+      <c r="J21" s="249">
         <v>-7.74</v>
       </c>
       <c r="K21" s="254">
         <v>-6.92</v>
       </c>
-      <c r="L21" s="255">
+      <c r="L21" s="258">
         <v>-6.67</v>
       </c>
-      <c r="M21" s="249">
+      <c r="M21" s="259">
         <v>-20</v>
       </c>
-      <c r="N21" s="256">
+      <c r="N21" s="250">
         <v>-17.49</v>
       </c>
-      <c r="O21" s="258">
+      <c r="O21" s="255">
         <v>-15.9</v>
       </c>
-      <c r="P21" s="250">
+      <c r="P21" s="256">
         <v>-19.69</v>
       </c>
       <c r="Q21" s="260">
         <v>-16.56</v>
       </c>
-      <c r="R21" s="257">
+      <c r="R21" s="253">
         <v>-17.03</v>
       </c>
       <c r="S21" s="248">
         <v>-17.59</v>
       </c>
       <c r="T21" s="251">
-        <v>1.23</v>
+        <v>-1.54</v>
       </c>
     </row>
     <row r="22">
@@ -11362,7 +11410,7 @@
       <c r="C22" t="str">
         <v>600343</v>
       </c>
-      <c r="D22" s="266" t="str">
+      <c r="D22" s="261" t="str">
         <v>净卖: -1.50亿</v>
       </c>
       <c r="E22">
@@ -11377,41 +11425,41 @@
       <c r="H22">
         <v>-2.42</v>
       </c>
-      <c r="I22" s="267">
+      <c r="I22" s="262">
         <v>5.68</v>
       </c>
-      <c r="J22" s="268">
+      <c r="J22" s="269">
         <v>9.44</v>
       </c>
-      <c r="K22" s="273">
+      <c r="K22" s="264">
         <v>20.4</v>
       </c>
-      <c r="L22" s="272">
+      <c r="L22" s="270">
         <v>32.45</v>
       </c>
-      <c r="M22" s="263">
+      <c r="M22" s="265">
         <v>25.78</v>
       </c>
-      <c r="N22" s="264">
+      <c r="N22" s="266">
         <v>29.91</v>
       </c>
-      <c r="O22" s="269">
+      <c r="O22" s="263">
         <v>19.51</v>
       </c>
-      <c r="P22" s="261">
+      <c r="P22" s="272">
         <v>20.5</v>
       </c>
-      <c r="Q22" s="265">
+      <c r="Q22" s="271">
         <v>27.5</v>
       </c>
-      <c r="R22" s="262">
+      <c r="R22" s="273">
         <v>22.58</v>
       </c>
-      <c r="S22" s="270">
+      <c r="S22" s="267">
         <v>25.45</v>
       </c>
-      <c r="T22" s="271">
-        <v>12.97</v>
+      <c r="T22" s="268">
+        <v>8.42</v>
       </c>
     </row>
     <row r="23">
@@ -11424,7 +11472,7 @@
       <c r="C23" t="str">
         <v>600151</v>
       </c>
-      <c r="D23" s="275" t="str">
+      <c r="D23" s="279" t="str">
         <v>净买: 9889.49万</v>
       </c>
       <c r="E23">
@@ -11439,41 +11487,41 @@
       <c r="H23">
         <v>3.9</v>
       </c>
-      <c r="I23" s="276">
+      <c r="I23" s="280">
         <v>5.88</v>
       </c>
-      <c r="J23" s="279">
+      <c r="J23" s="281">
         <v>7.37</v>
       </c>
-      <c r="K23" s="277">
+      <c r="K23" s="282">
         <v>13.25</v>
       </c>
-      <c r="L23" s="282">
+      <c r="L23" s="286">
         <v>18.63</v>
       </c>
-      <c r="M23" s="283">
+      <c r="M23" s="284">
         <v>18</v>
       </c>
-      <c r="N23" s="280">
+      <c r="N23" s="274">
         <v>11.5</v>
       </c>
-      <c r="O23" s="284">
+      <c r="O23" s="275">
         <v>0.37</v>
       </c>
-      <c r="P23" s="285">
+      <c r="P23" s="276">
         <v>-0.62</v>
       </c>
-      <c r="Q23" s="286">
+      <c r="Q23" s="277">
         <v>2.81</v>
       </c>
-      <c r="R23" s="281">
+      <c r="R23" s="283">
         <v>3.94</v>
       </c>
-      <c r="S23" s="278">
+      <c r="S23" s="285">
         <v>14.31</v>
       </c>
-      <c r="T23" s="274">
-        <v>-11.5</v>
+      <c r="T23" s="278">
+        <v>-14.38</v>
       </c>
     </row>
     <row r="24">
@@ -11501,41 +11549,41 @@
       <c r="H24">
         <v>-5.05</v>
       </c>
-      <c r="I24" s="292">
+      <c r="I24" s="297">
         <v>6.05</v>
       </c>
-      <c r="J24" s="294">
+      <c r="J24" s="289">
         <v>-4.33</v>
       </c>
-      <c r="K24" s="288">
+      <c r="K24" s="299">
         <v>-4.4</v>
       </c>
-      <c r="L24" s="289">
+      <c r="L24" s="293">
         <v>5.17</v>
       </c>
-      <c r="M24" s="293">
+      <c r="M24" s="290">
         <v>7.66</v>
       </c>
-      <c r="N24" s="290">
+      <c r="N24" s="298">
         <v>18.42</v>
       </c>
-      <c r="O24" s="297">
+      <c r="O24" s="294">
         <v>30.25</v>
       </c>
-      <c r="P24" s="291">
+      <c r="P24" s="287">
         <v>43.26</v>
       </c>
-      <c r="Q24" s="298">
+      <c r="Q24" s="291">
         <v>50.8</v>
       </c>
-      <c r="R24" s="299">
+      <c r="R24" s="295">
         <v>42.08</v>
       </c>
-      <c r="S24" s="287">
+      <c r="S24" s="288">
         <v>40.89</v>
       </c>
-      <c r="T24" s="295">
-        <v>54.13</v>
+      <c r="T24" s="292">
+        <v>51.19</v>
       </c>
     </row>
     <row r="25">
@@ -11548,7 +11596,7 @@
       <c r="C25" t="str">
         <v>002149</v>
       </c>
-      <c r="D25" s="311" t="str">
+      <c r="D25" s="310" t="str">
         <v>净买: 8459.47万</v>
       </c>
       <c r="E25">
@@ -11563,41 +11611,41 @@
       <c r="H25">
         <v>1.6</v>
       </c>
-      <c r="I25" s="307">
+      <c r="I25" s="311">
         <v>8.27</v>
       </c>
-      <c r="J25" s="304">
+      <c r="J25" s="302">
         <v>19.1</v>
       </c>
-      <c r="K25" s="302">
+      <c r="K25" s="312">
         <v>17.78</v>
       </c>
-      <c r="L25" s="305">
+      <c r="L25" s="303">
         <v>22.26</v>
       </c>
-      <c r="M25" s="312">
+      <c r="M25" s="300">
         <v>32.62</v>
       </c>
-      <c r="N25" s="306">
+      <c r="N25" s="304">
         <v>45.88</v>
       </c>
-      <c r="O25" s="308">
+      <c r="O25" s="305">
         <v>47.71</v>
       </c>
-      <c r="P25" s="300">
+      <c r="P25" s="301">
         <v>41.17</v>
       </c>
-      <c r="Q25" s="309">
+      <c r="Q25" s="306">
         <v>35.78</v>
       </c>
-      <c r="R25" s="303">
+      <c r="R25" s="309">
         <v>43.7</v>
       </c>
-      <c r="S25" s="310">
+      <c r="S25" s="307">
         <v>45.34</v>
       </c>
-      <c r="T25" s="301">
-        <v>82.76</v>
+      <c r="T25" s="308">
+        <v>78.72</v>
       </c>
     </row>
     <row r="26">
@@ -11610,7 +11658,7 @@
       <c r="C26" t="str">
         <v>002149</v>
       </c>
-      <c r="D26" s="314" t="str">
+      <c r="D26" s="318" t="str">
         <v>净卖: -9064.32万</v>
       </c>
       <c r="E26">
@@ -11625,41 +11673,41 @@
       <c r="H26">
         <v>2.07</v>
       </c>
-      <c r="I26" s="315">
+      <c r="I26" s="316">
         <v>7.77</v>
       </c>
-      <c r="J26" s="316">
+      <c r="J26" s="317">
         <v>6.57</v>
       </c>
-      <c r="K26" s="321">
+      <c r="K26" s="324">
         <v>10.63</v>
       </c>
-      <c r="L26" s="325">
+      <c r="L26" s="319">
         <v>20</v>
       </c>
-      <c r="M26" s="313">
+      <c r="M26" s="325">
         <v>32</v>
       </c>
-      <c r="N26" s="318">
+      <c r="N26" s="320">
         <v>33.66</v>
       </c>
-      <c r="O26" s="319">
+      <c r="O26" s="321">
         <v>27.74</v>
       </c>
       <c r="P26" s="322">
         <v>22.86</v>
       </c>
-      <c r="Q26" s="320">
+      <c r="Q26" s="313">
         <v>30.03</v>
       </c>
-      <c r="R26" s="317">
+      <c r="R26" s="314">
         <v>31.51</v>
       </c>
       <c r="S26" s="323">
         <v>42.26</v>
       </c>
-      <c r="T26" s="324">
-        <v>65.37</v>
+      <c r="T26" s="315">
+        <v>61.71</v>
       </c>
     </row>
     <row r="27">
@@ -11672,7 +11720,7 @@
       <c r="C27" t="str">
         <v>002149</v>
       </c>
-      <c r="D27" s="338" t="str">
+      <c r="D27" s="337" t="str">
         <v>净买: 7447.80万</v>
       </c>
       <c r="E27">
@@ -11687,41 +11735,41 @@
       <c r="H27">
         <v>0.1</v>
       </c>
-      <c r="I27" s="326">
+      <c r="I27" s="338">
         <v>9.9</v>
       </c>
-      <c r="J27" s="332">
+      <c r="J27" s="335">
         <v>11.27</v>
       </c>
-      <c r="K27" s="333">
+      <c r="K27" s="328">
         <v>6.35</v>
       </c>
-      <c r="L27" s="327">
+      <c r="L27" s="332">
         <v>2.28</v>
       </c>
-      <c r="M27" s="329">
+      <c r="M27" s="333">
         <v>8.25</v>
       </c>
-      <c r="N27" s="336">
+      <c r="N27" s="326">
         <v>9.49</v>
       </c>
       <c r="O27" s="334">
         <v>18.43</v>
       </c>
-      <c r="P27" s="337">
+      <c r="P27" s="329">
         <v>13.87</v>
       </c>
-      <c r="Q27" s="335">
+      <c r="Q27" s="327">
         <v>17.51</v>
       </c>
-      <c r="R27" s="330">
+      <c r="R27" s="336">
         <v>20.31</v>
       </c>
-      <c r="S27" s="328">
+      <c r="S27" s="330">
         <v>22.76</v>
       </c>
       <c r="T27" s="331">
-        <v>37.68</v>
+        <v>34.63</v>
       </c>
     </row>
     <row r="28">
@@ -11734,7 +11782,7 @@
       <c r="C28" t="str">
         <v>301005</v>
       </c>
-      <c r="D28" s="349" t="str">
+      <c r="D28" s="340" t="str">
         <v>净买: 8304.02万</v>
       </c>
       <c r="E28">
@@ -11749,41 +11797,41 @@
       <c r="H28">
         <v>5.58</v>
       </c>
-      <c r="I28" s="350">
+      <c r="I28" s="341">
         <v>13.66</v>
       </c>
-      <c r="J28" s="344">
+      <c r="J28" s="342">
         <v>15.41</v>
       </c>
-      <c r="K28" s="345">
+      <c r="K28" s="344">
         <v>34.28</v>
       </c>
-      <c r="L28" s="351">
+      <c r="L28" s="349">
         <v>23.58</v>
       </c>
-      <c r="M28" s="339">
+      <c r="M28" s="345">
         <v>30.8</v>
       </c>
-      <c r="N28" s="340">
+      <c r="N28" s="343">
         <v>27.1</v>
       </c>
-      <c r="O28" s="346">
+      <c r="O28" s="350">
         <v>39.67</v>
       </c>
-      <c r="P28" s="341">
+      <c r="P28" s="351">
         <v>34.97</v>
       </c>
-      <c r="Q28" s="347">
+      <c r="Q28" s="339">
         <v>45.55</v>
       </c>
-      <c r="R28" s="342">
+      <c r="R28" s="346">
         <v>49.76</v>
       </c>
-      <c r="S28" s="343">
+      <c r="S28" s="347">
         <v>66.78</v>
       </c>
       <c r="T28" s="348">
-        <v>41.1</v>
+        <v>41.48</v>
       </c>
     </row>
     <row r="29">
@@ -11796,7 +11844,7 @@
       <c r="C29" t="str">
         <v>300503</v>
       </c>
-      <c r="D29" s="362" t="str">
+      <c r="D29" s="356" t="str">
         <v>净买: 6889.84万</v>
       </c>
       <c r="E29">
@@ -11811,41 +11859,41 @@
       <c r="H29">
         <v>-5.69</v>
       </c>
-      <c r="I29" s="363">
+      <c r="I29" s="357">
         <v>25.74</v>
       </c>
-      <c r="J29" s="355">
+      <c r="J29" s="352">
         <v>25.58</v>
       </c>
-      <c r="K29" s="356">
+      <c r="K29" s="358">
         <v>19.55</v>
       </c>
       <c r="L29" s="359">
         <v>22.01</v>
       </c>
-      <c r="M29" s="360">
+      <c r="M29" s="362">
         <v>17.5</v>
       </c>
-      <c r="N29" s="354">
+      <c r="N29" s="353">
         <v>19.83</v>
       </c>
-      <c r="O29" s="364">
+      <c r="O29" s="360">
         <v>27.93</v>
       </c>
-      <c r="P29" s="361">
+      <c r="P29" s="354">
         <v>36.52</v>
       </c>
-      <c r="Q29" s="357">
+      <c r="Q29" s="363">
         <v>23.97</v>
       </c>
-      <c r="R29" s="358">
+      <c r="R29" s="361">
         <v>21.09</v>
       </c>
-      <c r="S29" s="352">
+      <c r="S29" s="364">
         <v>18.68</v>
       </c>
-      <c r="T29" s="353">
-        <v>24.02</v>
+      <c r="T29" s="355">
+        <v>28.1</v>
       </c>
     </row>
     <row r="30">
@@ -11858,7 +11906,7 @@
       <c r="C30" t="str">
         <v>002565</v>
       </c>
-      <c r="D30" s="366" t="str">
+      <c r="D30" s="374" t="str">
         <v>净卖: -6558.32万</v>
       </c>
       <c r="E30">
@@ -11873,41 +11921,41 @@
       <c r="H30">
         <v>5.73</v>
       </c>
-      <c r="I30" s="367">
+      <c r="I30" s="375">
         <v>-8.62</v>
       </c>
-      <c r="J30" s="368">
+      <c r="J30" s="367">
         <v>-4.85</v>
       </c>
-      <c r="K30" s="374">
+      <c r="K30" s="368">
         <v>0.41</v>
       </c>
-      <c r="L30" s="369">
+      <c r="L30" s="376">
         <v>10.47</v>
       </c>
-      <c r="M30" s="375">
+      <c r="M30" s="372">
         <v>15.07</v>
       </c>
-      <c r="N30" s="376">
+      <c r="N30" s="377">
         <v>18.11</v>
       </c>
-      <c r="O30" s="373">
+      <c r="O30" s="370">
         <v>6.3</v>
       </c>
-      <c r="P30" s="370">
+      <c r="P30" s="365">
         <v>-4.33</v>
       </c>
-      <c r="Q30" s="371">
+      <c r="Q30" s="369">
         <v>-13.88</v>
       </c>
-      <c r="R30" s="377">
+      <c r="R30" s="371">
         <v>-18.73</v>
       </c>
-      <c r="S30" s="372">
+      <c r="S30" s="366">
         <v>-18.16</v>
       </c>
-      <c r="T30" s="365">
-        <v>-4.18</v>
+      <c r="T30" s="373">
+        <v>-2.73</v>
       </c>
     </row>
     <row r="31">
@@ -11920,7 +11968,7 @@
       <c r="C31" t="str">
         <v>002151</v>
       </c>
-      <c r="D31" s="386" t="str">
+      <c r="D31" s="387" t="str">
         <v>净买: 7582.89万</v>
       </c>
       <c r="E31">
@@ -11935,41 +11983,41 @@
       <c r="H31">
         <v>9.62</v>
       </c>
-      <c r="I31" s="383">
+      <c r="I31" s="388">
         <v>0.34</v>
       </c>
-      <c r="J31" s="387">
+      <c r="J31" s="383">
         <v>10.38</v>
       </c>
-      <c r="K31" s="384">
+      <c r="K31" s="379">
         <v>15.86</v>
       </c>
-      <c r="L31" s="388">
+      <c r="L31" s="384">
         <v>19.86</v>
       </c>
-      <c r="M31" s="379">
+      <c r="M31" s="380">
         <v>22.13</v>
       </c>
-      <c r="N31" s="385">
+      <c r="N31" s="389">
         <v>34.34</v>
       </c>
-      <c r="O31" s="380">
+      <c r="O31" s="381">
         <v>20.9</v>
       </c>
-      <c r="P31" s="381">
+      <c r="P31" s="385">
         <v>8.9</v>
       </c>
-      <c r="Q31" s="382">
+      <c r="Q31" s="390">
         <v>5.08</v>
       </c>
-      <c r="R31" s="389">
+      <c r="R31" s="386">
         <v>0.26</v>
       </c>
-      <c r="S31" s="378">
+      <c r="S31" s="382">
         <v>-0.74</v>
       </c>
-      <c r="T31" s="390">
-        <v>-19.26</v>
+      <c r="T31" s="378">
+        <v>-21.08</v>
       </c>
     </row>
     <row r="32">
@@ -11982,7 +12030,7 @@
       <c r="C32" t="str">
         <v>601698</v>
       </c>
-      <c r="D32" s="396" t="str">
+      <c r="D32" s="398" t="str">
         <v>净买: 194.55万</v>
       </c>
       <c r="E32">
@@ -12000,38 +12048,38 @@
       <c r="I32" s="399">
         <v>7.2</v>
       </c>
-      <c r="J32" s="400">
+      <c r="J32" s="403">
         <v>17.92</v>
       </c>
-      <c r="K32" s="393">
+      <c r="K32" s="395">
         <v>19.67</v>
       </c>
-      <c r="L32" s="397">
+      <c r="L32" s="396">
         <v>21.47</v>
       </c>
-      <c r="M32" s="394">
+      <c r="M32" s="391">
         <v>33.61</v>
       </c>
-      <c r="N32" s="403">
+      <c r="N32" s="397">
         <v>46.97</v>
       </c>
-      <c r="O32" s="398">
+      <c r="O32" s="393">
         <v>32.27</v>
       </c>
-      <c r="P32" s="391">
+      <c r="P32" s="400">
         <v>19.04</v>
       </c>
-      <c r="Q32" s="395">
+      <c r="Q32" s="394">
         <v>7.15</v>
       </c>
-      <c r="R32" s="401">
+      <c r="R32" s="392">
         <v>9.55</v>
       </c>
-      <c r="S32" s="402">
+      <c r="S32" s="401">
         <v>8.54</v>
       </c>
-      <c r="T32" s="392">
-        <v>0.49</v>
+      <c r="T32" s="402">
+        <v>-4.23</v>
       </c>
     </row>
     <row r="33">
@@ -12044,7 +12092,7 @@
       <c r="C33" t="str">
         <v>603698</v>
       </c>
-      <c r="D33" s="408" t="str">
+      <c r="D33" s="407" t="str">
         <v>净买: 6020.50万</v>
       </c>
       <c r="E33">
@@ -12059,41 +12107,41 @@
       <c r="H33">
         <v>-3.65</v>
       </c>
-      <c r="I33" s="412">
+      <c r="I33" s="411">
         <v>14.16</v>
       </c>
-      <c r="J33" s="413">
+      <c r="J33" s="415">
         <v>8.62</v>
       </c>
-      <c r="K33" s="409">
+      <c r="K33" s="405">
         <v>15.14</v>
       </c>
-      <c r="L33" s="414">
+      <c r="L33" s="408">
         <v>18.92</v>
       </c>
-      <c r="M33" s="415">
+      <c r="M33" s="406">
         <v>30.81</v>
       </c>
-      <c r="N33" s="405">
+      <c r="N33" s="412">
         <v>17.73</v>
       </c>
-      <c r="O33" s="411">
+      <c r="O33" s="416">
         <v>5.95</v>
       </c>
-      <c r="P33" s="406">
+      <c r="P33" s="409">
         <v>3.38</v>
       </c>
-      <c r="Q33" s="416">
+      <c r="Q33" s="413">
         <v>8.46</v>
       </c>
-      <c r="R33" s="410">
+      <c r="R33" s="404">
         <v>3.19</v>
       </c>
-      <c r="S33" s="407">
+      <c r="S33" s="414">
         <v>-2.16</v>
       </c>
-      <c r="T33" s="404">
-        <v>8.81</v>
+      <c r="T33" s="410">
+        <v>6.73</v>
       </c>
     </row>
     <row r="34">
@@ -12106,7 +12154,7 @@
       <c r="C34" t="str">
         <v>002202</v>
       </c>
-      <c r="D34" s="423" t="str">
+      <c r="D34" s="428" t="str">
         <v>净买: 4.15亿</v>
       </c>
       <c r="E34">
@@ -12121,41 +12169,41 @@
       <c r="H34">
         <v>9.99</v>
       </c>
-      <c r="I34" s="420">
+      <c r="I34" s="417">
         <v>0</v>
       </c>
-      <c r="J34" s="424">
+      <c r="J34" s="420">
         <v>9.99</v>
       </c>
-      <c r="K34" s="426">
+      <c r="K34" s="425">
         <v>6.29</v>
       </c>
-      <c r="L34" s="429">
+      <c r="L34" s="426">
         <v>4.51</v>
       </c>
-      <c r="M34" s="425">
+      <c r="M34" s="427">
         <v>-5.95</v>
       </c>
-      <c r="N34" s="417">
+      <c r="N34" s="421">
         <v>-15.34</v>
       </c>
-      <c r="O34" s="427">
+      <c r="O34" s="418">
         <v>-13.27</v>
       </c>
-      <c r="P34" s="418">
+      <c r="P34" s="422">
         <v>-18.41</v>
       </c>
-      <c r="Q34" s="428">
+      <c r="Q34" s="423">
         <v>-20.32</v>
       </c>
       <c r="R34" s="419">
         <v>-15.81</v>
       </c>
-      <c r="S34" s="421">
+      <c r="S34" s="424">
         <v>-7.39</v>
       </c>
-      <c r="T34" s="422">
-        <v>-16.94</v>
+      <c r="T34" s="429">
+        <v>-20.13</v>
       </c>
     </row>
     <row r="35">
@@ -12168,7 +12216,7 @@
       <c r="C35" t="str">
         <v>002202</v>
       </c>
-      <c r="D35" s="433" t="str">
+      <c r="D35" s="437" t="str">
         <v>净买: 3.95亿</v>
       </c>
       <c r="E35">
@@ -12183,41 +12231,41 @@
       <c r="H35">
         <v>6.42</v>
       </c>
-      <c r="I35" s="434">
+      <c r="I35" s="438">
         <v>3.35</v>
       </c>
-      <c r="J35" s="438">
+      <c r="J35" s="439">
         <v>-0.12</v>
       </c>
-      <c r="K35" s="439">
+      <c r="K35" s="433">
         <v>-1.79</v>
       </c>
-      <c r="L35" s="435">
+      <c r="L35" s="430">
         <v>-11.62</v>
       </c>
-      <c r="M35" s="436">
+      <c r="M35" s="440">
         <v>-20.45</v>
       </c>
-      <c r="N35" s="437">
+      <c r="N35" s="441">
         <v>-18.51</v>
       </c>
-      <c r="O35" s="442">
+      <c r="O35" s="434">
         <v>-23.33</v>
       </c>
-      <c r="P35" s="440">
+      <c r="P35" s="442">
         <v>-25.13</v>
       </c>
       <c r="Q35" s="431">
         <v>-20.89</v>
       </c>
-      <c r="R35" s="441">
+      <c r="R35" s="432">
         <v>-12.97</v>
       </c>
-      <c r="S35" s="432">
+      <c r="S35" s="435">
         <v>-16.45</v>
       </c>
-      <c r="T35" s="430">
-        <v>-21.95</v>
+      <c r="T35" s="436">
+        <v>-24.95</v>
       </c>
     </row>
     <row r="36">
@@ -12230,7 +12278,7 @@
       <c r="C36" t="str">
         <v>000901</v>
       </c>
-      <c r="D36" s="451" t="str">
+      <c r="D36" s="452" t="str">
         <v>净买: 926.43万</v>
       </c>
       <c r="E36">
@@ -12245,41 +12293,41 @@
       <c r="H36">
         <v>1.96</v>
       </c>
-      <c r="I36" s="443">
+      <c r="I36" s="444">
         <v>6.61</v>
       </c>
-      <c r="J36" s="452">
+      <c r="J36" s="448">
         <v>-4.05</v>
       </c>
-      <c r="K36" s="453">
+      <c r="K36" s="451">
         <v>-11.42</v>
       </c>
       <c r="L36" s="449">
         <v>-16.39</v>
       </c>
-      <c r="M36" s="447">
+      <c r="M36" s="453">
         <v>-14.59</v>
       </c>
-      <c r="N36" s="450">
+      <c r="N36" s="445">
         <v>-14.59</v>
       </c>
-      <c r="O36" s="444">
+      <c r="O36" s="446">
         <v>-20.53</v>
       </c>
-      <c r="P36" s="448">
+      <c r="P36" s="450">
         <v>-21.57</v>
       </c>
       <c r="Q36" s="454">
         <v>-18.98</v>
       </c>
-      <c r="R36" s="445">
+      <c r="R36" s="447">
         <v>-15.35</v>
       </c>
       <c r="S36" s="455">
         <v>-23.06</v>
       </c>
-      <c r="T36" s="446">
-        <v>-33.2</v>
+      <c r="T36" s="443">
+        <v>-35.7</v>
       </c>
     </row>
     <row r="37">
@@ -12292,7 +12340,7 @@
       <c r="C37" t="str">
         <v>600498</v>
       </c>
-      <c r="D37" s="456" t="str">
+      <c r="D37" s="458" t="str">
         <v>净卖: -3.15亿</v>
       </c>
       <c r="E37">
@@ -12307,41 +12355,41 @@
       <c r="H37">
         <v>3.52</v>
       </c>
-      <c r="I37" s="461">
+      <c r="I37" s="467">
         <v>4.32</v>
       </c>
-      <c r="J37" s="457">
+      <c r="J37" s="468">
         <v>-6.12</v>
       </c>
-      <c r="K37" s="462">
+      <c r="K37" s="459">
         <v>-14.95</v>
       </c>
-      <c r="L37" s="458">
+      <c r="L37" s="464">
         <v>-14.32</v>
       </c>
-      <c r="M37" s="464">
+      <c r="M37" s="460">
         <v>-19.2</v>
       </c>
-      <c r="N37" s="466">
+      <c r="N37" s="465">
         <v>-20.25</v>
       </c>
-      <c r="O37" s="459">
+      <c r="O37" s="456">
         <v>-17.13</v>
       </c>
-      <c r="P37" s="467">
+      <c r="P37" s="461">
         <v>-8.85</v>
       </c>
-      <c r="Q37" s="463">
+      <c r="Q37" s="462">
         <v>-12.45</v>
       </c>
-      <c r="R37" s="460">
+      <c r="R37" s="463">
         <v>-13.08</v>
       </c>
-      <c r="S37" s="465">
+      <c r="S37" s="466">
         <v>-11.97</v>
       </c>
-      <c r="T37" s="468">
-        <v>12.47</v>
+      <c r="T37" s="457">
+        <v>13.99</v>
       </c>
     </row>
     <row r="38">
@@ -12354,7 +12402,7 @@
       <c r="C38" t="str">
         <v>002202</v>
       </c>
-      <c r="D38" s="479" t="str">
+      <c r="D38" s="473" t="str">
         <v>净卖: -1.92亿</v>
       </c>
       <c r="E38">
@@ -12369,41 +12417,41 @@
       <c r="H38">
         <v>-8.96</v>
       </c>
-      <c r="I38" s="478">
+      <c r="I38" s="480">
         <v>-1.15</v>
       </c>
-      <c r="J38" s="473">
+      <c r="J38" s="470">
         <v>-11.02</v>
       </c>
-      <c r="K38" s="480">
+      <c r="K38" s="474">
         <v>-8.85</v>
       </c>
-      <c r="L38" s="481">
+      <c r="L38" s="475">
         <v>-14.25</v>
       </c>
-      <c r="M38" s="474">
+      <c r="M38" s="476">
         <v>-16.26</v>
       </c>
-      <c r="N38" s="475">
+      <c r="N38" s="471">
         <v>-11.52</v>
       </c>
-      <c r="O38" s="469">
+      <c r="O38" s="477">
         <v>-2.67</v>
       </c>
-      <c r="P38" s="470">
+      <c r="P38" s="481">
         <v>-6.55</v>
       </c>
-      <c r="Q38" s="476">
+      <c r="Q38" s="469">
         <v>-5.92</v>
       </c>
-      <c r="R38" s="471">
+      <c r="R38" s="478">
         <v>-8.82</v>
       </c>
       <c r="S38" s="472">
         <v>-11.48</v>
       </c>
-      <c r="T38" s="477">
-        <v>-12.7</v>
+      <c r="T38" s="479">
+        <v>-16.06</v>
       </c>
     </row>
     <row r="39">
@@ -12416,7 +12464,7 @@
       <c r="C39" t="str">
         <v>002202</v>
       </c>
-      <c r="D39" s="490" t="str">
+      <c r="D39" s="494" t="str">
         <v>净卖: -1.10亿</v>
       </c>
       <c r="E39">
@@ -12431,41 +12479,41 @@
       <c r="H39">
         <v>-9.99</v>
       </c>
-      <c r="I39" s="491">
+      <c r="I39" s="482">
         <v>0</v>
       </c>
-      <c r="J39" s="492">
+      <c r="J39" s="490">
         <v>2.44</v>
       </c>
-      <c r="K39" s="487">
+      <c r="K39" s="483">
         <v>-3.62</v>
       </c>
-      <c r="L39" s="493">
+      <c r="L39" s="484">
         <v>-5.88</v>
       </c>
-      <c r="M39" s="494">
+      <c r="M39" s="492">
         <v>-0.55</v>
       </c>
-      <c r="N39" s="482">
+      <c r="N39" s="485">
         <v>9.39</v>
       </c>
-      <c r="O39" s="483">
+      <c r="O39" s="488">
         <v>5.03</v>
       </c>
-      <c r="P39" s="484">
+      <c r="P39" s="489">
         <v>5.73</v>
       </c>
-      <c r="Q39" s="485">
+      <c r="Q39" s="493">
         <v>2.48</v>
       </c>
-      <c r="R39" s="488">
+      <c r="R39" s="486">
         <v>-0.52</v>
       </c>
-      <c r="S39" s="486">
+      <c r="S39" s="491">
         <v>-3.44</v>
       </c>
-      <c r="T39" s="489">
-        <v>-1.89</v>
+      <c r="T39" s="487">
+        <v>-5.66</v>
       </c>
     </row>
     <row r="40">
@@ -12493,41 +12541,41 @@
       <c r="H40">
         <v>15.61</v>
       </c>
-      <c r="I40" s="496">
+      <c r="I40" s="504">
         <v>-6.17</v>
       </c>
-      <c r="J40" s="504">
+      <c r="J40" s="497">
         <v>-4.46</v>
       </c>
-      <c r="K40" s="505">
+      <c r="K40" s="498">
         <v>-11.42</v>
       </c>
-      <c r="L40" s="501">
+      <c r="L40" s="507">
         <v>-12.25</v>
       </c>
-      <c r="M40" s="497">
+      <c r="M40" s="502">
         <v>-16.96</v>
       </c>
-      <c r="N40" s="506">
+      <c r="N40" s="499">
         <v>-12.92</v>
       </c>
-      <c r="O40" s="498">
+      <c r="O40" s="500">
         <v>-6.46</v>
       </c>
-      <c r="P40" s="500">
+      <c r="P40" s="495">
         <v>0</v>
       </c>
-      <c r="Q40" s="507">
+      <c r="Q40" s="505">
         <v>-3.17</v>
       </c>
-      <c r="R40" s="495">
+      <c r="R40" s="501">
         <v>-6.54</v>
       </c>
-      <c r="S40" s="502">
+      <c r="S40" s="506">
         <v>-4.71</v>
       </c>
-      <c r="T40" s="499">
-        <v>-34.29</v>
+      <c r="T40" s="496">
+        <v>-36.83</v>
       </c>
     </row>
     <row r="41">
@@ -12540,7 +12588,7 @@
       <c r="C41" t="str">
         <v>001337</v>
       </c>
-      <c r="D41" s="513" t="str">
+      <c r="D41" s="517" t="str">
         <v>净买: 4696.53万</v>
       </c>
       <c r="E41">
@@ -12555,41 +12603,41 @@
       <c r="H41">
         <v>5.3</v>
       </c>
-      <c r="I41" s="510">
+      <c r="I41" s="518">
         <v>4.47</v>
       </c>
-      <c r="J41" s="520">
+      <c r="J41" s="513">
         <v>14.89</v>
       </c>
-      <c r="K41" s="514">
+      <c r="K41" s="519">
         <v>3.41</v>
       </c>
-      <c r="L41" s="515">
+      <c r="L41" s="516">
         <v>-6.94</v>
       </c>
-      <c r="M41" s="517">
+      <c r="M41" s="510">
         <v>-12.41</v>
       </c>
-      <c r="N41" s="508">
+      <c r="N41" s="514">
         <v>-20.23</v>
       </c>
-      <c r="O41" s="518">
+      <c r="O41" s="520">
         <v>-28.05</v>
       </c>
-      <c r="P41" s="511">
+      <c r="P41" s="515">
         <v>-27.52</v>
       </c>
-      <c r="Q41" s="512">
+      <c r="Q41" s="508">
         <v>-24</v>
       </c>
-      <c r="R41" s="516">
+      <c r="R41" s="511">
         <v>-27.11</v>
       </c>
-      <c r="S41" s="509">
+      <c r="S41" s="512">
         <v>-26.55</v>
       </c>
-      <c r="T41" s="519">
-        <v>-25.14</v>
+      <c r="T41" s="509">
+        <v>-26.16</v>
       </c>
     </row>
     <row r="42">
@@ -12602,7 +12650,7 @@
       <c r="C42" t="str">
         <v>001337</v>
       </c>
-      <c r="D42" s="521" t="str">
+      <c r="D42" s="525" t="str">
         <v>净卖: -5018.84万</v>
       </c>
       <c r="E42">
@@ -12617,41 +12665,41 @@
       <c r="H42">
         <v>10.01</v>
       </c>
-      <c r="I42" s="522">
+      <c r="I42" s="532">
         <v>-0.03</v>
       </c>
-      <c r="J42" s="524">
+      <c r="J42" s="526">
         <v>-10.02</v>
       </c>
-      <c r="K42" s="526">
+      <c r="K42" s="527">
         <v>-19.02</v>
       </c>
-      <c r="L42" s="527">
+      <c r="L42" s="533">
         <v>-23.78</v>
       </c>
-      <c r="M42" s="529">
+      <c r="M42" s="528">
         <v>-30.59</v>
       </c>
-      <c r="N42" s="523">
+      <c r="N42" s="529">
         <v>-37.39</v>
       </c>
-      <c r="O42" s="530">
+      <c r="O42" s="521">
         <v>-36.93</v>
       </c>
-      <c r="P42" s="528">
+      <c r="P42" s="522">
         <v>-33.87</v>
       </c>
-      <c r="Q42" s="531">
+      <c r="Q42" s="530">
         <v>-36.57</v>
       </c>
-      <c r="R42" s="525">
+      <c r="R42" s="523">
         <v>-36.08</v>
       </c>
-      <c r="S42" s="532">
+      <c r="S42" s="531">
         <v>-36.64</v>
       </c>
-      <c r="T42" s="533">
-        <v>-34.86</v>
+      <c r="T42" s="524">
+        <v>-35.74</v>
       </c>
     </row>
     <row r="43">
@@ -12664,7 +12712,7 @@
       <c r="C43" t="str">
         <v>000995</v>
       </c>
-      <c r="D43" s="539" t="str">
+      <c r="D43" s="546" t="str">
         <v>净买: 1752.24万</v>
       </c>
       <c r="E43">
@@ -12679,41 +12727,41 @@
       <c r="H43">
         <v>10.01</v>
       </c>
-      <c r="I43" s="540">
+      <c r="I43" s="544">
         <v>0</v>
       </c>
-      <c r="J43" s="544">
+      <c r="J43" s="539">
         <v>9.98</v>
       </c>
-      <c r="K43" s="535">
+      <c r="K43" s="540">
         <v>20.97</v>
       </c>
-      <c r="L43" s="536">
+      <c r="L43" s="534">
         <v>19.02</v>
       </c>
       <c r="M43" s="541">
         <v>26.11</v>
       </c>
-      <c r="N43" s="545">
+      <c r="N43" s="535">
         <v>13.5</v>
       </c>
       <c r="O43" s="542">
         <v>18.02</v>
       </c>
-      <c r="P43" s="537">
+      <c r="P43" s="543">
         <v>6.91</v>
       </c>
-      <c r="Q43" s="538">
+      <c r="Q43" s="536">
         <v>4.02</v>
       </c>
-      <c r="R43" s="543">
+      <c r="R43" s="537">
         <v>0.38</v>
       </c>
-      <c r="S43" s="546">
+      <c r="S43" s="545">
         <v>-1.63</v>
       </c>
-      <c r="T43" s="534">
-        <v>-16.01</v>
+      <c r="T43" s="538">
+        <v>-15.19</v>
       </c>
     </row>
     <row r="44">
@@ -12726,7 +12774,7 @@
       <c r="C44" t="str">
         <v>000995</v>
       </c>
-      <c r="D44" s="559" t="str">
+      <c r="D44" s="548" t="str">
         <v>净卖: -1741.06万</v>
       </c>
       <c r="E44">
@@ -12741,16 +12789,16 @@
       <c r="H44">
         <v>-4.33</v>
       </c>
-      <c r="I44" s="556">
+      <c r="I44" s="557">
         <v>14.96</v>
       </c>
-      <c r="J44" s="552">
+      <c r="J44" s="558">
         <v>26.44</v>
       </c>
-      <c r="K44" s="548">
+      <c r="K44" s="549">
         <v>24.41</v>
       </c>
-      <c r="L44" s="557">
+      <c r="L44" s="550">
         <v>31.82</v>
       </c>
       <c r="M44" s="553">
@@ -12759,23 +12807,23 @@
       <c r="N44" s="554">
         <v>23.36</v>
       </c>
-      <c r="O44" s="549">
+      <c r="O44" s="555">
         <v>11.75</v>
       </c>
-      <c r="P44" s="550">
+      <c r="P44" s="551">
         <v>8.73</v>
       </c>
-      <c r="Q44" s="547">
+      <c r="Q44" s="556">
         <v>4.92</v>
       </c>
-      <c r="R44" s="551">
+      <c r="R44" s="559">
         <v>2.82</v>
       </c>
-      <c r="S44" s="558">
+      <c r="S44" s="547">
         <v>3.87</v>
       </c>
-      <c r="T44" s="555">
-        <v>-12.2</v>
+      <c r="T44" s="552">
+        <v>-11.35</v>
       </c>
     </row>
     <row r="45">
@@ -12803,13 +12851,13 @@
       <c r="H45">
         <v>-0.29</v>
       </c>
-      <c r="I45" s="565">
+      <c r="I45" s="561">
         <v>20.35</v>
       </c>
-      <c r="J45" s="564">
+      <c r="J45" s="571">
         <v>23.96</v>
       </c>
-      <c r="K45" s="566">
+      <c r="K45" s="572">
         <v>16.61</v>
       </c>
       <c r="L45" s="568">
@@ -12818,26 +12866,26 @@
       <c r="M45" s="569">
         <v>10.84</v>
       </c>
-      <c r="N45" s="570">
+      <c r="N45" s="560">
         <v>7.09</v>
       </c>
-      <c r="O45" s="571">
+      <c r="O45" s="562">
         <v>7.44</v>
       </c>
-      <c r="P45" s="572">
+      <c r="P45" s="563">
         <v>2.1</v>
       </c>
-      <c r="Q45" s="560">
+      <c r="Q45" s="566">
         <v>1.76</v>
       </c>
-      <c r="R45" s="562">
+      <c r="R45" s="564">
         <v>6.85</v>
       </c>
-      <c r="S45" s="563">
+      <c r="S45" s="565">
         <v>11.3</v>
       </c>
-      <c r="T45" s="561">
-        <v>7.35</v>
+      <c r="T45" s="570">
+        <v>1.24</v>
       </c>
     </row>
     <row r="46">
@@ -12850,7 +12898,7 @@
       <c r="C46" t="str">
         <v>301396</v>
       </c>
-      <c r="D46" s="575" t="str">
+      <c r="D46" s="583" t="str">
         <v>净买: 9469.00万</v>
       </c>
       <c r="E46">
@@ -12865,35 +12913,37 @@
       <c r="H46">
         <v>2.83</v>
       </c>
-      <c r="I46" s="576">
+      <c r="I46" s="573">
         <v>16.7</v>
       </c>
-      <c r="J46" s="577">
+      <c r="J46" s="579">
         <v>13.98</v>
       </c>
-      <c r="K46" s="582">
+      <c r="K46" s="574">
         <v>16.53</v>
       </c>
-      <c r="L46" s="578">
+      <c r="L46" s="575">
         <v>12.63</v>
       </c>
-      <c r="M46" s="573">
+      <c r="M46" s="581">
         <v>30.75</v>
       </c>
-      <c r="N46" s="574">
+      <c r="N46" s="582">
         <v>34.4</v>
       </c>
-      <c r="O46" s="580">
+      <c r="O46" s="576">
         <v>34.05</v>
       </c>
-      <c r="P46" s="581">
+      <c r="P46" s="577">
         <v>26.29</v>
       </c>
-      <c r="Q46" t="str"/>
+      <c r="Q46" s="578">
+        <v>35.47</v>
+      </c>
       <c r="R46" t="str"/>
       <c r="S46" t="str"/>
-      <c r="T46" s="579">
-        <v>26.29</v>
+      <c r="T46" s="580">
+        <v>35.47</v>
       </c>
     </row>
     <row r="47">
@@ -12906,7 +12956,7 @@
       <c r="C47" t="str">
         <v>688677</v>
       </c>
-      <c r="D47" s="584" t="str">
+      <c r="D47" s="586" t="str">
         <v>净买: 2866.40万</v>
       </c>
       <c r="E47">
@@ -12921,10 +12971,12 @@
       <c r="H47">
         <v>2.16</v>
       </c>
-      <c r="I47" s="583">
+      <c r="I47" s="587">
         <v>17.46</v>
       </c>
-      <c r="J47" t="str"/>
+      <c r="J47" s="584">
+        <v>21.31</v>
+      </c>
       <c r="K47" t="str"/>
       <c r="L47" t="str"/>
       <c r="M47" t="str"/>
@@ -12934,7 +12986,9 @@
       <c r="Q47" t="str"/>
       <c r="R47" t="str"/>
       <c r="S47" t="str"/>
-      <c r="T47" t="str"/>
+      <c r="T47" s="585">
+        <v>21.31</v>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="str">
@@ -12951,7 +13005,7 @@
         <v>46</v>
       </c>
       <c r="J48">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K48">
         <v>45</v>
@@ -12972,7 +13026,7 @@
         <v>45</v>
       </c>
       <c r="Q48">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="R48">
         <v>44</v>
@@ -12981,7 +13035,7 @@
         <v>44</v>
       </c>
       <c r="T48">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="49">
@@ -12995,41 +13049,41 @@
       <c r="F49" t="str"/>
       <c r="G49" t="str"/>
       <c r="H49" t="str"/>
-      <c r="I49" s="585">
+      <c r="I49" s="599">
         <v>71.74</v>
       </c>
-      <c r="J49" s="586">
-        <v>64.44</v>
-      </c>
-      <c r="K49" s="587">
+      <c r="J49" s="588">
+        <v>65.22</v>
+      </c>
+      <c r="K49" s="596">
         <v>60</v>
       </c>
-      <c r="L49" s="595">
+      <c r="L49" s="597">
         <v>57.78</v>
       </c>
-      <c r="M49" s="591">
+      <c r="M49" s="594">
         <v>62.22</v>
       </c>
-      <c r="N49" s="589">
+      <c r="N49" s="595">
         <v>62.22</v>
       </c>
-      <c r="O49" s="592">
+      <c r="O49" s="589">
         <v>57.78</v>
       </c>
-      <c r="P49" s="593">
+      <c r="P49" s="592">
         <v>53.33</v>
       </c>
-      <c r="Q49" s="588">
-        <v>59.09</v>
-      </c>
-      <c r="R49" s="590">
+      <c r="Q49" s="590">
+        <v>60</v>
+      </c>
+      <c r="R49" s="591">
         <v>52.27</v>
       </c>
-      <c r="S49" s="596">
+      <c r="S49" s="593">
         <v>43.18</v>
       </c>
-      <c r="T49" s="594">
-        <v>35.56</v>
+      <c r="T49" s="598">
+        <v>32.61</v>
       </c>
     </row>
     <row r="50">
@@ -13043,41 +13097,41 @@
       <c r="F50" t="str"/>
       <c r="G50" t="str"/>
       <c r="H50" t="str"/>
-      <c r="I50" s="597">
+      <c r="I50" s="610">
         <v>5.99</v>
       </c>
-      <c r="J50" s="598">
-        <v>5.25</v>
-      </c>
-      <c r="K50" s="602">
+      <c r="J50" s="602">
+        <v>5.6</v>
+      </c>
+      <c r="K50" s="607">
         <v>4.3</v>
       </c>
-      <c r="L50" s="605">
+      <c r="L50" s="611">
         <v>3.84</v>
       </c>
-      <c r="M50" s="606">
+      <c r="M50" s="603">
         <v>4.94</v>
       </c>
-      <c r="N50" s="600">
+      <c r="N50" s="608">
         <v>5.96</v>
       </c>
-      <c r="O50" s="607">
+      <c r="O50" s="604">
         <v>4.53</v>
       </c>
-      <c r="P50" s="601">
+      <c r="P50" s="600">
         <v>3.34</v>
       </c>
-      <c r="Q50" s="599">
-        <v>3.34</v>
-      </c>
-      <c r="R50" s="608">
+      <c r="Q50" s="605">
+        <v>4.06</v>
+      </c>
+      <c r="R50" s="609">
         <v>3.21</v>
       </c>
-      <c r="S50" s="603">
+      <c r="S50" s="606">
         <v>3.56</v>
       </c>
-      <c r="T50" s="604">
-        <v>-3.25</v>
+      <c r="T50" s="601">
+        <v>-4.68</v>
       </c>
     </row>
   </sheetData>
